--- a/tracker/Partner-Direct-Tracker-TEMPLATE.xlsx
+++ b/tracker/Partner-Direct-Tracker-TEMPLATE.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Call Log" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Referral Log" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Objections" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Dashboard" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Referral Partners" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Dashboard" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -575,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B52"/>
+  <dimension ref="B2:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -641,226 +642,233 @@
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
         <is>
+          <t>Referral Partners — people who already walk into businesses you cannot reach. Give before you ask.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
           <t>Dashboard — targets vs. actual, pulled automatically from the logs. Set your Week 1 start date there.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Colour key</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Yellow cells are yours to fill in.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Blue-grey cells are calculated — don't type over them.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Grey italic rows are examples showing the expected format. Delete them once you start.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>The line</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>"I have a guy who was a client at LIV, he's in payment processing. There's a new program called</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Partner Direct — they partner customers directly with the processor, cutting out the middleman</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="4" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>cost, and rates start at three cents."</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr"/>
-    </row>
     <row r="23">
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Then stop talking.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="4" t="inlineStr"/>
-    </row>
     <row r="25">
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Technical question comes back? "I don't know that. Let me introduce you to Jeremy Schauffer."</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="3" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>The question that compounds — ask it every time, including the no's</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="4" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>"Who else do you know that takes cards?"</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="4" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Log the answer in the Call Log 'Names harvested' column. If Tier 4 stays empty, you aren't asking it.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="3" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>The handoff — same day, every time</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="4" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>To Jeremy:   Referral: [Name], [Business], [phone]. [One line on how you know them and what they're running.]</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="B34" s="4" t="inlineStr"/>
-    </row>
     <row r="35">
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>To the merchant:   [Name] — sent your info to Jeremy, he'll reach out in the next day or two.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="4" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">                   He's the one who actually knows this stuff. Any issues, tell me.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="4" t="inlineStr"/>
-    </row>
     <row r="38">
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>The second text is the part most people skip. It's what makes the introduction land.</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="3" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="3" t="inlineStr">
         <is>
           <t>Priority order (Meeting Notes §6, Rule 03)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Slam dunk   Authorize.net users — APS is one of only 11 processors directly integrated.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" s="4" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>Strong      E-commerce, and B2B (level 2/3 interchange optimization is a real edge).</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="4" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Good        Retail. Square and Clover users are worth asking.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="4" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Hardest     Restaurants, bars, lounges. Great if landed; resistance is about the solution, not the rate.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="4" t="inlineStr"/>
-    </row>
     <row r="46">
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Do not filter. Anyone who processes cards goes to Jeremy. The no's are the training.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="B48" s="3" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Don't</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="B49" s="4" t="inlineStr">
+    <row r="50">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Don't research gateways and interchange to prepare. Rule 01: knowing too much too fast is the failure mode.</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="B50" s="4" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Don't post rate numbers or the processor's name before Clay and Jeremy approve.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="4" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Don't screenshot residual income. Ever.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="4" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Don't chase. One follow-up — "Did Jeremy ever get you?" — then let it go.</t>
         </is>
@@ -15723,19 +15731,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J400"/>
+  <dimension ref="A1:L400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15753,45 +15763,55 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Sourced by</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>What they're running</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Sent merchant the heads-up text?</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>Jeremy status</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Why it didn't work</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>Date closed</t>
         </is>
       </c>
-      <c r="J2" s="6" t="inlineStr">
+      <c r="L2" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -15803,37 +15823,47 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
+          <t>Referral partner</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Dani (Breakthru liquor rep)</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
           <t>Marco Ruiz</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>Ruiz Hospitality Group</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>305-555-0142</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>Toast</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Jeremy contacted</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr"/>
-      <c r="I3" s="9" t="inlineStr"/>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr"/>
+      <c r="K3" s="9" t="inlineStr"/>
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>Wants to wait for contract end in March</t>
         </is>
@@ -15848,8 +15878,10 @@
       <c r="F4" s="10" t="n"/>
       <c r="G4" s="10" t="n"/>
       <c r="H4" s="10" t="n"/>
-      <c r="I4" s="12" t="n"/>
+      <c r="I4" s="10" t="n"/>
       <c r="J4" s="10" t="n"/>
+      <c r="K4" s="12" t="n"/>
+      <c r="L4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n"/>
@@ -15860,8 +15892,10 @@
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="10" t="n"/>
       <c r="H5" s="10" t="n"/>
-      <c r="I5" s="12" t="n"/>
+      <c r="I5" s="10" t="n"/>
       <c r="J5" s="10" t="n"/>
+      <c r="K5" s="12" t="n"/>
+      <c r="L5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n"/>
@@ -15872,8 +15906,10 @@
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="10" t="n"/>
       <c r="H6" s="10" t="n"/>
-      <c r="I6" s="12" t="n"/>
+      <c r="I6" s="10" t="n"/>
       <c r="J6" s="10" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n"/>
@@ -15884,8 +15920,10 @@
       <c r="F7" s="10" t="n"/>
       <c r="G7" s="10" t="n"/>
       <c r="H7" s="10" t="n"/>
-      <c r="I7" s="12" t="n"/>
+      <c r="I7" s="10" t="n"/>
       <c r="J7" s="10" t="n"/>
+      <c r="K7" s="12" t="n"/>
+      <c r="L7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n"/>
@@ -15896,8 +15934,10 @@
       <c r="F8" s="10" t="n"/>
       <c r="G8" s="10" t="n"/>
       <c r="H8" s="10" t="n"/>
-      <c r="I8" s="12" t="n"/>
+      <c r="I8" s="10" t="n"/>
       <c r="J8" s="10" t="n"/>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n"/>
@@ -15908,8 +15948,10 @@
       <c r="F9" s="10" t="n"/>
       <c r="G9" s="10" t="n"/>
       <c r="H9" s="10" t="n"/>
-      <c r="I9" s="12" t="n"/>
+      <c r="I9" s="10" t="n"/>
       <c r="J9" s="10" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n"/>
@@ -15920,8 +15962,10 @@
       <c r="F10" s="10" t="n"/>
       <c r="G10" s="10" t="n"/>
       <c r="H10" s="10" t="n"/>
-      <c r="I10" s="12" t="n"/>
+      <c r="I10" s="10" t="n"/>
       <c r="J10" s="10" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n"/>
@@ -15932,8 +15976,10 @@
       <c r="F11" s="10" t="n"/>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="10" t="n"/>
-      <c r="I11" s="12" t="n"/>
+      <c r="I11" s="10" t="n"/>
       <c r="J11" s="10" t="n"/>
+      <c r="K11" s="12" t="n"/>
+      <c r="L11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n"/>
@@ -15944,8 +15990,10 @@
       <c r="F12" s="10" t="n"/>
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="10" t="n"/>
-      <c r="I12" s="12" t="n"/>
+      <c r="I12" s="10" t="n"/>
       <c r="J12" s="10" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n"/>
@@ -15956,8 +16004,10 @@
       <c r="F13" s="10" t="n"/>
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="10" t="n"/>
-      <c r="I13" s="12" t="n"/>
+      <c r="I13" s="10" t="n"/>
       <c r="J13" s="10" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="n"/>
@@ -15968,8 +16018,10 @@
       <c r="F14" s="10" t="n"/>
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="10" t="n"/>
-      <c r="I14" s="12" t="n"/>
+      <c r="I14" s="10" t="n"/>
       <c r="J14" s="10" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n"/>
@@ -15980,8 +16032,10 @@
       <c r="F15" s="10" t="n"/>
       <c r="G15" s="10" t="n"/>
       <c r="H15" s="10" t="n"/>
-      <c r="I15" s="12" t="n"/>
+      <c r="I15" s="10" t="n"/>
       <c r="J15" s="10" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="n"/>
@@ -15992,8 +16046,10 @@
       <c r="F16" s="10" t="n"/>
       <c r="G16" s="10" t="n"/>
       <c r="H16" s="10" t="n"/>
-      <c r="I16" s="12" t="n"/>
+      <c r="I16" s="10" t="n"/>
       <c r="J16" s="10" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="n"/>
@@ -16004,8 +16060,10 @@
       <c r="F17" s="10" t="n"/>
       <c r="G17" s="10" t="n"/>
       <c r="H17" s="10" t="n"/>
-      <c r="I17" s="12" t="n"/>
+      <c r="I17" s="10" t="n"/>
       <c r="J17" s="10" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n"/>
@@ -16016,8 +16074,10 @@
       <c r="F18" s="10" t="n"/>
       <c r="G18" s="10" t="n"/>
       <c r="H18" s="10" t="n"/>
-      <c r="I18" s="12" t="n"/>
+      <c r="I18" s="10" t="n"/>
       <c r="J18" s="10" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="10" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="n"/>
@@ -16028,8 +16088,10 @@
       <c r="F19" s="10" t="n"/>
       <c r="G19" s="10" t="n"/>
       <c r="H19" s="10" t="n"/>
-      <c r="I19" s="12" t="n"/>
+      <c r="I19" s="10" t="n"/>
       <c r="J19" s="10" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="10" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n"/>
@@ -16040,8 +16102,10 @@
       <c r="F20" s="10" t="n"/>
       <c r="G20" s="10" t="n"/>
       <c r="H20" s="10" t="n"/>
-      <c r="I20" s="12" t="n"/>
+      <c r="I20" s="10" t="n"/>
       <c r="J20" s="10" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="10" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="n"/>
@@ -16052,8 +16116,10 @@
       <c r="F21" s="10" t="n"/>
       <c r="G21" s="10" t="n"/>
       <c r="H21" s="10" t="n"/>
-      <c r="I21" s="12" t="n"/>
+      <c r="I21" s="10" t="n"/>
       <c r="J21" s="10" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n"/>
@@ -16064,8 +16130,10 @@
       <c r="F22" s="10" t="n"/>
       <c r="G22" s="10" t="n"/>
       <c r="H22" s="10" t="n"/>
-      <c r="I22" s="12" t="n"/>
+      <c r="I22" s="10" t="n"/>
       <c r="J22" s="10" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="12" t="n"/>
@@ -16076,8 +16144,10 @@
       <c r="F23" s="10" t="n"/>
       <c r="G23" s="10" t="n"/>
       <c r="H23" s="10" t="n"/>
-      <c r="I23" s="12" t="n"/>
+      <c r="I23" s="10" t="n"/>
       <c r="J23" s="10" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n"/>
@@ -16088,8 +16158,10 @@
       <c r="F24" s="10" t="n"/>
       <c r="G24" s="10" t="n"/>
       <c r="H24" s="10" t="n"/>
-      <c r="I24" s="12" t="n"/>
+      <c r="I24" s="10" t="n"/>
       <c r="J24" s="10" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="12" t="n"/>
@@ -16100,8 +16172,10 @@
       <c r="F25" s="10" t="n"/>
       <c r="G25" s="10" t="n"/>
       <c r="H25" s="10" t="n"/>
-      <c r="I25" s="12" t="n"/>
+      <c r="I25" s="10" t="n"/>
       <c r="J25" s="10" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="10" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n"/>
@@ -16112,8 +16186,10 @@
       <c r="F26" s="10" t="n"/>
       <c r="G26" s="10" t="n"/>
       <c r="H26" s="10" t="n"/>
-      <c r="I26" s="12" t="n"/>
+      <c r="I26" s="10" t="n"/>
       <c r="J26" s="10" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="10" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="n"/>
@@ -16124,8 +16200,10 @@
       <c r="F27" s="10" t="n"/>
       <c r="G27" s="10" t="n"/>
       <c r="H27" s="10" t="n"/>
-      <c r="I27" s="12" t="n"/>
+      <c r="I27" s="10" t="n"/>
       <c r="J27" s="10" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="10" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n"/>
@@ -16136,8 +16214,10 @@
       <c r="F28" s="10" t="n"/>
       <c r="G28" s="10" t="n"/>
       <c r="H28" s="10" t="n"/>
-      <c r="I28" s="12" t="n"/>
+      <c r="I28" s="10" t="n"/>
       <c r="J28" s="10" t="n"/>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="12" t="n"/>
@@ -16148,8 +16228,10 @@
       <c r="F29" s="10" t="n"/>
       <c r="G29" s="10" t="n"/>
       <c r="H29" s="10" t="n"/>
-      <c r="I29" s="12" t="n"/>
+      <c r="I29" s="10" t="n"/>
       <c r="J29" s="10" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n"/>
@@ -16160,8 +16242,10 @@
       <c r="F30" s="10" t="n"/>
       <c r="G30" s="10" t="n"/>
       <c r="H30" s="10" t="n"/>
-      <c r="I30" s="12" t="n"/>
+      <c r="I30" s="10" t="n"/>
       <c r="J30" s="10" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="10" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="12" t="n"/>
@@ -16172,8 +16256,10 @@
       <c r="F31" s="10" t="n"/>
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="10" t="n"/>
-      <c r="I31" s="12" t="n"/>
+      <c r="I31" s="10" t="n"/>
       <c r="J31" s="10" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="10" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n"/>
@@ -16184,8 +16270,10 @@
       <c r="F32" s="10" t="n"/>
       <c r="G32" s="10" t="n"/>
       <c r="H32" s="10" t="n"/>
-      <c r="I32" s="12" t="n"/>
+      <c r="I32" s="10" t="n"/>
       <c r="J32" s="10" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="10" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="12" t="n"/>
@@ -16196,8 +16284,10 @@
       <c r="F33" s="10" t="n"/>
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="10" t="n"/>
-      <c r="I33" s="12" t="n"/>
+      <c r="I33" s="10" t="n"/>
       <c r="J33" s="10" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="10" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="n"/>
@@ -16208,8 +16298,10 @@
       <c r="F34" s="10" t="n"/>
       <c r="G34" s="10" t="n"/>
       <c r="H34" s="10" t="n"/>
-      <c r="I34" s="12" t="n"/>
+      <c r="I34" s="10" t="n"/>
       <c r="J34" s="10" t="n"/>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="10" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="12" t="n"/>
@@ -16220,8 +16312,10 @@
       <c r="F35" s="10" t="n"/>
       <c r="G35" s="10" t="n"/>
       <c r="H35" s="10" t="n"/>
-      <c r="I35" s="12" t="n"/>
+      <c r="I35" s="10" t="n"/>
       <c r="J35" s="10" t="n"/>
+      <c r="K35" s="12" t="n"/>
+      <c r="L35" s="10" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="12" t="n"/>
@@ -16232,8 +16326,10 @@
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="10" t="n"/>
       <c r="H36" s="10" t="n"/>
-      <c r="I36" s="12" t="n"/>
+      <c r="I36" s="10" t="n"/>
       <c r="J36" s="10" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="10" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="12" t="n"/>
@@ -16244,8 +16340,10 @@
       <c r="F37" s="10" t="n"/>
       <c r="G37" s="10" t="n"/>
       <c r="H37" s="10" t="n"/>
-      <c r="I37" s="12" t="n"/>
+      <c r="I37" s="10" t="n"/>
       <c r="J37" s="10" t="n"/>
+      <c r="K37" s="12" t="n"/>
+      <c r="L37" s="10" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="12" t="n"/>
@@ -16256,8 +16354,10 @@
       <c r="F38" s="10" t="n"/>
       <c r="G38" s="10" t="n"/>
       <c r="H38" s="10" t="n"/>
-      <c r="I38" s="12" t="n"/>
+      <c r="I38" s="10" t="n"/>
       <c r="J38" s="10" t="n"/>
+      <c r="K38" s="12" t="n"/>
+      <c r="L38" s="10" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="12" t="n"/>
@@ -16268,8 +16368,10 @@
       <c r="F39" s="10" t="n"/>
       <c r="G39" s="10" t="n"/>
       <c r="H39" s="10" t="n"/>
-      <c r="I39" s="12" t="n"/>
+      <c r="I39" s="10" t="n"/>
       <c r="J39" s="10" t="n"/>
+      <c r="K39" s="12" t="n"/>
+      <c r="L39" s="10" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="12" t="n"/>
@@ -16280,8 +16382,10 @@
       <c r="F40" s="10" t="n"/>
       <c r="G40" s="10" t="n"/>
       <c r="H40" s="10" t="n"/>
-      <c r="I40" s="12" t="n"/>
+      <c r="I40" s="10" t="n"/>
       <c r="J40" s="10" t="n"/>
+      <c r="K40" s="12" t="n"/>
+      <c r="L40" s="10" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="n"/>
@@ -16292,8 +16396,10 @@
       <c r="F41" s="10" t="n"/>
       <c r="G41" s="10" t="n"/>
       <c r="H41" s="10" t="n"/>
-      <c r="I41" s="12" t="n"/>
+      <c r="I41" s="10" t="n"/>
       <c r="J41" s="10" t="n"/>
+      <c r="K41" s="12" t="n"/>
+      <c r="L41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="12" t="n"/>
@@ -16304,8 +16410,10 @@
       <c r="F42" s="10" t="n"/>
       <c r="G42" s="10" t="n"/>
       <c r="H42" s="10" t="n"/>
-      <c r="I42" s="12" t="n"/>
+      <c r="I42" s="10" t="n"/>
       <c r="J42" s="10" t="n"/>
+      <c r="K42" s="12" t="n"/>
+      <c r="L42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="12" t="n"/>
@@ -16316,8 +16424,10 @@
       <c r="F43" s="10" t="n"/>
       <c r="G43" s="10" t="n"/>
       <c r="H43" s="10" t="n"/>
-      <c r="I43" s="12" t="n"/>
+      <c r="I43" s="10" t="n"/>
       <c r="J43" s="10" t="n"/>
+      <c r="K43" s="12" t="n"/>
+      <c r="L43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="12" t="n"/>
@@ -16328,8 +16438,10 @@
       <c r="F44" s="10" t="n"/>
       <c r="G44" s="10" t="n"/>
       <c r="H44" s="10" t="n"/>
-      <c r="I44" s="12" t="n"/>
+      <c r="I44" s="10" t="n"/>
       <c r="J44" s="10" t="n"/>
+      <c r="K44" s="12" t="n"/>
+      <c r="L44" s="10" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="12" t="n"/>
@@ -16340,8 +16452,10 @@
       <c r="F45" s="10" t="n"/>
       <c r="G45" s="10" t="n"/>
       <c r="H45" s="10" t="n"/>
-      <c r="I45" s="12" t="n"/>
+      <c r="I45" s="10" t="n"/>
       <c r="J45" s="10" t="n"/>
+      <c r="K45" s="12" t="n"/>
+      <c r="L45" s="10" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="12" t="n"/>
@@ -16352,8 +16466,10 @@
       <c r="F46" s="10" t="n"/>
       <c r="G46" s="10" t="n"/>
       <c r="H46" s="10" t="n"/>
-      <c r="I46" s="12" t="n"/>
+      <c r="I46" s="10" t="n"/>
       <c r="J46" s="10" t="n"/>
+      <c r="K46" s="12" t="n"/>
+      <c r="L46" s="10" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="n"/>
@@ -16364,8 +16480,10 @@
       <c r="F47" s="10" t="n"/>
       <c r="G47" s="10" t="n"/>
       <c r="H47" s="10" t="n"/>
-      <c r="I47" s="12" t="n"/>
+      <c r="I47" s="10" t="n"/>
       <c r="J47" s="10" t="n"/>
+      <c r="K47" s="12" t="n"/>
+      <c r="L47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="12" t="n"/>
@@ -16376,8 +16494,10 @@
       <c r="F48" s="10" t="n"/>
       <c r="G48" s="10" t="n"/>
       <c r="H48" s="10" t="n"/>
-      <c r="I48" s="12" t="n"/>
+      <c r="I48" s="10" t="n"/>
       <c r="J48" s="10" t="n"/>
+      <c r="K48" s="12" t="n"/>
+      <c r="L48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="12" t="n"/>
@@ -16388,8 +16508,10 @@
       <c r="F49" s="10" t="n"/>
       <c r="G49" s="10" t="n"/>
       <c r="H49" s="10" t="n"/>
-      <c r="I49" s="12" t="n"/>
+      <c r="I49" s="10" t="n"/>
       <c r="J49" s="10" t="n"/>
+      <c r="K49" s="12" t="n"/>
+      <c r="L49" s="10" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="12" t="n"/>
@@ -16400,8 +16522,10 @@
       <c r="F50" s="10" t="n"/>
       <c r="G50" s="10" t="n"/>
       <c r="H50" s="10" t="n"/>
-      <c r="I50" s="12" t="n"/>
+      <c r="I50" s="10" t="n"/>
       <c r="J50" s="10" t="n"/>
+      <c r="K50" s="12" t="n"/>
+      <c r="L50" s="10" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="12" t="n"/>
@@ -16412,8 +16536,10 @@
       <c r="F51" s="10" t="n"/>
       <c r="G51" s="10" t="n"/>
       <c r="H51" s="10" t="n"/>
-      <c r="I51" s="12" t="n"/>
+      <c r="I51" s="10" t="n"/>
       <c r="J51" s="10" t="n"/>
+      <c r="K51" s="12" t="n"/>
+      <c r="L51" s="10" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="12" t="n"/>
@@ -16424,8 +16550,10 @@
       <c r="F52" s="10" t="n"/>
       <c r="G52" s="10" t="n"/>
       <c r="H52" s="10" t="n"/>
-      <c r="I52" s="12" t="n"/>
+      <c r="I52" s="10" t="n"/>
       <c r="J52" s="10" t="n"/>
+      <c r="K52" s="12" t="n"/>
+      <c r="L52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="12" t="n"/>
@@ -16436,8 +16564,10 @@
       <c r="F53" s="10" t="n"/>
       <c r="G53" s="10" t="n"/>
       <c r="H53" s="10" t="n"/>
-      <c r="I53" s="12" t="n"/>
+      <c r="I53" s="10" t="n"/>
       <c r="J53" s="10" t="n"/>
+      <c r="K53" s="12" t="n"/>
+      <c r="L53" s="10" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="12" t="n"/>
@@ -16448,8 +16578,10 @@
       <c r="F54" s="10" t="n"/>
       <c r="G54" s="10" t="n"/>
       <c r="H54" s="10" t="n"/>
-      <c r="I54" s="12" t="n"/>
+      <c r="I54" s="10" t="n"/>
       <c r="J54" s="10" t="n"/>
+      <c r="K54" s="12" t="n"/>
+      <c r="L54" s="10" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="12" t="n"/>
@@ -16460,8 +16592,10 @@
       <c r="F55" s="10" t="n"/>
       <c r="G55" s="10" t="n"/>
       <c r="H55" s="10" t="n"/>
-      <c r="I55" s="12" t="n"/>
+      <c r="I55" s="10" t="n"/>
       <c r="J55" s="10" t="n"/>
+      <c r="K55" s="12" t="n"/>
+      <c r="L55" s="10" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="12" t="n"/>
@@ -16472,8 +16606,10 @@
       <c r="F56" s="10" t="n"/>
       <c r="G56" s="10" t="n"/>
       <c r="H56" s="10" t="n"/>
-      <c r="I56" s="12" t="n"/>
+      <c r="I56" s="10" t="n"/>
       <c r="J56" s="10" t="n"/>
+      <c r="K56" s="12" t="n"/>
+      <c r="L56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="12" t="n"/>
@@ -16484,8 +16620,10 @@
       <c r="F57" s="10" t="n"/>
       <c r="G57" s="10" t="n"/>
       <c r="H57" s="10" t="n"/>
-      <c r="I57" s="12" t="n"/>
+      <c r="I57" s="10" t="n"/>
       <c r="J57" s="10" t="n"/>
+      <c r="K57" s="12" t="n"/>
+      <c r="L57" s="10" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="12" t="n"/>
@@ -16496,8 +16634,10 @@
       <c r="F58" s="10" t="n"/>
       <c r="G58" s="10" t="n"/>
       <c r="H58" s="10" t="n"/>
-      <c r="I58" s="12" t="n"/>
+      <c r="I58" s="10" t="n"/>
       <c r="J58" s="10" t="n"/>
+      <c r="K58" s="12" t="n"/>
+      <c r="L58" s="10" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="n"/>
@@ -16508,8 +16648,10 @@
       <c r="F59" s="10" t="n"/>
       <c r="G59" s="10" t="n"/>
       <c r="H59" s="10" t="n"/>
-      <c r="I59" s="12" t="n"/>
+      <c r="I59" s="10" t="n"/>
       <c r="J59" s="10" t="n"/>
+      <c r="K59" s="12" t="n"/>
+      <c r="L59" s="10" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="12" t="n"/>
@@ -16520,8 +16662,10 @@
       <c r="F60" s="10" t="n"/>
       <c r="G60" s="10" t="n"/>
       <c r="H60" s="10" t="n"/>
-      <c r="I60" s="12" t="n"/>
+      <c r="I60" s="10" t="n"/>
       <c r="J60" s="10" t="n"/>
+      <c r="K60" s="12" t="n"/>
+      <c r="L60" s="10" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="12" t="n"/>
@@ -16532,8 +16676,10 @@
       <c r="F61" s="10" t="n"/>
       <c r="G61" s="10" t="n"/>
       <c r="H61" s="10" t="n"/>
-      <c r="I61" s="12" t="n"/>
+      <c r="I61" s="10" t="n"/>
       <c r="J61" s="10" t="n"/>
+      <c r="K61" s="12" t="n"/>
+      <c r="L61" s="10" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="n"/>
@@ -16544,8 +16690,10 @@
       <c r="F62" s="10" t="n"/>
       <c r="G62" s="10" t="n"/>
       <c r="H62" s="10" t="n"/>
-      <c r="I62" s="12" t="n"/>
+      <c r="I62" s="10" t="n"/>
       <c r="J62" s="10" t="n"/>
+      <c r="K62" s="12" t="n"/>
+      <c r="L62" s="10" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="n"/>
@@ -16556,8 +16704,10 @@
       <c r="F63" s="10" t="n"/>
       <c r="G63" s="10" t="n"/>
       <c r="H63" s="10" t="n"/>
-      <c r="I63" s="12" t="n"/>
+      <c r="I63" s="10" t="n"/>
       <c r="J63" s="10" t="n"/>
+      <c r="K63" s="12" t="n"/>
+      <c r="L63" s="10" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="12" t="n"/>
@@ -16568,8 +16718,10 @@
       <c r="F64" s="10" t="n"/>
       <c r="G64" s="10" t="n"/>
       <c r="H64" s="10" t="n"/>
-      <c r="I64" s="12" t="n"/>
+      <c r="I64" s="10" t="n"/>
       <c r="J64" s="10" t="n"/>
+      <c r="K64" s="12" t="n"/>
+      <c r="L64" s="10" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="12" t="n"/>
@@ -16580,8 +16732,10 @@
       <c r="F65" s="10" t="n"/>
       <c r="G65" s="10" t="n"/>
       <c r="H65" s="10" t="n"/>
-      <c r="I65" s="12" t="n"/>
+      <c r="I65" s="10" t="n"/>
       <c r="J65" s="10" t="n"/>
+      <c r="K65" s="12" t="n"/>
+      <c r="L65" s="10" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="12" t="n"/>
@@ -16592,8 +16746,10 @@
       <c r="F66" s="10" t="n"/>
       <c r="G66" s="10" t="n"/>
       <c r="H66" s="10" t="n"/>
-      <c r="I66" s="12" t="n"/>
+      <c r="I66" s="10" t="n"/>
       <c r="J66" s="10" t="n"/>
+      <c r="K66" s="12" t="n"/>
+      <c r="L66" s="10" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="12" t="n"/>
@@ -16604,8 +16760,10 @@
       <c r="F67" s="10" t="n"/>
       <c r="G67" s="10" t="n"/>
       <c r="H67" s="10" t="n"/>
-      <c r="I67" s="12" t="n"/>
+      <c r="I67" s="10" t="n"/>
       <c r="J67" s="10" t="n"/>
+      <c r="K67" s="12" t="n"/>
+      <c r="L67" s="10" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="12" t="n"/>
@@ -16616,8 +16774,10 @@
       <c r="F68" s="10" t="n"/>
       <c r="G68" s="10" t="n"/>
       <c r="H68" s="10" t="n"/>
-      <c r="I68" s="12" t="n"/>
+      <c r="I68" s="10" t="n"/>
       <c r="J68" s="10" t="n"/>
+      <c r="K68" s="12" t="n"/>
+      <c r="L68" s="10" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="12" t="n"/>
@@ -16628,8 +16788,10 @@
       <c r="F69" s="10" t="n"/>
       <c r="G69" s="10" t="n"/>
       <c r="H69" s="10" t="n"/>
-      <c r="I69" s="12" t="n"/>
+      <c r="I69" s="10" t="n"/>
       <c r="J69" s="10" t="n"/>
+      <c r="K69" s="12" t="n"/>
+      <c r="L69" s="10" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="12" t="n"/>
@@ -16640,8 +16802,10 @@
       <c r="F70" s="10" t="n"/>
       <c r="G70" s="10" t="n"/>
       <c r="H70" s="10" t="n"/>
-      <c r="I70" s="12" t="n"/>
+      <c r="I70" s="10" t="n"/>
       <c r="J70" s="10" t="n"/>
+      <c r="K70" s="12" t="n"/>
+      <c r="L70" s="10" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="12" t="n"/>
@@ -16652,8 +16816,10 @@
       <c r="F71" s="10" t="n"/>
       <c r="G71" s="10" t="n"/>
       <c r="H71" s="10" t="n"/>
-      <c r="I71" s="12" t="n"/>
+      <c r="I71" s="10" t="n"/>
       <c r="J71" s="10" t="n"/>
+      <c r="K71" s="12" t="n"/>
+      <c r="L71" s="10" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="12" t="n"/>
@@ -16664,8 +16830,10 @@
       <c r="F72" s="10" t="n"/>
       <c r="G72" s="10" t="n"/>
       <c r="H72" s="10" t="n"/>
-      <c r="I72" s="12" t="n"/>
+      <c r="I72" s="10" t="n"/>
       <c r="J72" s="10" t="n"/>
+      <c r="K72" s="12" t="n"/>
+      <c r="L72" s="10" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="12" t="n"/>
@@ -16676,8 +16844,10 @@
       <c r="F73" s="10" t="n"/>
       <c r="G73" s="10" t="n"/>
       <c r="H73" s="10" t="n"/>
-      <c r="I73" s="12" t="n"/>
+      <c r="I73" s="10" t="n"/>
       <c r="J73" s="10" t="n"/>
+      <c r="K73" s="12" t="n"/>
+      <c r="L73" s="10" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="12" t="n"/>
@@ -16688,8 +16858,10 @@
       <c r="F74" s="10" t="n"/>
       <c r="G74" s="10" t="n"/>
       <c r="H74" s="10" t="n"/>
-      <c r="I74" s="12" t="n"/>
+      <c r="I74" s="10" t="n"/>
       <c r="J74" s="10" t="n"/>
+      <c r="K74" s="12" t="n"/>
+      <c r="L74" s="10" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="12" t="n"/>
@@ -16700,8 +16872,10 @@
       <c r="F75" s="10" t="n"/>
       <c r="G75" s="10" t="n"/>
       <c r="H75" s="10" t="n"/>
-      <c r="I75" s="12" t="n"/>
+      <c r="I75" s="10" t="n"/>
       <c r="J75" s="10" t="n"/>
+      <c r="K75" s="12" t="n"/>
+      <c r="L75" s="10" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="12" t="n"/>
@@ -16712,8 +16886,10 @@
       <c r="F76" s="10" t="n"/>
       <c r="G76" s="10" t="n"/>
       <c r="H76" s="10" t="n"/>
-      <c r="I76" s="12" t="n"/>
+      <c r="I76" s="10" t="n"/>
       <c r="J76" s="10" t="n"/>
+      <c r="K76" s="12" t="n"/>
+      <c r="L76" s="10" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="12" t="n"/>
@@ -16724,8 +16900,10 @@
       <c r="F77" s="10" t="n"/>
       <c r="G77" s="10" t="n"/>
       <c r="H77" s="10" t="n"/>
-      <c r="I77" s="12" t="n"/>
+      <c r="I77" s="10" t="n"/>
       <c r="J77" s="10" t="n"/>
+      <c r="K77" s="12" t="n"/>
+      <c r="L77" s="10" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="12" t="n"/>
@@ -16736,8 +16914,10 @@
       <c r="F78" s="10" t="n"/>
       <c r="G78" s="10" t="n"/>
       <c r="H78" s="10" t="n"/>
-      <c r="I78" s="12" t="n"/>
+      <c r="I78" s="10" t="n"/>
       <c r="J78" s="10" t="n"/>
+      <c r="K78" s="12" t="n"/>
+      <c r="L78" s="10" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="12" t="n"/>
@@ -16748,8 +16928,10 @@
       <c r="F79" s="10" t="n"/>
       <c r="G79" s="10" t="n"/>
       <c r="H79" s="10" t="n"/>
-      <c r="I79" s="12" t="n"/>
+      <c r="I79" s="10" t="n"/>
       <c r="J79" s="10" t="n"/>
+      <c r="K79" s="12" t="n"/>
+      <c r="L79" s="10" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="12" t="n"/>
@@ -16760,8 +16942,10 @@
       <c r="F80" s="10" t="n"/>
       <c r="G80" s="10" t="n"/>
       <c r="H80" s="10" t="n"/>
-      <c r="I80" s="12" t="n"/>
+      <c r="I80" s="10" t="n"/>
       <c r="J80" s="10" t="n"/>
+      <c r="K80" s="12" t="n"/>
+      <c r="L80" s="10" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="12" t="n"/>
@@ -16772,8 +16956,10 @@
       <c r="F81" s="10" t="n"/>
       <c r="G81" s="10" t="n"/>
       <c r="H81" s="10" t="n"/>
-      <c r="I81" s="12" t="n"/>
+      <c r="I81" s="10" t="n"/>
       <c r="J81" s="10" t="n"/>
+      <c r="K81" s="12" t="n"/>
+      <c r="L81" s="10" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="12" t="n"/>
@@ -16784,8 +16970,10 @@
       <c r="F82" s="10" t="n"/>
       <c r="G82" s="10" t="n"/>
       <c r="H82" s="10" t="n"/>
-      <c r="I82" s="12" t="n"/>
+      <c r="I82" s="10" t="n"/>
       <c r="J82" s="10" t="n"/>
+      <c r="K82" s="12" t="n"/>
+      <c r="L82" s="10" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="12" t="n"/>
@@ -16796,8 +16984,10 @@
       <c r="F83" s="10" t="n"/>
       <c r="G83" s="10" t="n"/>
       <c r="H83" s="10" t="n"/>
-      <c r="I83" s="12" t="n"/>
+      <c r="I83" s="10" t="n"/>
       <c r="J83" s="10" t="n"/>
+      <c r="K83" s="12" t="n"/>
+      <c r="L83" s="10" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="12" t="n"/>
@@ -16808,8 +16998,10 @@
       <c r="F84" s="10" t="n"/>
       <c r="G84" s="10" t="n"/>
       <c r="H84" s="10" t="n"/>
-      <c r="I84" s="12" t="n"/>
+      <c r="I84" s="10" t="n"/>
       <c r="J84" s="10" t="n"/>
+      <c r="K84" s="12" t="n"/>
+      <c r="L84" s="10" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="12" t="n"/>
@@ -16820,8 +17012,10 @@
       <c r="F85" s="10" t="n"/>
       <c r="G85" s="10" t="n"/>
       <c r="H85" s="10" t="n"/>
-      <c r="I85" s="12" t="n"/>
+      <c r="I85" s="10" t="n"/>
       <c r="J85" s="10" t="n"/>
+      <c r="K85" s="12" t="n"/>
+      <c r="L85" s="10" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="12" t="n"/>
@@ -16832,8 +17026,10 @@
       <c r="F86" s="10" t="n"/>
       <c r="G86" s="10" t="n"/>
       <c r="H86" s="10" t="n"/>
-      <c r="I86" s="12" t="n"/>
+      <c r="I86" s="10" t="n"/>
       <c r="J86" s="10" t="n"/>
+      <c r="K86" s="12" t="n"/>
+      <c r="L86" s="10" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="12" t="n"/>
@@ -16844,8 +17040,10 @@
       <c r="F87" s="10" t="n"/>
       <c r="G87" s="10" t="n"/>
       <c r="H87" s="10" t="n"/>
-      <c r="I87" s="12" t="n"/>
+      <c r="I87" s="10" t="n"/>
       <c r="J87" s="10" t="n"/>
+      <c r="K87" s="12" t="n"/>
+      <c r="L87" s="10" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="12" t="n"/>
@@ -16856,8 +17054,10 @@
       <c r="F88" s="10" t="n"/>
       <c r="G88" s="10" t="n"/>
       <c r="H88" s="10" t="n"/>
-      <c r="I88" s="12" t="n"/>
+      <c r="I88" s="10" t="n"/>
       <c r="J88" s="10" t="n"/>
+      <c r="K88" s="12" t="n"/>
+      <c r="L88" s="10" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="12" t="n"/>
@@ -16868,8 +17068,10 @@
       <c r="F89" s="10" t="n"/>
       <c r="G89" s="10" t="n"/>
       <c r="H89" s="10" t="n"/>
-      <c r="I89" s="12" t="n"/>
+      <c r="I89" s="10" t="n"/>
       <c r="J89" s="10" t="n"/>
+      <c r="K89" s="12" t="n"/>
+      <c r="L89" s="10" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="12" t="n"/>
@@ -16880,8 +17082,10 @@
       <c r="F90" s="10" t="n"/>
       <c r="G90" s="10" t="n"/>
       <c r="H90" s="10" t="n"/>
-      <c r="I90" s="12" t="n"/>
+      <c r="I90" s="10" t="n"/>
       <c r="J90" s="10" t="n"/>
+      <c r="K90" s="12" t="n"/>
+      <c r="L90" s="10" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="12" t="n"/>
@@ -16892,8 +17096,10 @@
       <c r="F91" s="10" t="n"/>
       <c r="G91" s="10" t="n"/>
       <c r="H91" s="10" t="n"/>
-      <c r="I91" s="12" t="n"/>
+      <c r="I91" s="10" t="n"/>
       <c r="J91" s="10" t="n"/>
+      <c r="K91" s="12" t="n"/>
+      <c r="L91" s="10" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="12" t="n"/>
@@ -16904,8 +17110,10 @@
       <c r="F92" s="10" t="n"/>
       <c r="G92" s="10" t="n"/>
       <c r="H92" s="10" t="n"/>
-      <c r="I92" s="12" t="n"/>
+      <c r="I92" s="10" t="n"/>
       <c r="J92" s="10" t="n"/>
+      <c r="K92" s="12" t="n"/>
+      <c r="L92" s="10" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="12" t="n"/>
@@ -16916,8 +17124,10 @@
       <c r="F93" s="10" t="n"/>
       <c r="G93" s="10" t="n"/>
       <c r="H93" s="10" t="n"/>
-      <c r="I93" s="12" t="n"/>
+      <c r="I93" s="10" t="n"/>
       <c r="J93" s="10" t="n"/>
+      <c r="K93" s="12" t="n"/>
+      <c r="L93" s="10" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="12" t="n"/>
@@ -16928,8 +17138,10 @@
       <c r="F94" s="10" t="n"/>
       <c r="G94" s="10" t="n"/>
       <c r="H94" s="10" t="n"/>
-      <c r="I94" s="12" t="n"/>
+      <c r="I94" s="10" t="n"/>
       <c r="J94" s="10" t="n"/>
+      <c r="K94" s="12" t="n"/>
+      <c r="L94" s="10" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="12" t="n"/>
@@ -16940,8 +17152,10 @@
       <c r="F95" s="10" t="n"/>
       <c r="G95" s="10" t="n"/>
       <c r="H95" s="10" t="n"/>
-      <c r="I95" s="12" t="n"/>
+      <c r="I95" s="10" t="n"/>
       <c r="J95" s="10" t="n"/>
+      <c r="K95" s="12" t="n"/>
+      <c r="L95" s="10" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="12" t="n"/>
@@ -16952,8 +17166,10 @@
       <c r="F96" s="10" t="n"/>
       <c r="G96" s="10" t="n"/>
       <c r="H96" s="10" t="n"/>
-      <c r="I96" s="12" t="n"/>
+      <c r="I96" s="10" t="n"/>
       <c r="J96" s="10" t="n"/>
+      <c r="K96" s="12" t="n"/>
+      <c r="L96" s="10" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="12" t="n"/>
@@ -16964,8 +17180,10 @@
       <c r="F97" s="10" t="n"/>
       <c r="G97" s="10" t="n"/>
       <c r="H97" s="10" t="n"/>
-      <c r="I97" s="12" t="n"/>
+      <c r="I97" s="10" t="n"/>
       <c r="J97" s="10" t="n"/>
+      <c r="K97" s="12" t="n"/>
+      <c r="L97" s="10" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="12" t="n"/>
@@ -16976,8 +17194,10 @@
       <c r="F98" s="10" t="n"/>
       <c r="G98" s="10" t="n"/>
       <c r="H98" s="10" t="n"/>
-      <c r="I98" s="12" t="n"/>
+      <c r="I98" s="10" t="n"/>
       <c r="J98" s="10" t="n"/>
+      <c r="K98" s="12" t="n"/>
+      <c r="L98" s="10" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="12" t="n"/>
@@ -16988,8 +17208,10 @@
       <c r="F99" s="10" t="n"/>
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="n"/>
-      <c r="I99" s="12" t="n"/>
+      <c r="I99" s="10" t="n"/>
       <c r="J99" s="10" t="n"/>
+      <c r="K99" s="12" t="n"/>
+      <c r="L99" s="10" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="12" t="n"/>
@@ -17000,8 +17222,10 @@
       <c r="F100" s="10" t="n"/>
       <c r="G100" s="10" t="n"/>
       <c r="H100" s="10" t="n"/>
-      <c r="I100" s="12" t="n"/>
+      <c r="I100" s="10" t="n"/>
       <c r="J100" s="10" t="n"/>
+      <c r="K100" s="12" t="n"/>
+      <c r="L100" s="10" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="12" t="n"/>
@@ -17012,8 +17236,10 @@
       <c r="F101" s="10" t="n"/>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n"/>
-      <c r="I101" s="12" t="n"/>
+      <c r="I101" s="10" t="n"/>
       <c r="J101" s="10" t="n"/>
+      <c r="K101" s="12" t="n"/>
+      <c r="L101" s="10" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="12" t="n"/>
@@ -17024,8 +17250,10 @@
       <c r="F102" s="10" t="n"/>
       <c r="G102" s="10" t="n"/>
       <c r="H102" s="10" t="n"/>
-      <c r="I102" s="12" t="n"/>
+      <c r="I102" s="10" t="n"/>
       <c r="J102" s="10" t="n"/>
+      <c r="K102" s="12" t="n"/>
+      <c r="L102" s="10" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="12" t="n"/>
@@ -17036,8 +17264,10 @@
       <c r="F103" s="10" t="n"/>
       <c r="G103" s="10" t="n"/>
       <c r="H103" s="10" t="n"/>
-      <c r="I103" s="12" t="n"/>
+      <c r="I103" s="10" t="n"/>
       <c r="J103" s="10" t="n"/>
+      <c r="K103" s="12" t="n"/>
+      <c r="L103" s="10" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="12" t="n"/>
@@ -17048,8 +17278,10 @@
       <c r="F104" s="10" t="n"/>
       <c r="G104" s="10" t="n"/>
       <c r="H104" s="10" t="n"/>
-      <c r="I104" s="12" t="n"/>
+      <c r="I104" s="10" t="n"/>
       <c r="J104" s="10" t="n"/>
+      <c r="K104" s="12" t="n"/>
+      <c r="L104" s="10" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="12" t="n"/>
@@ -17060,8 +17292,10 @@
       <c r="F105" s="10" t="n"/>
       <c r="G105" s="10" t="n"/>
       <c r="H105" s="10" t="n"/>
-      <c r="I105" s="12" t="n"/>
+      <c r="I105" s="10" t="n"/>
       <c r="J105" s="10" t="n"/>
+      <c r="K105" s="12" t="n"/>
+      <c r="L105" s="10" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="12" t="n"/>
@@ -17072,8 +17306,10 @@
       <c r="F106" s="10" t="n"/>
       <c r="G106" s="10" t="n"/>
       <c r="H106" s="10" t="n"/>
-      <c r="I106" s="12" t="n"/>
+      <c r="I106" s="10" t="n"/>
       <c r="J106" s="10" t="n"/>
+      <c r="K106" s="12" t="n"/>
+      <c r="L106" s="10" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="12" t="n"/>
@@ -17084,8 +17320,10 @@
       <c r="F107" s="10" t="n"/>
       <c r="G107" s="10" t="n"/>
       <c r="H107" s="10" t="n"/>
-      <c r="I107" s="12" t="n"/>
+      <c r="I107" s="10" t="n"/>
       <c r="J107" s="10" t="n"/>
+      <c r="K107" s="12" t="n"/>
+      <c r="L107" s="10" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="12" t="n"/>
@@ -17096,8 +17334,10 @@
       <c r="F108" s="10" t="n"/>
       <c r="G108" s="10" t="n"/>
       <c r="H108" s="10" t="n"/>
-      <c r="I108" s="12" t="n"/>
+      <c r="I108" s="10" t="n"/>
       <c r="J108" s="10" t="n"/>
+      <c r="K108" s="12" t="n"/>
+      <c r="L108" s="10" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="12" t="n"/>
@@ -17108,8 +17348,10 @@
       <c r="F109" s="10" t="n"/>
       <c r="G109" s="10" t="n"/>
       <c r="H109" s="10" t="n"/>
-      <c r="I109" s="12" t="n"/>
+      <c r="I109" s="10" t="n"/>
       <c r="J109" s="10" t="n"/>
+      <c r="K109" s="12" t="n"/>
+      <c r="L109" s="10" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="12" t="n"/>
@@ -17120,8 +17362,10 @@
       <c r="F110" s="10" t="n"/>
       <c r="G110" s="10" t="n"/>
       <c r="H110" s="10" t="n"/>
-      <c r="I110" s="12" t="n"/>
+      <c r="I110" s="10" t="n"/>
       <c r="J110" s="10" t="n"/>
+      <c r="K110" s="12" t="n"/>
+      <c r="L110" s="10" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="12" t="n"/>
@@ -17132,8 +17376,10 @@
       <c r="F111" s="10" t="n"/>
       <c r="G111" s="10" t="n"/>
       <c r="H111" s="10" t="n"/>
-      <c r="I111" s="12" t="n"/>
+      <c r="I111" s="10" t="n"/>
       <c r="J111" s="10" t="n"/>
+      <c r="K111" s="12" t="n"/>
+      <c r="L111" s="10" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="12" t="n"/>
@@ -17144,8 +17390,10 @@
       <c r="F112" s="10" t="n"/>
       <c r="G112" s="10" t="n"/>
       <c r="H112" s="10" t="n"/>
-      <c r="I112" s="12" t="n"/>
+      <c r="I112" s="10" t="n"/>
       <c r="J112" s="10" t="n"/>
+      <c r="K112" s="12" t="n"/>
+      <c r="L112" s="10" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="12" t="n"/>
@@ -17156,8 +17404,10 @@
       <c r="F113" s="10" t="n"/>
       <c r="G113" s="10" t="n"/>
       <c r="H113" s="10" t="n"/>
-      <c r="I113" s="12" t="n"/>
+      <c r="I113" s="10" t="n"/>
       <c r="J113" s="10" t="n"/>
+      <c r="K113" s="12" t="n"/>
+      <c r="L113" s="10" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="12" t="n"/>
@@ -17168,8 +17418,10 @@
       <c r="F114" s="10" t="n"/>
       <c r="G114" s="10" t="n"/>
       <c r="H114" s="10" t="n"/>
-      <c r="I114" s="12" t="n"/>
+      <c r="I114" s="10" t="n"/>
       <c r="J114" s="10" t="n"/>
+      <c r="K114" s="12" t="n"/>
+      <c r="L114" s="10" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="12" t="n"/>
@@ -17180,8 +17432,10 @@
       <c r="F115" s="10" t="n"/>
       <c r="G115" s="10" t="n"/>
       <c r="H115" s="10" t="n"/>
-      <c r="I115" s="12" t="n"/>
+      <c r="I115" s="10" t="n"/>
       <c r="J115" s="10" t="n"/>
+      <c r="K115" s="12" t="n"/>
+      <c r="L115" s="10" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="12" t="n"/>
@@ -17192,8 +17446,10 @@
       <c r="F116" s="10" t="n"/>
       <c r="G116" s="10" t="n"/>
       <c r="H116" s="10" t="n"/>
-      <c r="I116" s="12" t="n"/>
+      <c r="I116" s="10" t="n"/>
       <c r="J116" s="10" t="n"/>
+      <c r="K116" s="12" t="n"/>
+      <c r="L116" s="10" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="12" t="n"/>
@@ -17204,8 +17460,10 @@
       <c r="F117" s="10" t="n"/>
       <c r="G117" s="10" t="n"/>
       <c r="H117" s="10" t="n"/>
-      <c r="I117" s="12" t="n"/>
+      <c r="I117" s="10" t="n"/>
       <c r="J117" s="10" t="n"/>
+      <c r="K117" s="12" t="n"/>
+      <c r="L117" s="10" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="12" t="n"/>
@@ -17216,8 +17474,10 @@
       <c r="F118" s="10" t="n"/>
       <c r="G118" s="10" t="n"/>
       <c r="H118" s="10" t="n"/>
-      <c r="I118" s="12" t="n"/>
+      <c r="I118" s="10" t="n"/>
       <c r="J118" s="10" t="n"/>
+      <c r="K118" s="12" t="n"/>
+      <c r="L118" s="10" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="12" t="n"/>
@@ -17228,8 +17488,10 @@
       <c r="F119" s="10" t="n"/>
       <c r="G119" s="10" t="n"/>
       <c r="H119" s="10" t="n"/>
-      <c r="I119" s="12" t="n"/>
+      <c r="I119" s="10" t="n"/>
       <c r="J119" s="10" t="n"/>
+      <c r="K119" s="12" t="n"/>
+      <c r="L119" s="10" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="12" t="n"/>
@@ -17240,8 +17502,10 @@
       <c r="F120" s="10" t="n"/>
       <c r="G120" s="10" t="n"/>
       <c r="H120" s="10" t="n"/>
-      <c r="I120" s="12" t="n"/>
+      <c r="I120" s="10" t="n"/>
       <c r="J120" s="10" t="n"/>
+      <c r="K120" s="12" t="n"/>
+      <c r="L120" s="10" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="12" t="n"/>
@@ -17252,8 +17516,10 @@
       <c r="F121" s="10" t="n"/>
       <c r="G121" s="10" t="n"/>
       <c r="H121" s="10" t="n"/>
-      <c r="I121" s="12" t="n"/>
+      <c r="I121" s="10" t="n"/>
       <c r="J121" s="10" t="n"/>
+      <c r="K121" s="12" t="n"/>
+      <c r="L121" s="10" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="12" t="n"/>
@@ -17264,8 +17530,10 @@
       <c r="F122" s="10" t="n"/>
       <c r="G122" s="10" t="n"/>
       <c r="H122" s="10" t="n"/>
-      <c r="I122" s="12" t="n"/>
+      <c r="I122" s="10" t="n"/>
       <c r="J122" s="10" t="n"/>
+      <c r="K122" s="12" t="n"/>
+      <c r="L122" s="10" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="12" t="n"/>
@@ -17276,8 +17544,10 @@
       <c r="F123" s="10" t="n"/>
       <c r="G123" s="10" t="n"/>
       <c r="H123" s="10" t="n"/>
-      <c r="I123" s="12" t="n"/>
+      <c r="I123" s="10" t="n"/>
       <c r="J123" s="10" t="n"/>
+      <c r="K123" s="12" t="n"/>
+      <c r="L123" s="10" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="12" t="n"/>
@@ -17288,8 +17558,10 @@
       <c r="F124" s="10" t="n"/>
       <c r="G124" s="10" t="n"/>
       <c r="H124" s="10" t="n"/>
-      <c r="I124" s="12" t="n"/>
+      <c r="I124" s="10" t="n"/>
       <c r="J124" s="10" t="n"/>
+      <c r="K124" s="12" t="n"/>
+      <c r="L124" s="10" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="12" t="n"/>
@@ -17300,8 +17572,10 @@
       <c r="F125" s="10" t="n"/>
       <c r="G125" s="10" t="n"/>
       <c r="H125" s="10" t="n"/>
-      <c r="I125" s="12" t="n"/>
+      <c r="I125" s="10" t="n"/>
       <c r="J125" s="10" t="n"/>
+      <c r="K125" s="12" t="n"/>
+      <c r="L125" s="10" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="12" t="n"/>
@@ -17312,8 +17586,10 @@
       <c r="F126" s="10" t="n"/>
       <c r="G126" s="10" t="n"/>
       <c r="H126" s="10" t="n"/>
-      <c r="I126" s="12" t="n"/>
+      <c r="I126" s="10" t="n"/>
       <c r="J126" s="10" t="n"/>
+      <c r="K126" s="12" t="n"/>
+      <c r="L126" s="10" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="12" t="n"/>
@@ -17324,8 +17600,10 @@
       <c r="F127" s="10" t="n"/>
       <c r="G127" s="10" t="n"/>
       <c r="H127" s="10" t="n"/>
-      <c r="I127" s="12" t="n"/>
+      <c r="I127" s="10" t="n"/>
       <c r="J127" s="10" t="n"/>
+      <c r="K127" s="12" t="n"/>
+      <c r="L127" s="10" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="12" t="n"/>
@@ -17336,8 +17614,10 @@
       <c r="F128" s="10" t="n"/>
       <c r="G128" s="10" t="n"/>
       <c r="H128" s="10" t="n"/>
-      <c r="I128" s="12" t="n"/>
+      <c r="I128" s="10" t="n"/>
       <c r="J128" s="10" t="n"/>
+      <c r="K128" s="12" t="n"/>
+      <c r="L128" s="10" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="12" t="n"/>
@@ -17348,8 +17628,10 @@
       <c r="F129" s="10" t="n"/>
       <c r="G129" s="10" t="n"/>
       <c r="H129" s="10" t="n"/>
-      <c r="I129" s="12" t="n"/>
+      <c r="I129" s="10" t="n"/>
       <c r="J129" s="10" t="n"/>
+      <c r="K129" s="12" t="n"/>
+      <c r="L129" s="10" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="12" t="n"/>
@@ -17360,8 +17642,10 @@
       <c r="F130" s="10" t="n"/>
       <c r="G130" s="10" t="n"/>
       <c r="H130" s="10" t="n"/>
-      <c r="I130" s="12" t="n"/>
+      <c r="I130" s="10" t="n"/>
       <c r="J130" s="10" t="n"/>
+      <c r="K130" s="12" t="n"/>
+      <c r="L130" s="10" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="12" t="n"/>
@@ -17372,8 +17656,10 @@
       <c r="F131" s="10" t="n"/>
       <c r="G131" s="10" t="n"/>
       <c r="H131" s="10" t="n"/>
-      <c r="I131" s="12" t="n"/>
+      <c r="I131" s="10" t="n"/>
       <c r="J131" s="10" t="n"/>
+      <c r="K131" s="12" t="n"/>
+      <c r="L131" s="10" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="12" t="n"/>
@@ -17384,8 +17670,10 @@
       <c r="F132" s="10" t="n"/>
       <c r="G132" s="10" t="n"/>
       <c r="H132" s="10" t="n"/>
-      <c r="I132" s="12" t="n"/>
+      <c r="I132" s="10" t="n"/>
       <c r="J132" s="10" t="n"/>
+      <c r="K132" s="12" t="n"/>
+      <c r="L132" s="10" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="12" t="n"/>
@@ -17396,8 +17684,10 @@
       <c r="F133" s="10" t="n"/>
       <c r="G133" s="10" t="n"/>
       <c r="H133" s="10" t="n"/>
-      <c r="I133" s="12" t="n"/>
+      <c r="I133" s="10" t="n"/>
       <c r="J133" s="10" t="n"/>
+      <c r="K133" s="12" t="n"/>
+      <c r="L133" s="10" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="12" t="n"/>
@@ -17408,8 +17698,10 @@
       <c r="F134" s="10" t="n"/>
       <c r="G134" s="10" t="n"/>
       <c r="H134" s="10" t="n"/>
-      <c r="I134" s="12" t="n"/>
+      <c r="I134" s="10" t="n"/>
       <c r="J134" s="10" t="n"/>
+      <c r="K134" s="12" t="n"/>
+      <c r="L134" s="10" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="12" t="n"/>
@@ -17420,8 +17712,10 @@
       <c r="F135" s="10" t="n"/>
       <c r="G135" s="10" t="n"/>
       <c r="H135" s="10" t="n"/>
-      <c r="I135" s="12" t="n"/>
+      <c r="I135" s="10" t="n"/>
       <c r="J135" s="10" t="n"/>
+      <c r="K135" s="12" t="n"/>
+      <c r="L135" s="10" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="12" t="n"/>
@@ -17432,8 +17726,10 @@
       <c r="F136" s="10" t="n"/>
       <c r="G136" s="10" t="n"/>
       <c r="H136" s="10" t="n"/>
-      <c r="I136" s="12" t="n"/>
+      <c r="I136" s="10" t="n"/>
       <c r="J136" s="10" t="n"/>
+      <c r="K136" s="12" t="n"/>
+      <c r="L136" s="10" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="12" t="n"/>
@@ -17444,8 +17740,10 @@
       <c r="F137" s="10" t="n"/>
       <c r="G137" s="10" t="n"/>
       <c r="H137" s="10" t="n"/>
-      <c r="I137" s="12" t="n"/>
+      <c r="I137" s="10" t="n"/>
       <c r="J137" s="10" t="n"/>
+      <c r="K137" s="12" t="n"/>
+      <c r="L137" s="10" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="12" t="n"/>
@@ -17456,8 +17754,10 @@
       <c r="F138" s="10" t="n"/>
       <c r="G138" s="10" t="n"/>
       <c r="H138" s="10" t="n"/>
-      <c r="I138" s="12" t="n"/>
+      <c r="I138" s="10" t="n"/>
       <c r="J138" s="10" t="n"/>
+      <c r="K138" s="12" t="n"/>
+      <c r="L138" s="10" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="12" t="n"/>
@@ -17468,8 +17768,10 @@
       <c r="F139" s="10" t="n"/>
       <c r="G139" s="10" t="n"/>
       <c r="H139" s="10" t="n"/>
-      <c r="I139" s="12" t="n"/>
+      <c r="I139" s="10" t="n"/>
       <c r="J139" s="10" t="n"/>
+      <c r="K139" s="12" t="n"/>
+      <c r="L139" s="10" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="12" t="n"/>
@@ -17480,8 +17782,10 @@
       <c r="F140" s="10" t="n"/>
       <c r="G140" s="10" t="n"/>
       <c r="H140" s="10" t="n"/>
-      <c r="I140" s="12" t="n"/>
+      <c r="I140" s="10" t="n"/>
       <c r="J140" s="10" t="n"/>
+      <c r="K140" s="12" t="n"/>
+      <c r="L140" s="10" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="12" t="n"/>
@@ -17492,8 +17796,10 @@
       <c r="F141" s="10" t="n"/>
       <c r="G141" s="10" t="n"/>
       <c r="H141" s="10" t="n"/>
-      <c r="I141" s="12" t="n"/>
+      <c r="I141" s="10" t="n"/>
       <c r="J141" s="10" t="n"/>
+      <c r="K141" s="12" t="n"/>
+      <c r="L141" s="10" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="12" t="n"/>
@@ -17504,8 +17810,10 @@
       <c r="F142" s="10" t="n"/>
       <c r="G142" s="10" t="n"/>
       <c r="H142" s="10" t="n"/>
-      <c r="I142" s="12" t="n"/>
+      <c r="I142" s="10" t="n"/>
       <c r="J142" s="10" t="n"/>
+      <c r="K142" s="12" t="n"/>
+      <c r="L142" s="10" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="12" t="n"/>
@@ -17516,8 +17824,10 @@
       <c r="F143" s="10" t="n"/>
       <c r="G143" s="10" t="n"/>
       <c r="H143" s="10" t="n"/>
-      <c r="I143" s="12" t="n"/>
+      <c r="I143" s="10" t="n"/>
       <c r="J143" s="10" t="n"/>
+      <c r="K143" s="12" t="n"/>
+      <c r="L143" s="10" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="12" t="n"/>
@@ -17528,8 +17838,10 @@
       <c r="F144" s="10" t="n"/>
       <c r="G144" s="10" t="n"/>
       <c r="H144" s="10" t="n"/>
-      <c r="I144" s="12" t="n"/>
+      <c r="I144" s="10" t="n"/>
       <c r="J144" s="10" t="n"/>
+      <c r="K144" s="12" t="n"/>
+      <c r="L144" s="10" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="12" t="n"/>
@@ -17540,8 +17852,10 @@
       <c r="F145" s="10" t="n"/>
       <c r="G145" s="10" t="n"/>
       <c r="H145" s="10" t="n"/>
-      <c r="I145" s="12" t="n"/>
+      <c r="I145" s="10" t="n"/>
       <c r="J145" s="10" t="n"/>
+      <c r="K145" s="12" t="n"/>
+      <c r="L145" s="10" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="12" t="n"/>
@@ -17552,8 +17866,10 @@
       <c r="F146" s="10" t="n"/>
       <c r="G146" s="10" t="n"/>
       <c r="H146" s="10" t="n"/>
-      <c r="I146" s="12" t="n"/>
+      <c r="I146" s="10" t="n"/>
       <c r="J146" s="10" t="n"/>
+      <c r="K146" s="12" t="n"/>
+      <c r="L146" s="10" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="12" t="n"/>
@@ -17564,8 +17880,10 @@
       <c r="F147" s="10" t="n"/>
       <c r="G147" s="10" t="n"/>
       <c r="H147" s="10" t="n"/>
-      <c r="I147" s="12" t="n"/>
+      <c r="I147" s="10" t="n"/>
       <c r="J147" s="10" t="n"/>
+      <c r="K147" s="12" t="n"/>
+      <c r="L147" s="10" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="12" t="n"/>
@@ -17576,8 +17894,10 @@
       <c r="F148" s="10" t="n"/>
       <c r="G148" s="10" t="n"/>
       <c r="H148" s="10" t="n"/>
-      <c r="I148" s="12" t="n"/>
+      <c r="I148" s="10" t="n"/>
       <c r="J148" s="10" t="n"/>
+      <c r="K148" s="12" t="n"/>
+      <c r="L148" s="10" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="12" t="n"/>
@@ -17588,8 +17908,10 @@
       <c r="F149" s="10" t="n"/>
       <c r="G149" s="10" t="n"/>
       <c r="H149" s="10" t="n"/>
-      <c r="I149" s="12" t="n"/>
+      <c r="I149" s="10" t="n"/>
       <c r="J149" s="10" t="n"/>
+      <c r="K149" s="12" t="n"/>
+      <c r="L149" s="10" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="12" t="n"/>
@@ -17600,8 +17922,10 @@
       <c r="F150" s="10" t="n"/>
       <c r="G150" s="10" t="n"/>
       <c r="H150" s="10" t="n"/>
-      <c r="I150" s="12" t="n"/>
+      <c r="I150" s="10" t="n"/>
       <c r="J150" s="10" t="n"/>
+      <c r="K150" s="12" t="n"/>
+      <c r="L150" s="10" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="12" t="n"/>
@@ -17612,8 +17936,10 @@
       <c r="F151" s="10" t="n"/>
       <c r="G151" s="10" t="n"/>
       <c r="H151" s="10" t="n"/>
-      <c r="I151" s="12" t="n"/>
+      <c r="I151" s="10" t="n"/>
       <c r="J151" s="10" t="n"/>
+      <c r="K151" s="12" t="n"/>
+      <c r="L151" s="10" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="12" t="n"/>
@@ -17624,8 +17950,10 @@
       <c r="F152" s="10" t="n"/>
       <c r="G152" s="10" t="n"/>
       <c r="H152" s="10" t="n"/>
-      <c r="I152" s="12" t="n"/>
+      <c r="I152" s="10" t="n"/>
       <c r="J152" s="10" t="n"/>
+      <c r="K152" s="12" t="n"/>
+      <c r="L152" s="10" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="12" t="n"/>
@@ -17636,8 +17964,10 @@
       <c r="F153" s="10" t="n"/>
       <c r="G153" s="10" t="n"/>
       <c r="H153" s="10" t="n"/>
-      <c r="I153" s="12" t="n"/>
+      <c r="I153" s="10" t="n"/>
       <c r="J153" s="10" t="n"/>
+      <c r="K153" s="12" t="n"/>
+      <c r="L153" s="10" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="12" t="n"/>
@@ -17648,8 +17978,10 @@
       <c r="F154" s="10" t="n"/>
       <c r="G154" s="10" t="n"/>
       <c r="H154" s="10" t="n"/>
-      <c r="I154" s="12" t="n"/>
+      <c r="I154" s="10" t="n"/>
       <c r="J154" s="10" t="n"/>
+      <c r="K154" s="12" t="n"/>
+      <c r="L154" s="10" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="12" t="n"/>
@@ -17660,8 +17992,10 @@
       <c r="F155" s="10" t="n"/>
       <c r="G155" s="10" t="n"/>
       <c r="H155" s="10" t="n"/>
-      <c r="I155" s="12" t="n"/>
+      <c r="I155" s="10" t="n"/>
       <c r="J155" s="10" t="n"/>
+      <c r="K155" s="12" t="n"/>
+      <c r="L155" s="10" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="12" t="n"/>
@@ -17672,8 +18006,10 @@
       <c r="F156" s="10" t="n"/>
       <c r="G156" s="10" t="n"/>
       <c r="H156" s="10" t="n"/>
-      <c r="I156" s="12" t="n"/>
+      <c r="I156" s="10" t="n"/>
       <c r="J156" s="10" t="n"/>
+      <c r="K156" s="12" t="n"/>
+      <c r="L156" s="10" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="12" t="n"/>
@@ -17684,8 +18020,10 @@
       <c r="F157" s="10" t="n"/>
       <c r="G157" s="10" t="n"/>
       <c r="H157" s="10" t="n"/>
-      <c r="I157" s="12" t="n"/>
+      <c r="I157" s="10" t="n"/>
       <c r="J157" s="10" t="n"/>
+      <c r="K157" s="12" t="n"/>
+      <c r="L157" s="10" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="12" t="n"/>
@@ -17696,8 +18034,10 @@
       <c r="F158" s="10" t="n"/>
       <c r="G158" s="10" t="n"/>
       <c r="H158" s="10" t="n"/>
-      <c r="I158" s="12" t="n"/>
+      <c r="I158" s="10" t="n"/>
       <c r="J158" s="10" t="n"/>
+      <c r="K158" s="12" t="n"/>
+      <c r="L158" s="10" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="12" t="n"/>
@@ -17708,8 +18048,10 @@
       <c r="F159" s="10" t="n"/>
       <c r="G159" s="10" t="n"/>
       <c r="H159" s="10" t="n"/>
-      <c r="I159" s="12" t="n"/>
+      <c r="I159" s="10" t="n"/>
       <c r="J159" s="10" t="n"/>
+      <c r="K159" s="12" t="n"/>
+      <c r="L159" s="10" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="12" t="n"/>
@@ -17720,8 +18062,10 @@
       <c r="F160" s="10" t="n"/>
       <c r="G160" s="10" t="n"/>
       <c r="H160" s="10" t="n"/>
-      <c r="I160" s="12" t="n"/>
+      <c r="I160" s="10" t="n"/>
       <c r="J160" s="10" t="n"/>
+      <c r="K160" s="12" t="n"/>
+      <c r="L160" s="10" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="12" t="n"/>
@@ -17732,8 +18076,10 @@
       <c r="F161" s="10" t="n"/>
       <c r="G161" s="10" t="n"/>
       <c r="H161" s="10" t="n"/>
-      <c r="I161" s="12" t="n"/>
+      <c r="I161" s="10" t="n"/>
       <c r="J161" s="10" t="n"/>
+      <c r="K161" s="12" t="n"/>
+      <c r="L161" s="10" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="12" t="n"/>
@@ -17744,8 +18090,10 @@
       <c r="F162" s="10" t="n"/>
       <c r="G162" s="10" t="n"/>
       <c r="H162" s="10" t="n"/>
-      <c r="I162" s="12" t="n"/>
+      <c r="I162" s="10" t="n"/>
       <c r="J162" s="10" t="n"/>
+      <c r="K162" s="12" t="n"/>
+      <c r="L162" s="10" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="12" t="n"/>
@@ -17756,8 +18104,10 @@
       <c r="F163" s="10" t="n"/>
       <c r="G163" s="10" t="n"/>
       <c r="H163" s="10" t="n"/>
-      <c r="I163" s="12" t="n"/>
+      <c r="I163" s="10" t="n"/>
       <c r="J163" s="10" t="n"/>
+      <c r="K163" s="12" t="n"/>
+      <c r="L163" s="10" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="12" t="n"/>
@@ -17768,8 +18118,10 @@
       <c r="F164" s="10" t="n"/>
       <c r="G164" s="10" t="n"/>
       <c r="H164" s="10" t="n"/>
-      <c r="I164" s="12" t="n"/>
+      <c r="I164" s="10" t="n"/>
       <c r="J164" s="10" t="n"/>
+      <c r="K164" s="12" t="n"/>
+      <c r="L164" s="10" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="12" t="n"/>
@@ -17780,8 +18132,10 @@
       <c r="F165" s="10" t="n"/>
       <c r="G165" s="10" t="n"/>
       <c r="H165" s="10" t="n"/>
-      <c r="I165" s="12" t="n"/>
+      <c r="I165" s="10" t="n"/>
       <c r="J165" s="10" t="n"/>
+      <c r="K165" s="12" t="n"/>
+      <c r="L165" s="10" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="12" t="n"/>
@@ -17792,8 +18146,10 @@
       <c r="F166" s="10" t="n"/>
       <c r="G166" s="10" t="n"/>
       <c r="H166" s="10" t="n"/>
-      <c r="I166" s="12" t="n"/>
+      <c r="I166" s="10" t="n"/>
       <c r="J166" s="10" t="n"/>
+      <c r="K166" s="12" t="n"/>
+      <c r="L166" s="10" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="12" t="n"/>
@@ -17804,8 +18160,10 @@
       <c r="F167" s="10" t="n"/>
       <c r="G167" s="10" t="n"/>
       <c r="H167" s="10" t="n"/>
-      <c r="I167" s="12" t="n"/>
+      <c r="I167" s="10" t="n"/>
       <c r="J167" s="10" t="n"/>
+      <c r="K167" s="12" t="n"/>
+      <c r="L167" s="10" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="12" t="n"/>
@@ -17816,8 +18174,10 @@
       <c r="F168" s="10" t="n"/>
       <c r="G168" s="10" t="n"/>
       <c r="H168" s="10" t="n"/>
-      <c r="I168" s="12" t="n"/>
+      <c r="I168" s="10" t="n"/>
       <c r="J168" s="10" t="n"/>
+      <c r="K168" s="12" t="n"/>
+      <c r="L168" s="10" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="12" t="n"/>
@@ -17828,8 +18188,10 @@
       <c r="F169" s="10" t="n"/>
       <c r="G169" s="10" t="n"/>
       <c r="H169" s="10" t="n"/>
-      <c r="I169" s="12" t="n"/>
+      <c r="I169" s="10" t="n"/>
       <c r="J169" s="10" t="n"/>
+      <c r="K169" s="12" t="n"/>
+      <c r="L169" s="10" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="12" t="n"/>
@@ -17840,8 +18202,10 @@
       <c r="F170" s="10" t="n"/>
       <c r="G170" s="10" t="n"/>
       <c r="H170" s="10" t="n"/>
-      <c r="I170" s="12" t="n"/>
+      <c r="I170" s="10" t="n"/>
       <c r="J170" s="10" t="n"/>
+      <c r="K170" s="12" t="n"/>
+      <c r="L170" s="10" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="12" t="n"/>
@@ -17852,8 +18216,10 @@
       <c r="F171" s="10" t="n"/>
       <c r="G171" s="10" t="n"/>
       <c r="H171" s="10" t="n"/>
-      <c r="I171" s="12" t="n"/>
+      <c r="I171" s="10" t="n"/>
       <c r="J171" s="10" t="n"/>
+      <c r="K171" s="12" t="n"/>
+      <c r="L171" s="10" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="12" t="n"/>
@@ -17864,8 +18230,10 @@
       <c r="F172" s="10" t="n"/>
       <c r="G172" s="10" t="n"/>
       <c r="H172" s="10" t="n"/>
-      <c r="I172" s="12" t="n"/>
+      <c r="I172" s="10" t="n"/>
       <c r="J172" s="10" t="n"/>
+      <c r="K172" s="12" t="n"/>
+      <c r="L172" s="10" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="12" t="n"/>
@@ -17876,8 +18244,10 @@
       <c r="F173" s="10" t="n"/>
       <c r="G173" s="10" t="n"/>
       <c r="H173" s="10" t="n"/>
-      <c r="I173" s="12" t="n"/>
+      <c r="I173" s="10" t="n"/>
       <c r="J173" s="10" t="n"/>
+      <c r="K173" s="12" t="n"/>
+      <c r="L173" s="10" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="12" t="n"/>
@@ -17888,8 +18258,10 @@
       <c r="F174" s="10" t="n"/>
       <c r="G174" s="10" t="n"/>
       <c r="H174" s="10" t="n"/>
-      <c r="I174" s="12" t="n"/>
+      <c r="I174" s="10" t="n"/>
       <c r="J174" s="10" t="n"/>
+      <c r="K174" s="12" t="n"/>
+      <c r="L174" s="10" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="12" t="n"/>
@@ -17900,8 +18272,10 @@
       <c r="F175" s="10" t="n"/>
       <c r="G175" s="10" t="n"/>
       <c r="H175" s="10" t="n"/>
-      <c r="I175" s="12" t="n"/>
+      <c r="I175" s="10" t="n"/>
       <c r="J175" s="10" t="n"/>
+      <c r="K175" s="12" t="n"/>
+      <c r="L175" s="10" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="12" t="n"/>
@@ -17912,8 +18286,10 @@
       <c r="F176" s="10" t="n"/>
       <c r="G176" s="10" t="n"/>
       <c r="H176" s="10" t="n"/>
-      <c r="I176" s="12" t="n"/>
+      <c r="I176" s="10" t="n"/>
       <c r="J176" s="10" t="n"/>
+      <c r="K176" s="12" t="n"/>
+      <c r="L176" s="10" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="12" t="n"/>
@@ -17924,8 +18300,10 @@
       <c r="F177" s="10" t="n"/>
       <c r="G177" s="10" t="n"/>
       <c r="H177" s="10" t="n"/>
-      <c r="I177" s="12" t="n"/>
+      <c r="I177" s="10" t="n"/>
       <c r="J177" s="10" t="n"/>
+      <c r="K177" s="12" t="n"/>
+      <c r="L177" s="10" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="12" t="n"/>
@@ -17936,8 +18314,10 @@
       <c r="F178" s="10" t="n"/>
       <c r="G178" s="10" t="n"/>
       <c r="H178" s="10" t="n"/>
-      <c r="I178" s="12" t="n"/>
+      <c r="I178" s="10" t="n"/>
       <c r="J178" s="10" t="n"/>
+      <c r="K178" s="12" t="n"/>
+      <c r="L178" s="10" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="12" t="n"/>
@@ -17948,8 +18328,10 @@
       <c r="F179" s="10" t="n"/>
       <c r="G179" s="10" t="n"/>
       <c r="H179" s="10" t="n"/>
-      <c r="I179" s="12" t="n"/>
+      <c r="I179" s="10" t="n"/>
       <c r="J179" s="10" t="n"/>
+      <c r="K179" s="12" t="n"/>
+      <c r="L179" s="10" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="12" t="n"/>
@@ -17960,8 +18342,10 @@
       <c r="F180" s="10" t="n"/>
       <c r="G180" s="10" t="n"/>
       <c r="H180" s="10" t="n"/>
-      <c r="I180" s="12" t="n"/>
+      <c r="I180" s="10" t="n"/>
       <c r="J180" s="10" t="n"/>
+      <c r="K180" s="12" t="n"/>
+      <c r="L180" s="10" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="12" t="n"/>
@@ -17972,8 +18356,10 @@
       <c r="F181" s="10" t="n"/>
       <c r="G181" s="10" t="n"/>
       <c r="H181" s="10" t="n"/>
-      <c r="I181" s="12" t="n"/>
+      <c r="I181" s="10" t="n"/>
       <c r="J181" s="10" t="n"/>
+      <c r="K181" s="12" t="n"/>
+      <c r="L181" s="10" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="12" t="n"/>
@@ -17984,8 +18370,10 @@
       <c r="F182" s="10" t="n"/>
       <c r="G182" s="10" t="n"/>
       <c r="H182" s="10" t="n"/>
-      <c r="I182" s="12" t="n"/>
+      <c r="I182" s="10" t="n"/>
       <c r="J182" s="10" t="n"/>
+      <c r="K182" s="12" t="n"/>
+      <c r="L182" s="10" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="12" t="n"/>
@@ -17996,8 +18384,10 @@
       <c r="F183" s="10" t="n"/>
       <c r="G183" s="10" t="n"/>
       <c r="H183" s="10" t="n"/>
-      <c r="I183" s="12" t="n"/>
+      <c r="I183" s="10" t="n"/>
       <c r="J183" s="10" t="n"/>
+      <c r="K183" s="12" t="n"/>
+      <c r="L183" s="10" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="12" t="n"/>
@@ -18008,8 +18398,10 @@
       <c r="F184" s="10" t="n"/>
       <c r="G184" s="10" t="n"/>
       <c r="H184" s="10" t="n"/>
-      <c r="I184" s="12" t="n"/>
+      <c r="I184" s="10" t="n"/>
       <c r="J184" s="10" t="n"/>
+      <c r="K184" s="12" t="n"/>
+      <c r="L184" s="10" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="12" t="n"/>
@@ -18020,8 +18412,10 @@
       <c r="F185" s="10" t="n"/>
       <c r="G185" s="10" t="n"/>
       <c r="H185" s="10" t="n"/>
-      <c r="I185" s="12" t="n"/>
+      <c r="I185" s="10" t="n"/>
       <c r="J185" s="10" t="n"/>
+      <c r="K185" s="12" t="n"/>
+      <c r="L185" s="10" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="12" t="n"/>
@@ -18032,8 +18426,10 @@
       <c r="F186" s="10" t="n"/>
       <c r="G186" s="10" t="n"/>
       <c r="H186" s="10" t="n"/>
-      <c r="I186" s="12" t="n"/>
+      <c r="I186" s="10" t="n"/>
       <c r="J186" s="10" t="n"/>
+      <c r="K186" s="12" t="n"/>
+      <c r="L186" s="10" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="12" t="n"/>
@@ -18044,8 +18440,10 @@
       <c r="F187" s="10" t="n"/>
       <c r="G187" s="10" t="n"/>
       <c r="H187" s="10" t="n"/>
-      <c r="I187" s="12" t="n"/>
+      <c r="I187" s="10" t="n"/>
       <c r="J187" s="10" t="n"/>
+      <c r="K187" s="12" t="n"/>
+      <c r="L187" s="10" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="12" t="n"/>
@@ -18056,8 +18454,10 @@
       <c r="F188" s="10" t="n"/>
       <c r="G188" s="10" t="n"/>
       <c r="H188" s="10" t="n"/>
-      <c r="I188" s="12" t="n"/>
+      <c r="I188" s="10" t="n"/>
       <c r="J188" s="10" t="n"/>
+      <c r="K188" s="12" t="n"/>
+      <c r="L188" s="10" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="12" t="n"/>
@@ -18068,8 +18468,10 @@
       <c r="F189" s="10" t="n"/>
       <c r="G189" s="10" t="n"/>
       <c r="H189" s="10" t="n"/>
-      <c r="I189" s="12" t="n"/>
+      <c r="I189" s="10" t="n"/>
       <c r="J189" s="10" t="n"/>
+      <c r="K189" s="12" t="n"/>
+      <c r="L189" s="10" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="12" t="n"/>
@@ -18080,8 +18482,10 @@
       <c r="F190" s="10" t="n"/>
       <c r="G190" s="10" t="n"/>
       <c r="H190" s="10" t="n"/>
-      <c r="I190" s="12" t="n"/>
+      <c r="I190" s="10" t="n"/>
       <c r="J190" s="10" t="n"/>
+      <c r="K190" s="12" t="n"/>
+      <c r="L190" s="10" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="12" t="n"/>
@@ -18092,8 +18496,10 @@
       <c r="F191" s="10" t="n"/>
       <c r="G191" s="10" t="n"/>
       <c r="H191" s="10" t="n"/>
-      <c r="I191" s="12" t="n"/>
+      <c r="I191" s="10" t="n"/>
       <c r="J191" s="10" t="n"/>
+      <c r="K191" s="12" t="n"/>
+      <c r="L191" s="10" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="12" t="n"/>
@@ -18104,8 +18510,10 @@
       <c r="F192" s="10" t="n"/>
       <c r="G192" s="10" t="n"/>
       <c r="H192" s="10" t="n"/>
-      <c r="I192" s="12" t="n"/>
+      <c r="I192" s="10" t="n"/>
       <c r="J192" s="10" t="n"/>
+      <c r="K192" s="12" t="n"/>
+      <c r="L192" s="10" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="12" t="n"/>
@@ -18116,8 +18524,10 @@
       <c r="F193" s="10" t="n"/>
       <c r="G193" s="10" t="n"/>
       <c r="H193" s="10" t="n"/>
-      <c r="I193" s="12" t="n"/>
+      <c r="I193" s="10" t="n"/>
       <c r="J193" s="10" t="n"/>
+      <c r="K193" s="12" t="n"/>
+      <c r="L193" s="10" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="12" t="n"/>
@@ -18128,8 +18538,10 @@
       <c r="F194" s="10" t="n"/>
       <c r="G194" s="10" t="n"/>
       <c r="H194" s="10" t="n"/>
-      <c r="I194" s="12" t="n"/>
+      <c r="I194" s="10" t="n"/>
       <c r="J194" s="10" t="n"/>
+      <c r="K194" s="12" t="n"/>
+      <c r="L194" s="10" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="12" t="n"/>
@@ -18140,8 +18552,10 @@
       <c r="F195" s="10" t="n"/>
       <c r="G195" s="10" t="n"/>
       <c r="H195" s="10" t="n"/>
-      <c r="I195" s="12" t="n"/>
+      <c r="I195" s="10" t="n"/>
       <c r="J195" s="10" t="n"/>
+      <c r="K195" s="12" t="n"/>
+      <c r="L195" s="10" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="12" t="n"/>
@@ -18152,8 +18566,10 @@
       <c r="F196" s="10" t="n"/>
       <c r="G196" s="10" t="n"/>
       <c r="H196" s="10" t="n"/>
-      <c r="I196" s="12" t="n"/>
+      <c r="I196" s="10" t="n"/>
       <c r="J196" s="10" t="n"/>
+      <c r="K196" s="12" t="n"/>
+      <c r="L196" s="10" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="12" t="n"/>
@@ -18164,8 +18580,10 @@
       <c r="F197" s="10" t="n"/>
       <c r="G197" s="10" t="n"/>
       <c r="H197" s="10" t="n"/>
-      <c r="I197" s="12" t="n"/>
+      <c r="I197" s="10" t="n"/>
       <c r="J197" s="10" t="n"/>
+      <c r="K197" s="12" t="n"/>
+      <c r="L197" s="10" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="12" t="n"/>
@@ -18176,8 +18594,10 @@
       <c r="F198" s="10" t="n"/>
       <c r="G198" s="10" t="n"/>
       <c r="H198" s="10" t="n"/>
-      <c r="I198" s="12" t="n"/>
+      <c r="I198" s="10" t="n"/>
       <c r="J198" s="10" t="n"/>
+      <c r="K198" s="12" t="n"/>
+      <c r="L198" s="10" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="12" t="n"/>
@@ -18188,8 +18608,10 @@
       <c r="F199" s="10" t="n"/>
       <c r="G199" s="10" t="n"/>
       <c r="H199" s="10" t="n"/>
-      <c r="I199" s="12" t="n"/>
+      <c r="I199" s="10" t="n"/>
       <c r="J199" s="10" t="n"/>
+      <c r="K199" s="12" t="n"/>
+      <c r="L199" s="10" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="12" t="n"/>
@@ -18200,8 +18622,10 @@
       <c r="F200" s="10" t="n"/>
       <c r="G200" s="10" t="n"/>
       <c r="H200" s="10" t="n"/>
-      <c r="I200" s="12" t="n"/>
+      <c r="I200" s="10" t="n"/>
       <c r="J200" s="10" t="n"/>
+      <c r="K200" s="12" t="n"/>
+      <c r="L200" s="10" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="12" t="n"/>
@@ -18212,8 +18636,10 @@
       <c r="F201" s="10" t="n"/>
       <c r="G201" s="10" t="n"/>
       <c r="H201" s="10" t="n"/>
-      <c r="I201" s="12" t="n"/>
+      <c r="I201" s="10" t="n"/>
       <c r="J201" s="10" t="n"/>
+      <c r="K201" s="12" t="n"/>
+      <c r="L201" s="10" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="12" t="n"/>
@@ -18224,8 +18650,10 @@
       <c r="F202" s="10" t="n"/>
       <c r="G202" s="10" t="n"/>
       <c r="H202" s="10" t="n"/>
-      <c r="I202" s="12" t="n"/>
+      <c r="I202" s="10" t="n"/>
       <c r="J202" s="10" t="n"/>
+      <c r="K202" s="12" t="n"/>
+      <c r="L202" s="10" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="12" t="n"/>
@@ -18236,8 +18664,10 @@
       <c r="F203" s="10" t="n"/>
       <c r="G203" s="10" t="n"/>
       <c r="H203" s="10" t="n"/>
-      <c r="I203" s="12" t="n"/>
+      <c r="I203" s="10" t="n"/>
       <c r="J203" s="10" t="n"/>
+      <c r="K203" s="12" t="n"/>
+      <c r="L203" s="10" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="12" t="n"/>
@@ -18248,8 +18678,10 @@
       <c r="F204" s="10" t="n"/>
       <c r="G204" s="10" t="n"/>
       <c r="H204" s="10" t="n"/>
-      <c r="I204" s="12" t="n"/>
+      <c r="I204" s="10" t="n"/>
       <c r="J204" s="10" t="n"/>
+      <c r="K204" s="12" t="n"/>
+      <c r="L204" s="10" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="12" t="n"/>
@@ -18260,8 +18692,10 @@
       <c r="F205" s="10" t="n"/>
       <c r="G205" s="10" t="n"/>
       <c r="H205" s="10" t="n"/>
-      <c r="I205" s="12" t="n"/>
+      <c r="I205" s="10" t="n"/>
       <c r="J205" s="10" t="n"/>
+      <c r="K205" s="12" t="n"/>
+      <c r="L205" s="10" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="12" t="n"/>
@@ -18272,8 +18706,10 @@
       <c r="F206" s="10" t="n"/>
       <c r="G206" s="10" t="n"/>
       <c r="H206" s="10" t="n"/>
-      <c r="I206" s="12" t="n"/>
+      <c r="I206" s="10" t="n"/>
       <c r="J206" s="10" t="n"/>
+      <c r="K206" s="12" t="n"/>
+      <c r="L206" s="10" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="12" t="n"/>
@@ -18284,8 +18720,10 @@
       <c r="F207" s="10" t="n"/>
       <c r="G207" s="10" t="n"/>
       <c r="H207" s="10" t="n"/>
-      <c r="I207" s="12" t="n"/>
+      <c r="I207" s="10" t="n"/>
       <c r="J207" s="10" t="n"/>
+      <c r="K207" s="12" t="n"/>
+      <c r="L207" s="10" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="12" t="n"/>
@@ -18296,8 +18734,10 @@
       <c r="F208" s="10" t="n"/>
       <c r="G208" s="10" t="n"/>
       <c r="H208" s="10" t="n"/>
-      <c r="I208" s="12" t="n"/>
+      <c r="I208" s="10" t="n"/>
       <c r="J208" s="10" t="n"/>
+      <c r="K208" s="12" t="n"/>
+      <c r="L208" s="10" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="12" t="n"/>
@@ -18308,8 +18748,10 @@
       <c r="F209" s="10" t="n"/>
       <c r="G209" s="10" t="n"/>
       <c r="H209" s="10" t="n"/>
-      <c r="I209" s="12" t="n"/>
+      <c r="I209" s="10" t="n"/>
       <c r="J209" s="10" t="n"/>
+      <c r="K209" s="12" t="n"/>
+      <c r="L209" s="10" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="12" t="n"/>
@@ -18320,8 +18762,10 @@
       <c r="F210" s="10" t="n"/>
       <c r="G210" s="10" t="n"/>
       <c r="H210" s="10" t="n"/>
-      <c r="I210" s="12" t="n"/>
+      <c r="I210" s="10" t="n"/>
       <c r="J210" s="10" t="n"/>
+      <c r="K210" s="12" t="n"/>
+      <c r="L210" s="10" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="12" t="n"/>
@@ -18332,8 +18776,10 @@
       <c r="F211" s="10" t="n"/>
       <c r="G211" s="10" t="n"/>
       <c r="H211" s="10" t="n"/>
-      <c r="I211" s="12" t="n"/>
+      <c r="I211" s="10" t="n"/>
       <c r="J211" s="10" t="n"/>
+      <c r="K211" s="12" t="n"/>
+      <c r="L211" s="10" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="12" t="n"/>
@@ -18344,8 +18790,10 @@
       <c r="F212" s="10" t="n"/>
       <c r="G212" s="10" t="n"/>
       <c r="H212" s="10" t="n"/>
-      <c r="I212" s="12" t="n"/>
+      <c r="I212" s="10" t="n"/>
       <c r="J212" s="10" t="n"/>
+      <c r="K212" s="12" t="n"/>
+      <c r="L212" s="10" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="12" t="n"/>
@@ -18356,8 +18804,10 @@
       <c r="F213" s="10" t="n"/>
       <c r="G213" s="10" t="n"/>
       <c r="H213" s="10" t="n"/>
-      <c r="I213" s="12" t="n"/>
+      <c r="I213" s="10" t="n"/>
       <c r="J213" s="10" t="n"/>
+      <c r="K213" s="12" t="n"/>
+      <c r="L213" s="10" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="12" t="n"/>
@@ -18368,8 +18818,10 @@
       <c r="F214" s="10" t="n"/>
       <c r="G214" s="10" t="n"/>
       <c r="H214" s="10" t="n"/>
-      <c r="I214" s="12" t="n"/>
+      <c r="I214" s="10" t="n"/>
       <c r="J214" s="10" t="n"/>
+      <c r="K214" s="12" t="n"/>
+      <c r="L214" s="10" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="12" t="n"/>
@@ -18380,8 +18832,10 @@
       <c r="F215" s="10" t="n"/>
       <c r="G215" s="10" t="n"/>
       <c r="H215" s="10" t="n"/>
-      <c r="I215" s="12" t="n"/>
+      <c r="I215" s="10" t="n"/>
       <c r="J215" s="10" t="n"/>
+      <c r="K215" s="12" t="n"/>
+      <c r="L215" s="10" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="12" t="n"/>
@@ -18392,8 +18846,10 @@
       <c r="F216" s="10" t="n"/>
       <c r="G216" s="10" t="n"/>
       <c r="H216" s="10" t="n"/>
-      <c r="I216" s="12" t="n"/>
+      <c r="I216" s="10" t="n"/>
       <c r="J216" s="10" t="n"/>
+      <c r="K216" s="12" t="n"/>
+      <c r="L216" s="10" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="12" t="n"/>
@@ -18404,8 +18860,10 @@
       <c r="F217" s="10" t="n"/>
       <c r="G217" s="10" t="n"/>
       <c r="H217" s="10" t="n"/>
-      <c r="I217" s="12" t="n"/>
+      <c r="I217" s="10" t="n"/>
       <c r="J217" s="10" t="n"/>
+      <c r="K217" s="12" t="n"/>
+      <c r="L217" s="10" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="12" t="n"/>
@@ -18416,8 +18874,10 @@
       <c r="F218" s="10" t="n"/>
       <c r="G218" s="10" t="n"/>
       <c r="H218" s="10" t="n"/>
-      <c r="I218" s="12" t="n"/>
+      <c r="I218" s="10" t="n"/>
       <c r="J218" s="10" t="n"/>
+      <c r="K218" s="12" t="n"/>
+      <c r="L218" s="10" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="12" t="n"/>
@@ -18428,8 +18888,10 @@
       <c r="F219" s="10" t="n"/>
       <c r="G219" s="10" t="n"/>
       <c r="H219" s="10" t="n"/>
-      <c r="I219" s="12" t="n"/>
+      <c r="I219" s="10" t="n"/>
       <c r="J219" s="10" t="n"/>
+      <c r="K219" s="12" t="n"/>
+      <c r="L219" s="10" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="12" t="n"/>
@@ -18440,8 +18902,10 @@
       <c r="F220" s="10" t="n"/>
       <c r="G220" s="10" t="n"/>
       <c r="H220" s="10" t="n"/>
-      <c r="I220" s="12" t="n"/>
+      <c r="I220" s="10" t="n"/>
       <c r="J220" s="10" t="n"/>
+      <c r="K220" s="12" t="n"/>
+      <c r="L220" s="10" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="12" t="n"/>
@@ -18452,8 +18916,10 @@
       <c r="F221" s="10" t="n"/>
       <c r="G221" s="10" t="n"/>
       <c r="H221" s="10" t="n"/>
-      <c r="I221" s="12" t="n"/>
+      <c r="I221" s="10" t="n"/>
       <c r="J221" s="10" t="n"/>
+      <c r="K221" s="12" t="n"/>
+      <c r="L221" s="10" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="12" t="n"/>
@@ -18464,8 +18930,10 @@
       <c r="F222" s="10" t="n"/>
       <c r="G222" s="10" t="n"/>
       <c r="H222" s="10" t="n"/>
-      <c r="I222" s="12" t="n"/>
+      <c r="I222" s="10" t="n"/>
       <c r="J222" s="10" t="n"/>
+      <c r="K222" s="12" t="n"/>
+      <c r="L222" s="10" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="12" t="n"/>
@@ -18476,8 +18944,10 @@
       <c r="F223" s="10" t="n"/>
       <c r="G223" s="10" t="n"/>
       <c r="H223" s="10" t="n"/>
-      <c r="I223" s="12" t="n"/>
+      <c r="I223" s="10" t="n"/>
       <c r="J223" s="10" t="n"/>
+      <c r="K223" s="12" t="n"/>
+      <c r="L223" s="10" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="12" t="n"/>
@@ -18488,8 +18958,10 @@
       <c r="F224" s="10" t="n"/>
       <c r="G224" s="10" t="n"/>
       <c r="H224" s="10" t="n"/>
-      <c r="I224" s="12" t="n"/>
+      <c r="I224" s="10" t="n"/>
       <c r="J224" s="10" t="n"/>
+      <c r="K224" s="12" t="n"/>
+      <c r="L224" s="10" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="12" t="n"/>
@@ -18500,8 +18972,10 @@
       <c r="F225" s="10" t="n"/>
       <c r="G225" s="10" t="n"/>
       <c r="H225" s="10" t="n"/>
-      <c r="I225" s="12" t="n"/>
+      <c r="I225" s="10" t="n"/>
       <c r="J225" s="10" t="n"/>
+      <c r="K225" s="12" t="n"/>
+      <c r="L225" s="10" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="12" t="n"/>
@@ -18512,8 +18986,10 @@
       <c r="F226" s="10" t="n"/>
       <c r="G226" s="10" t="n"/>
       <c r="H226" s="10" t="n"/>
-      <c r="I226" s="12" t="n"/>
+      <c r="I226" s="10" t="n"/>
       <c r="J226" s="10" t="n"/>
+      <c r="K226" s="12" t="n"/>
+      <c r="L226" s="10" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="12" t="n"/>
@@ -18524,8 +19000,10 @@
       <c r="F227" s="10" t="n"/>
       <c r="G227" s="10" t="n"/>
       <c r="H227" s="10" t="n"/>
-      <c r="I227" s="12" t="n"/>
+      <c r="I227" s="10" t="n"/>
       <c r="J227" s="10" t="n"/>
+      <c r="K227" s="12" t="n"/>
+      <c r="L227" s="10" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="12" t="n"/>
@@ -18536,8 +19014,10 @@
       <c r="F228" s="10" t="n"/>
       <c r="G228" s="10" t="n"/>
       <c r="H228" s="10" t="n"/>
-      <c r="I228" s="12" t="n"/>
+      <c r="I228" s="10" t="n"/>
       <c r="J228" s="10" t="n"/>
+      <c r="K228" s="12" t="n"/>
+      <c r="L228" s="10" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="12" t="n"/>
@@ -18548,8 +19028,10 @@
       <c r="F229" s="10" t="n"/>
       <c r="G229" s="10" t="n"/>
       <c r="H229" s="10" t="n"/>
-      <c r="I229" s="12" t="n"/>
+      <c r="I229" s="10" t="n"/>
       <c r="J229" s="10" t="n"/>
+      <c r="K229" s="12" t="n"/>
+      <c r="L229" s="10" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="12" t="n"/>
@@ -18560,8 +19042,10 @@
       <c r="F230" s="10" t="n"/>
       <c r="G230" s="10" t="n"/>
       <c r="H230" s="10" t="n"/>
-      <c r="I230" s="12" t="n"/>
+      <c r="I230" s="10" t="n"/>
       <c r="J230" s="10" t="n"/>
+      <c r="K230" s="12" t="n"/>
+      <c r="L230" s="10" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="12" t="n"/>
@@ -18572,8 +19056,10 @@
       <c r="F231" s="10" t="n"/>
       <c r="G231" s="10" t="n"/>
       <c r="H231" s="10" t="n"/>
-      <c r="I231" s="12" t="n"/>
+      <c r="I231" s="10" t="n"/>
       <c r="J231" s="10" t="n"/>
+      <c r="K231" s="12" t="n"/>
+      <c r="L231" s="10" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="12" t="n"/>
@@ -18584,8 +19070,10 @@
       <c r="F232" s="10" t="n"/>
       <c r="G232" s="10" t="n"/>
       <c r="H232" s="10" t="n"/>
-      <c r="I232" s="12" t="n"/>
+      <c r="I232" s="10" t="n"/>
       <c r="J232" s="10" t="n"/>
+      <c r="K232" s="12" t="n"/>
+      <c r="L232" s="10" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="12" t="n"/>
@@ -18596,8 +19084,10 @@
       <c r="F233" s="10" t="n"/>
       <c r="G233" s="10" t="n"/>
       <c r="H233" s="10" t="n"/>
-      <c r="I233" s="12" t="n"/>
+      <c r="I233" s="10" t="n"/>
       <c r="J233" s="10" t="n"/>
+      <c r="K233" s="12" t="n"/>
+      <c r="L233" s="10" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="12" t="n"/>
@@ -18608,8 +19098,10 @@
       <c r="F234" s="10" t="n"/>
       <c r="G234" s="10" t="n"/>
       <c r="H234" s="10" t="n"/>
-      <c r="I234" s="12" t="n"/>
+      <c r="I234" s="10" t="n"/>
       <c r="J234" s="10" t="n"/>
+      <c r="K234" s="12" t="n"/>
+      <c r="L234" s="10" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="12" t="n"/>
@@ -18620,8 +19112,10 @@
       <c r="F235" s="10" t="n"/>
       <c r="G235" s="10" t="n"/>
       <c r="H235" s="10" t="n"/>
-      <c r="I235" s="12" t="n"/>
+      <c r="I235" s="10" t="n"/>
       <c r="J235" s="10" t="n"/>
+      <c r="K235" s="12" t="n"/>
+      <c r="L235" s="10" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="12" t="n"/>
@@ -18632,8 +19126,10 @@
       <c r="F236" s="10" t="n"/>
       <c r="G236" s="10" t="n"/>
       <c r="H236" s="10" t="n"/>
-      <c r="I236" s="12" t="n"/>
+      <c r="I236" s="10" t="n"/>
       <c r="J236" s="10" t="n"/>
+      <c r="K236" s="12" t="n"/>
+      <c r="L236" s="10" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="12" t="n"/>
@@ -18644,8 +19140,10 @@
       <c r="F237" s="10" t="n"/>
       <c r="G237" s="10" t="n"/>
       <c r="H237" s="10" t="n"/>
-      <c r="I237" s="12" t="n"/>
+      <c r="I237" s="10" t="n"/>
       <c r="J237" s="10" t="n"/>
+      <c r="K237" s="12" t="n"/>
+      <c r="L237" s="10" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="12" t="n"/>
@@ -18656,8 +19154,10 @@
       <c r="F238" s="10" t="n"/>
       <c r="G238" s="10" t="n"/>
       <c r="H238" s="10" t="n"/>
-      <c r="I238" s="12" t="n"/>
+      <c r="I238" s="10" t="n"/>
       <c r="J238" s="10" t="n"/>
+      <c r="K238" s="12" t="n"/>
+      <c r="L238" s="10" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="12" t="n"/>
@@ -18668,8 +19168,10 @@
       <c r="F239" s="10" t="n"/>
       <c r="G239" s="10" t="n"/>
       <c r="H239" s="10" t="n"/>
-      <c r="I239" s="12" t="n"/>
+      <c r="I239" s="10" t="n"/>
       <c r="J239" s="10" t="n"/>
+      <c r="K239" s="12" t="n"/>
+      <c r="L239" s="10" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="12" t="n"/>
@@ -18680,8 +19182,10 @@
       <c r="F240" s="10" t="n"/>
       <c r="G240" s="10" t="n"/>
       <c r="H240" s="10" t="n"/>
-      <c r="I240" s="12" t="n"/>
+      <c r="I240" s="10" t="n"/>
       <c r="J240" s="10" t="n"/>
+      <c r="K240" s="12" t="n"/>
+      <c r="L240" s="10" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="12" t="n"/>
@@ -18692,8 +19196,10 @@
       <c r="F241" s="10" t="n"/>
       <c r="G241" s="10" t="n"/>
       <c r="H241" s="10" t="n"/>
-      <c r="I241" s="12" t="n"/>
+      <c r="I241" s="10" t="n"/>
       <c r="J241" s="10" t="n"/>
+      <c r="K241" s="12" t="n"/>
+      <c r="L241" s="10" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="12" t="n"/>
@@ -18704,8 +19210,10 @@
       <c r="F242" s="10" t="n"/>
       <c r="G242" s="10" t="n"/>
       <c r="H242" s="10" t="n"/>
-      <c r="I242" s="12" t="n"/>
+      <c r="I242" s="10" t="n"/>
       <c r="J242" s="10" t="n"/>
+      <c r="K242" s="12" t="n"/>
+      <c r="L242" s="10" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="12" t="n"/>
@@ -18716,8 +19224,10 @@
       <c r="F243" s="10" t="n"/>
       <c r="G243" s="10" t="n"/>
       <c r="H243" s="10" t="n"/>
-      <c r="I243" s="12" t="n"/>
+      <c r="I243" s="10" t="n"/>
       <c r="J243" s="10" t="n"/>
+      <c r="K243" s="12" t="n"/>
+      <c r="L243" s="10" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="12" t="n"/>
@@ -18728,8 +19238,10 @@
       <c r="F244" s="10" t="n"/>
       <c r="G244" s="10" t="n"/>
       <c r="H244" s="10" t="n"/>
-      <c r="I244" s="12" t="n"/>
+      <c r="I244" s="10" t="n"/>
       <c r="J244" s="10" t="n"/>
+      <c r="K244" s="12" t="n"/>
+      <c r="L244" s="10" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="12" t="n"/>
@@ -18740,8 +19252,10 @@
       <c r="F245" s="10" t="n"/>
       <c r="G245" s="10" t="n"/>
       <c r="H245" s="10" t="n"/>
-      <c r="I245" s="12" t="n"/>
+      <c r="I245" s="10" t="n"/>
       <c r="J245" s="10" t="n"/>
+      <c r="K245" s="12" t="n"/>
+      <c r="L245" s="10" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="12" t="n"/>
@@ -18752,8 +19266,10 @@
       <c r="F246" s="10" t="n"/>
       <c r="G246" s="10" t="n"/>
       <c r="H246" s="10" t="n"/>
-      <c r="I246" s="12" t="n"/>
+      <c r="I246" s="10" t="n"/>
       <c r="J246" s="10" t="n"/>
+      <c r="K246" s="12" t="n"/>
+      <c r="L246" s="10" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="12" t="n"/>
@@ -18764,8 +19280,10 @@
       <c r="F247" s="10" t="n"/>
       <c r="G247" s="10" t="n"/>
       <c r="H247" s="10" t="n"/>
-      <c r="I247" s="12" t="n"/>
+      <c r="I247" s="10" t="n"/>
       <c r="J247" s="10" t="n"/>
+      <c r="K247" s="12" t="n"/>
+      <c r="L247" s="10" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="12" t="n"/>
@@ -18776,8 +19294,10 @@
       <c r="F248" s="10" t="n"/>
       <c r="G248" s="10" t="n"/>
       <c r="H248" s="10" t="n"/>
-      <c r="I248" s="12" t="n"/>
+      <c r="I248" s="10" t="n"/>
       <c r="J248" s="10" t="n"/>
+      <c r="K248" s="12" t="n"/>
+      <c r="L248" s="10" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="12" t="n"/>
@@ -18788,8 +19308,10 @@
       <c r="F249" s="10" t="n"/>
       <c r="G249" s="10" t="n"/>
       <c r="H249" s="10" t="n"/>
-      <c r="I249" s="12" t="n"/>
+      <c r="I249" s="10" t="n"/>
       <c r="J249" s="10" t="n"/>
+      <c r="K249" s="12" t="n"/>
+      <c r="L249" s="10" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="12" t="n"/>
@@ -18800,8 +19322,10 @@
       <c r="F250" s="10" t="n"/>
       <c r="G250" s="10" t="n"/>
       <c r="H250" s="10" t="n"/>
-      <c r="I250" s="12" t="n"/>
+      <c r="I250" s="10" t="n"/>
       <c r="J250" s="10" t="n"/>
+      <c r="K250" s="12" t="n"/>
+      <c r="L250" s="10" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="12" t="n"/>
@@ -18812,8 +19336,10 @@
       <c r="F251" s="10" t="n"/>
       <c r="G251" s="10" t="n"/>
       <c r="H251" s="10" t="n"/>
-      <c r="I251" s="12" t="n"/>
+      <c r="I251" s="10" t="n"/>
       <c r="J251" s="10" t="n"/>
+      <c r="K251" s="12" t="n"/>
+      <c r="L251" s="10" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="12" t="n"/>
@@ -18824,8 +19350,10 @@
       <c r="F252" s="10" t="n"/>
       <c r="G252" s="10" t="n"/>
       <c r="H252" s="10" t="n"/>
-      <c r="I252" s="12" t="n"/>
+      <c r="I252" s="10" t="n"/>
       <c r="J252" s="10" t="n"/>
+      <c r="K252" s="12" t="n"/>
+      <c r="L252" s="10" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="12" t="n"/>
@@ -18836,8 +19364,10 @@
       <c r="F253" s="10" t="n"/>
       <c r="G253" s="10" t="n"/>
       <c r="H253" s="10" t="n"/>
-      <c r="I253" s="12" t="n"/>
+      <c r="I253" s="10" t="n"/>
       <c r="J253" s="10" t="n"/>
+      <c r="K253" s="12" t="n"/>
+      <c r="L253" s="10" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="12" t="n"/>
@@ -18848,8 +19378,10 @@
       <c r="F254" s="10" t="n"/>
       <c r="G254" s="10" t="n"/>
       <c r="H254" s="10" t="n"/>
-      <c r="I254" s="12" t="n"/>
+      <c r="I254" s="10" t="n"/>
       <c r="J254" s="10" t="n"/>
+      <c r="K254" s="12" t="n"/>
+      <c r="L254" s="10" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="12" t="n"/>
@@ -18860,8 +19392,10 @@
       <c r="F255" s="10" t="n"/>
       <c r="G255" s="10" t="n"/>
       <c r="H255" s="10" t="n"/>
-      <c r="I255" s="12" t="n"/>
+      <c r="I255" s="10" t="n"/>
       <c r="J255" s="10" t="n"/>
+      <c r="K255" s="12" t="n"/>
+      <c r="L255" s="10" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="12" t="n"/>
@@ -18872,8 +19406,10 @@
       <c r="F256" s="10" t="n"/>
       <c r="G256" s="10" t="n"/>
       <c r="H256" s="10" t="n"/>
-      <c r="I256" s="12" t="n"/>
+      <c r="I256" s="10" t="n"/>
       <c r="J256" s="10" t="n"/>
+      <c r="K256" s="12" t="n"/>
+      <c r="L256" s="10" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="12" t="n"/>
@@ -18884,8 +19420,10 @@
       <c r="F257" s="10" t="n"/>
       <c r="G257" s="10" t="n"/>
       <c r="H257" s="10" t="n"/>
-      <c r="I257" s="12" t="n"/>
+      <c r="I257" s="10" t="n"/>
       <c r="J257" s="10" t="n"/>
+      <c r="K257" s="12" t="n"/>
+      <c r="L257" s="10" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="12" t="n"/>
@@ -18896,8 +19434,10 @@
       <c r="F258" s="10" t="n"/>
       <c r="G258" s="10" t="n"/>
       <c r="H258" s="10" t="n"/>
-      <c r="I258" s="12" t="n"/>
+      <c r="I258" s="10" t="n"/>
       <c r="J258" s="10" t="n"/>
+      <c r="K258" s="12" t="n"/>
+      <c r="L258" s="10" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="12" t="n"/>
@@ -18908,8 +19448,10 @@
       <c r="F259" s="10" t="n"/>
       <c r="G259" s="10" t="n"/>
       <c r="H259" s="10" t="n"/>
-      <c r="I259" s="12" t="n"/>
+      <c r="I259" s="10" t="n"/>
       <c r="J259" s="10" t="n"/>
+      <c r="K259" s="12" t="n"/>
+      <c r="L259" s="10" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="12" t="n"/>
@@ -18920,8 +19462,10 @@
       <c r="F260" s="10" t="n"/>
       <c r="G260" s="10" t="n"/>
       <c r="H260" s="10" t="n"/>
-      <c r="I260" s="12" t="n"/>
+      <c r="I260" s="10" t="n"/>
       <c r="J260" s="10" t="n"/>
+      <c r="K260" s="12" t="n"/>
+      <c r="L260" s="10" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="12" t="n"/>
@@ -18932,8 +19476,10 @@
       <c r="F261" s="10" t="n"/>
       <c r="G261" s="10" t="n"/>
       <c r="H261" s="10" t="n"/>
-      <c r="I261" s="12" t="n"/>
+      <c r="I261" s="10" t="n"/>
       <c r="J261" s="10" t="n"/>
+      <c r="K261" s="12" t="n"/>
+      <c r="L261" s="10" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="12" t="n"/>
@@ -18944,8 +19490,10 @@
       <c r="F262" s="10" t="n"/>
       <c r="G262" s="10" t="n"/>
       <c r="H262" s="10" t="n"/>
-      <c r="I262" s="12" t="n"/>
+      <c r="I262" s="10" t="n"/>
       <c r="J262" s="10" t="n"/>
+      <c r="K262" s="12" t="n"/>
+      <c r="L262" s="10" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="12" t="n"/>
@@ -18956,8 +19504,10 @@
       <c r="F263" s="10" t="n"/>
       <c r="G263" s="10" t="n"/>
       <c r="H263" s="10" t="n"/>
-      <c r="I263" s="12" t="n"/>
+      <c r="I263" s="10" t="n"/>
       <c r="J263" s="10" t="n"/>
+      <c r="K263" s="12" t="n"/>
+      <c r="L263" s="10" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="12" t="n"/>
@@ -18968,8 +19518,10 @@
       <c r="F264" s="10" t="n"/>
       <c r="G264" s="10" t="n"/>
       <c r="H264" s="10" t="n"/>
-      <c r="I264" s="12" t="n"/>
+      <c r="I264" s="10" t="n"/>
       <c r="J264" s="10" t="n"/>
+      <c r="K264" s="12" t="n"/>
+      <c r="L264" s="10" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="12" t="n"/>
@@ -18980,8 +19532,10 @@
       <c r="F265" s="10" t="n"/>
       <c r="G265" s="10" t="n"/>
       <c r="H265" s="10" t="n"/>
-      <c r="I265" s="12" t="n"/>
+      <c r="I265" s="10" t="n"/>
       <c r="J265" s="10" t="n"/>
+      <c r="K265" s="12" t="n"/>
+      <c r="L265" s="10" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="12" t="n"/>
@@ -18992,8 +19546,10 @@
       <c r="F266" s="10" t="n"/>
       <c r="G266" s="10" t="n"/>
       <c r="H266" s="10" t="n"/>
-      <c r="I266" s="12" t="n"/>
+      <c r="I266" s="10" t="n"/>
       <c r="J266" s="10" t="n"/>
+      <c r="K266" s="12" t="n"/>
+      <c r="L266" s="10" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="12" t="n"/>
@@ -19004,8 +19560,10 @@
       <c r="F267" s="10" t="n"/>
       <c r="G267" s="10" t="n"/>
       <c r="H267" s="10" t="n"/>
-      <c r="I267" s="12" t="n"/>
+      <c r="I267" s="10" t="n"/>
       <c r="J267" s="10" t="n"/>
+      <c r="K267" s="12" t="n"/>
+      <c r="L267" s="10" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="12" t="n"/>
@@ -19016,8 +19574,10 @@
       <c r="F268" s="10" t="n"/>
       <c r="G268" s="10" t="n"/>
       <c r="H268" s="10" t="n"/>
-      <c r="I268" s="12" t="n"/>
+      <c r="I268" s="10" t="n"/>
       <c r="J268" s="10" t="n"/>
+      <c r="K268" s="12" t="n"/>
+      <c r="L268" s="10" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="12" t="n"/>
@@ -19028,8 +19588,10 @@
       <c r="F269" s="10" t="n"/>
       <c r="G269" s="10" t="n"/>
       <c r="H269" s="10" t="n"/>
-      <c r="I269" s="12" t="n"/>
+      <c r="I269" s="10" t="n"/>
       <c r="J269" s="10" t="n"/>
+      <c r="K269" s="12" t="n"/>
+      <c r="L269" s="10" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="12" t="n"/>
@@ -19040,8 +19602,10 @@
       <c r="F270" s="10" t="n"/>
       <c r="G270" s="10" t="n"/>
       <c r="H270" s="10" t="n"/>
-      <c r="I270" s="12" t="n"/>
+      <c r="I270" s="10" t="n"/>
       <c r="J270" s="10" t="n"/>
+      <c r="K270" s="12" t="n"/>
+      <c r="L270" s="10" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="12" t="n"/>
@@ -19052,8 +19616,10 @@
       <c r="F271" s="10" t="n"/>
       <c r="G271" s="10" t="n"/>
       <c r="H271" s="10" t="n"/>
-      <c r="I271" s="12" t="n"/>
+      <c r="I271" s="10" t="n"/>
       <c r="J271" s="10" t="n"/>
+      <c r="K271" s="12" t="n"/>
+      <c r="L271" s="10" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="12" t="n"/>
@@ -19064,8 +19630,10 @@
       <c r="F272" s="10" t="n"/>
       <c r="G272" s="10" t="n"/>
       <c r="H272" s="10" t="n"/>
-      <c r="I272" s="12" t="n"/>
+      <c r="I272" s="10" t="n"/>
       <c r="J272" s="10" t="n"/>
+      <c r="K272" s="12" t="n"/>
+      <c r="L272" s="10" t="n"/>
     </row>
     <row r="273">
       <c r="A273" s="12" t="n"/>
@@ -19076,8 +19644,10 @@
       <c r="F273" s="10" t="n"/>
       <c r="G273" s="10" t="n"/>
       <c r="H273" s="10" t="n"/>
-      <c r="I273" s="12" t="n"/>
+      <c r="I273" s="10" t="n"/>
       <c r="J273" s="10" t="n"/>
+      <c r="K273" s="12" t="n"/>
+      <c r="L273" s="10" t="n"/>
     </row>
     <row r="274">
       <c r="A274" s="12" t="n"/>
@@ -19088,8 +19658,10 @@
       <c r="F274" s="10" t="n"/>
       <c r="G274" s="10" t="n"/>
       <c r="H274" s="10" t="n"/>
-      <c r="I274" s="12" t="n"/>
+      <c r="I274" s="10" t="n"/>
       <c r="J274" s="10" t="n"/>
+      <c r="K274" s="12" t="n"/>
+      <c r="L274" s="10" t="n"/>
     </row>
     <row r="275">
       <c r="A275" s="12" t="n"/>
@@ -19100,8 +19672,10 @@
       <c r="F275" s="10" t="n"/>
       <c r="G275" s="10" t="n"/>
       <c r="H275" s="10" t="n"/>
-      <c r="I275" s="12" t="n"/>
+      <c r="I275" s="10" t="n"/>
       <c r="J275" s="10" t="n"/>
+      <c r="K275" s="12" t="n"/>
+      <c r="L275" s="10" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="12" t="n"/>
@@ -19112,8 +19686,10 @@
       <c r="F276" s="10" t="n"/>
       <c r="G276" s="10" t="n"/>
       <c r="H276" s="10" t="n"/>
-      <c r="I276" s="12" t="n"/>
+      <c r="I276" s="10" t="n"/>
       <c r="J276" s="10" t="n"/>
+      <c r="K276" s="12" t="n"/>
+      <c r="L276" s="10" t="n"/>
     </row>
     <row r="277">
       <c r="A277" s="12" t="n"/>
@@ -19124,8 +19700,10 @@
       <c r="F277" s="10" t="n"/>
       <c r="G277" s="10" t="n"/>
       <c r="H277" s="10" t="n"/>
-      <c r="I277" s="12" t="n"/>
+      <c r="I277" s="10" t="n"/>
       <c r="J277" s="10" t="n"/>
+      <c r="K277" s="12" t="n"/>
+      <c r="L277" s="10" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="12" t="n"/>
@@ -19136,8 +19714,10 @@
       <c r="F278" s="10" t="n"/>
       <c r="G278" s="10" t="n"/>
       <c r="H278" s="10" t="n"/>
-      <c r="I278" s="12" t="n"/>
+      <c r="I278" s="10" t="n"/>
       <c r="J278" s="10" t="n"/>
+      <c r="K278" s="12" t="n"/>
+      <c r="L278" s="10" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="12" t="n"/>
@@ -19148,8 +19728,10 @@
       <c r="F279" s="10" t="n"/>
       <c r="G279" s="10" t="n"/>
       <c r="H279" s="10" t="n"/>
-      <c r="I279" s="12" t="n"/>
+      <c r="I279" s="10" t="n"/>
       <c r="J279" s="10" t="n"/>
+      <c r="K279" s="12" t="n"/>
+      <c r="L279" s="10" t="n"/>
     </row>
     <row r="280">
       <c r="A280" s="12" t="n"/>
@@ -19160,8 +19742,10 @@
       <c r="F280" s="10" t="n"/>
       <c r="G280" s="10" t="n"/>
       <c r="H280" s="10" t="n"/>
-      <c r="I280" s="12" t="n"/>
+      <c r="I280" s="10" t="n"/>
       <c r="J280" s="10" t="n"/>
+      <c r="K280" s="12" t="n"/>
+      <c r="L280" s="10" t="n"/>
     </row>
     <row r="281">
       <c r="A281" s="12" t="n"/>
@@ -19172,8 +19756,10 @@
       <c r="F281" s="10" t="n"/>
       <c r="G281" s="10" t="n"/>
       <c r="H281" s="10" t="n"/>
-      <c r="I281" s="12" t="n"/>
+      <c r="I281" s="10" t="n"/>
       <c r="J281" s="10" t="n"/>
+      <c r="K281" s="12" t="n"/>
+      <c r="L281" s="10" t="n"/>
     </row>
     <row r="282">
       <c r="A282" s="12" t="n"/>
@@ -19184,8 +19770,10 @@
       <c r="F282" s="10" t="n"/>
       <c r="G282" s="10" t="n"/>
       <c r="H282" s="10" t="n"/>
-      <c r="I282" s="12" t="n"/>
+      <c r="I282" s="10" t="n"/>
       <c r="J282" s="10" t="n"/>
+      <c r="K282" s="12" t="n"/>
+      <c r="L282" s="10" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="12" t="n"/>
@@ -19196,8 +19784,10 @@
       <c r="F283" s="10" t="n"/>
       <c r="G283" s="10" t="n"/>
       <c r="H283" s="10" t="n"/>
-      <c r="I283" s="12" t="n"/>
+      <c r="I283" s="10" t="n"/>
       <c r="J283" s="10" t="n"/>
+      <c r="K283" s="12" t="n"/>
+      <c r="L283" s="10" t="n"/>
     </row>
     <row r="284">
       <c r="A284" s="12" t="n"/>
@@ -19208,8 +19798,10 @@
       <c r="F284" s="10" t="n"/>
       <c r="G284" s="10" t="n"/>
       <c r="H284" s="10" t="n"/>
-      <c r="I284" s="12" t="n"/>
+      <c r="I284" s="10" t="n"/>
       <c r="J284" s="10" t="n"/>
+      <c r="K284" s="12" t="n"/>
+      <c r="L284" s="10" t="n"/>
     </row>
     <row r="285">
       <c r="A285" s="12" t="n"/>
@@ -19220,8 +19812,10 @@
       <c r="F285" s="10" t="n"/>
       <c r="G285" s="10" t="n"/>
       <c r="H285" s="10" t="n"/>
-      <c r="I285" s="12" t="n"/>
+      <c r="I285" s="10" t="n"/>
       <c r="J285" s="10" t="n"/>
+      <c r="K285" s="12" t="n"/>
+      <c r="L285" s="10" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="12" t="n"/>
@@ -19232,8 +19826,10 @@
       <c r="F286" s="10" t="n"/>
       <c r="G286" s="10" t="n"/>
       <c r="H286" s="10" t="n"/>
-      <c r="I286" s="12" t="n"/>
+      <c r="I286" s="10" t="n"/>
       <c r="J286" s="10" t="n"/>
+      <c r="K286" s="12" t="n"/>
+      <c r="L286" s="10" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="12" t="n"/>
@@ -19244,8 +19840,10 @@
       <c r="F287" s="10" t="n"/>
       <c r="G287" s="10" t="n"/>
       <c r="H287" s="10" t="n"/>
-      <c r="I287" s="12" t="n"/>
+      <c r="I287" s="10" t="n"/>
       <c r="J287" s="10" t="n"/>
+      <c r="K287" s="12" t="n"/>
+      <c r="L287" s="10" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="12" t="n"/>
@@ -19256,8 +19854,10 @@
       <c r="F288" s="10" t="n"/>
       <c r="G288" s="10" t="n"/>
       <c r="H288" s="10" t="n"/>
-      <c r="I288" s="12" t="n"/>
+      <c r="I288" s="10" t="n"/>
       <c r="J288" s="10" t="n"/>
+      <c r="K288" s="12" t="n"/>
+      <c r="L288" s="10" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="12" t="n"/>
@@ -19268,8 +19868,10 @@
       <c r="F289" s="10" t="n"/>
       <c r="G289" s="10" t="n"/>
       <c r="H289" s="10" t="n"/>
-      <c r="I289" s="12" t="n"/>
+      <c r="I289" s="10" t="n"/>
       <c r="J289" s="10" t="n"/>
+      <c r="K289" s="12" t="n"/>
+      <c r="L289" s="10" t="n"/>
     </row>
     <row r="290">
       <c r="A290" s="12" t="n"/>
@@ -19280,8 +19882,10 @@
       <c r="F290" s="10" t="n"/>
       <c r="G290" s="10" t="n"/>
       <c r="H290" s="10" t="n"/>
-      <c r="I290" s="12" t="n"/>
+      <c r="I290" s="10" t="n"/>
       <c r="J290" s="10" t="n"/>
+      <c r="K290" s="12" t="n"/>
+      <c r="L290" s="10" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="12" t="n"/>
@@ -19292,8 +19896,10 @@
       <c r="F291" s="10" t="n"/>
       <c r="G291" s="10" t="n"/>
       <c r="H291" s="10" t="n"/>
-      <c r="I291" s="12" t="n"/>
+      <c r="I291" s="10" t="n"/>
       <c r="J291" s="10" t="n"/>
+      <c r="K291" s="12" t="n"/>
+      <c r="L291" s="10" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="12" t="n"/>
@@ -19304,8 +19910,10 @@
       <c r="F292" s="10" t="n"/>
       <c r="G292" s="10" t="n"/>
       <c r="H292" s="10" t="n"/>
-      <c r="I292" s="12" t="n"/>
+      <c r="I292" s="10" t="n"/>
       <c r="J292" s="10" t="n"/>
+      <c r="K292" s="12" t="n"/>
+      <c r="L292" s="10" t="n"/>
     </row>
     <row r="293">
       <c r="A293" s="12" t="n"/>
@@ -19316,8 +19924,10 @@
       <c r="F293" s="10" t="n"/>
       <c r="G293" s="10" t="n"/>
       <c r="H293" s="10" t="n"/>
-      <c r="I293" s="12" t="n"/>
+      <c r="I293" s="10" t="n"/>
       <c r="J293" s="10" t="n"/>
+      <c r="K293" s="12" t="n"/>
+      <c r="L293" s="10" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="12" t="n"/>
@@ -19328,8 +19938,10 @@
       <c r="F294" s="10" t="n"/>
       <c r="G294" s="10" t="n"/>
       <c r="H294" s="10" t="n"/>
-      <c r="I294" s="12" t="n"/>
+      <c r="I294" s="10" t="n"/>
       <c r="J294" s="10" t="n"/>
+      <c r="K294" s="12" t="n"/>
+      <c r="L294" s="10" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="12" t="n"/>
@@ -19340,8 +19952,10 @@
       <c r="F295" s="10" t="n"/>
       <c r="G295" s="10" t="n"/>
       <c r="H295" s="10" t="n"/>
-      <c r="I295" s="12" t="n"/>
+      <c r="I295" s="10" t="n"/>
       <c r="J295" s="10" t="n"/>
+      <c r="K295" s="12" t="n"/>
+      <c r="L295" s="10" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="12" t="n"/>
@@ -19352,8 +19966,10 @@
       <c r="F296" s="10" t="n"/>
       <c r="G296" s="10" t="n"/>
       <c r="H296" s="10" t="n"/>
-      <c r="I296" s="12" t="n"/>
+      <c r="I296" s="10" t="n"/>
       <c r="J296" s="10" t="n"/>
+      <c r="K296" s="12" t="n"/>
+      <c r="L296" s="10" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="12" t="n"/>
@@ -19364,8 +19980,10 @@
       <c r="F297" s="10" t="n"/>
       <c r="G297" s="10" t="n"/>
       <c r="H297" s="10" t="n"/>
-      <c r="I297" s="12" t="n"/>
+      <c r="I297" s="10" t="n"/>
       <c r="J297" s="10" t="n"/>
+      <c r="K297" s="12" t="n"/>
+      <c r="L297" s="10" t="n"/>
     </row>
     <row r="298">
       <c r="A298" s="12" t="n"/>
@@ -19376,8 +19994,10 @@
       <c r="F298" s="10" t="n"/>
       <c r="G298" s="10" t="n"/>
       <c r="H298" s="10" t="n"/>
-      <c r="I298" s="12" t="n"/>
+      <c r="I298" s="10" t="n"/>
       <c r="J298" s="10" t="n"/>
+      <c r="K298" s="12" t="n"/>
+      <c r="L298" s="10" t="n"/>
     </row>
     <row r="299">
       <c r="A299" s="12" t="n"/>
@@ -19388,8 +20008,10 @@
       <c r="F299" s="10" t="n"/>
       <c r="G299" s="10" t="n"/>
       <c r="H299" s="10" t="n"/>
-      <c r="I299" s="12" t="n"/>
+      <c r="I299" s="10" t="n"/>
       <c r="J299" s="10" t="n"/>
+      <c r="K299" s="12" t="n"/>
+      <c r="L299" s="10" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="12" t="n"/>
@@ -19400,8 +20022,10 @@
       <c r="F300" s="10" t="n"/>
       <c r="G300" s="10" t="n"/>
       <c r="H300" s="10" t="n"/>
-      <c r="I300" s="12" t="n"/>
+      <c r="I300" s="10" t="n"/>
       <c r="J300" s="10" t="n"/>
+      <c r="K300" s="12" t="n"/>
+      <c r="L300" s="10" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="12" t="n"/>
@@ -19412,8 +20036,10 @@
       <c r="F301" s="10" t="n"/>
       <c r="G301" s="10" t="n"/>
       <c r="H301" s="10" t="n"/>
-      <c r="I301" s="12" t="n"/>
+      <c r="I301" s="10" t="n"/>
       <c r="J301" s="10" t="n"/>
+      <c r="K301" s="12" t="n"/>
+      <c r="L301" s="10" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="12" t="n"/>
@@ -19424,8 +20050,10 @@
       <c r="F302" s="10" t="n"/>
       <c r="G302" s="10" t="n"/>
       <c r="H302" s="10" t="n"/>
-      <c r="I302" s="12" t="n"/>
+      <c r="I302" s="10" t="n"/>
       <c r="J302" s="10" t="n"/>
+      <c r="K302" s="12" t="n"/>
+      <c r="L302" s="10" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="12" t="n"/>
@@ -19436,8 +20064,10 @@
       <c r="F303" s="10" t="n"/>
       <c r="G303" s="10" t="n"/>
       <c r="H303" s="10" t="n"/>
-      <c r="I303" s="12" t="n"/>
+      <c r="I303" s="10" t="n"/>
       <c r="J303" s="10" t="n"/>
+      <c r="K303" s="12" t="n"/>
+      <c r="L303" s="10" t="n"/>
     </row>
     <row r="304">
       <c r="A304" s="12" t="n"/>
@@ -19448,8 +20078,10 @@
       <c r="F304" s="10" t="n"/>
       <c r="G304" s="10" t="n"/>
       <c r="H304" s="10" t="n"/>
-      <c r="I304" s="12" t="n"/>
+      <c r="I304" s="10" t="n"/>
       <c r="J304" s="10" t="n"/>
+      <c r="K304" s="12" t="n"/>
+      <c r="L304" s="10" t="n"/>
     </row>
     <row r="305">
       <c r="A305" s="12" t="n"/>
@@ -19460,8 +20092,10 @@
       <c r="F305" s="10" t="n"/>
       <c r="G305" s="10" t="n"/>
       <c r="H305" s="10" t="n"/>
-      <c r="I305" s="12" t="n"/>
+      <c r="I305" s="10" t="n"/>
       <c r="J305" s="10" t="n"/>
+      <c r="K305" s="12" t="n"/>
+      <c r="L305" s="10" t="n"/>
     </row>
     <row r="306">
       <c r="A306" s="12" t="n"/>
@@ -19472,8 +20106,10 @@
       <c r="F306" s="10" t="n"/>
       <c r="G306" s="10" t="n"/>
       <c r="H306" s="10" t="n"/>
-      <c r="I306" s="12" t="n"/>
+      <c r="I306" s="10" t="n"/>
       <c r="J306" s="10" t="n"/>
+      <c r="K306" s="12" t="n"/>
+      <c r="L306" s="10" t="n"/>
     </row>
     <row r="307">
       <c r="A307" s="12" t="n"/>
@@ -19484,8 +20120,10 @@
       <c r="F307" s="10" t="n"/>
       <c r="G307" s="10" t="n"/>
       <c r="H307" s="10" t="n"/>
-      <c r="I307" s="12" t="n"/>
+      <c r="I307" s="10" t="n"/>
       <c r="J307" s="10" t="n"/>
+      <c r="K307" s="12" t="n"/>
+      <c r="L307" s="10" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="12" t="n"/>
@@ -19496,8 +20134,10 @@
       <c r="F308" s="10" t="n"/>
       <c r="G308" s="10" t="n"/>
       <c r="H308" s="10" t="n"/>
-      <c r="I308" s="12" t="n"/>
+      <c r="I308" s="10" t="n"/>
       <c r="J308" s="10" t="n"/>
+      <c r="K308" s="12" t="n"/>
+      <c r="L308" s="10" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="12" t="n"/>
@@ -19508,8 +20148,10 @@
       <c r="F309" s="10" t="n"/>
       <c r="G309" s="10" t="n"/>
       <c r="H309" s="10" t="n"/>
-      <c r="I309" s="12" t="n"/>
+      <c r="I309" s="10" t="n"/>
       <c r="J309" s="10" t="n"/>
+      <c r="K309" s="12" t="n"/>
+      <c r="L309" s="10" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="12" t="n"/>
@@ -19520,8 +20162,10 @@
       <c r="F310" s="10" t="n"/>
       <c r="G310" s="10" t="n"/>
       <c r="H310" s="10" t="n"/>
-      <c r="I310" s="12" t="n"/>
+      <c r="I310" s="10" t="n"/>
       <c r="J310" s="10" t="n"/>
+      <c r="K310" s="12" t="n"/>
+      <c r="L310" s="10" t="n"/>
     </row>
     <row r="311">
       <c r="A311" s="12" t="n"/>
@@ -19532,8 +20176,10 @@
       <c r="F311" s="10" t="n"/>
       <c r="G311" s="10" t="n"/>
       <c r="H311" s="10" t="n"/>
-      <c r="I311" s="12" t="n"/>
+      <c r="I311" s="10" t="n"/>
       <c r="J311" s="10" t="n"/>
+      <c r="K311" s="12" t="n"/>
+      <c r="L311" s="10" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="12" t="n"/>
@@ -19544,8 +20190,10 @@
       <c r="F312" s="10" t="n"/>
       <c r="G312" s="10" t="n"/>
       <c r="H312" s="10" t="n"/>
-      <c r="I312" s="12" t="n"/>
+      <c r="I312" s="10" t="n"/>
       <c r="J312" s="10" t="n"/>
+      <c r="K312" s="12" t="n"/>
+      <c r="L312" s="10" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="12" t="n"/>
@@ -19556,8 +20204,10 @@
       <c r="F313" s="10" t="n"/>
       <c r="G313" s="10" t="n"/>
       <c r="H313" s="10" t="n"/>
-      <c r="I313" s="12" t="n"/>
+      <c r="I313" s="10" t="n"/>
       <c r="J313" s="10" t="n"/>
+      <c r="K313" s="12" t="n"/>
+      <c r="L313" s="10" t="n"/>
     </row>
     <row r="314">
       <c r="A314" s="12" t="n"/>
@@ -19568,8 +20218,10 @@
       <c r="F314" s="10" t="n"/>
       <c r="G314" s="10" t="n"/>
       <c r="H314" s="10" t="n"/>
-      <c r="I314" s="12" t="n"/>
+      <c r="I314" s="10" t="n"/>
       <c r="J314" s="10" t="n"/>
+      <c r="K314" s="12" t="n"/>
+      <c r="L314" s="10" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="12" t="n"/>
@@ -19580,8 +20232,10 @@
       <c r="F315" s="10" t="n"/>
       <c r="G315" s="10" t="n"/>
       <c r="H315" s="10" t="n"/>
-      <c r="I315" s="12" t="n"/>
+      <c r="I315" s="10" t="n"/>
       <c r="J315" s="10" t="n"/>
+      <c r="K315" s="12" t="n"/>
+      <c r="L315" s="10" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="12" t="n"/>
@@ -19592,8 +20246,10 @@
       <c r="F316" s="10" t="n"/>
       <c r="G316" s="10" t="n"/>
       <c r="H316" s="10" t="n"/>
-      <c r="I316" s="12" t="n"/>
+      <c r="I316" s="10" t="n"/>
       <c r="J316" s="10" t="n"/>
+      <c r="K316" s="12" t="n"/>
+      <c r="L316" s="10" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="12" t="n"/>
@@ -19604,8 +20260,10 @@
       <c r="F317" s="10" t="n"/>
       <c r="G317" s="10" t="n"/>
       <c r="H317" s="10" t="n"/>
-      <c r="I317" s="12" t="n"/>
+      <c r="I317" s="10" t="n"/>
       <c r="J317" s="10" t="n"/>
+      <c r="K317" s="12" t="n"/>
+      <c r="L317" s="10" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="12" t="n"/>
@@ -19616,8 +20274,10 @@
       <c r="F318" s="10" t="n"/>
       <c r="G318" s="10" t="n"/>
       <c r="H318" s="10" t="n"/>
-      <c r="I318" s="12" t="n"/>
+      <c r="I318" s="10" t="n"/>
       <c r="J318" s="10" t="n"/>
+      <c r="K318" s="12" t="n"/>
+      <c r="L318" s="10" t="n"/>
     </row>
     <row r="319">
       <c r="A319" s="12" t="n"/>
@@ -19628,8 +20288,10 @@
       <c r="F319" s="10" t="n"/>
       <c r="G319" s="10" t="n"/>
       <c r="H319" s="10" t="n"/>
-      <c r="I319" s="12" t="n"/>
+      <c r="I319" s="10" t="n"/>
       <c r="J319" s="10" t="n"/>
+      <c r="K319" s="12" t="n"/>
+      <c r="L319" s="10" t="n"/>
     </row>
     <row r="320">
       <c r="A320" s="12" t="n"/>
@@ -19640,8 +20302,10 @@
       <c r="F320" s="10" t="n"/>
       <c r="G320" s="10" t="n"/>
       <c r="H320" s="10" t="n"/>
-      <c r="I320" s="12" t="n"/>
+      <c r="I320" s="10" t="n"/>
       <c r="J320" s="10" t="n"/>
+      <c r="K320" s="12" t="n"/>
+      <c r="L320" s="10" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="12" t="n"/>
@@ -19652,8 +20316,10 @@
       <c r="F321" s="10" t="n"/>
       <c r="G321" s="10" t="n"/>
       <c r="H321" s="10" t="n"/>
-      <c r="I321" s="12" t="n"/>
+      <c r="I321" s="10" t="n"/>
       <c r="J321" s="10" t="n"/>
+      <c r="K321" s="12" t="n"/>
+      <c r="L321" s="10" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="12" t="n"/>
@@ -19664,8 +20330,10 @@
       <c r="F322" s="10" t="n"/>
       <c r="G322" s="10" t="n"/>
       <c r="H322" s="10" t="n"/>
-      <c r="I322" s="12" t="n"/>
+      <c r="I322" s="10" t="n"/>
       <c r="J322" s="10" t="n"/>
+      <c r="K322" s="12" t="n"/>
+      <c r="L322" s="10" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="12" t="n"/>
@@ -19676,8 +20344,10 @@
       <c r="F323" s="10" t="n"/>
       <c r="G323" s="10" t="n"/>
       <c r="H323" s="10" t="n"/>
-      <c r="I323" s="12" t="n"/>
+      <c r="I323" s="10" t="n"/>
       <c r="J323" s="10" t="n"/>
+      <c r="K323" s="12" t="n"/>
+      <c r="L323" s="10" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="12" t="n"/>
@@ -19688,8 +20358,10 @@
       <c r="F324" s="10" t="n"/>
       <c r="G324" s="10" t="n"/>
       <c r="H324" s="10" t="n"/>
-      <c r="I324" s="12" t="n"/>
+      <c r="I324" s="10" t="n"/>
       <c r="J324" s="10" t="n"/>
+      <c r="K324" s="12" t="n"/>
+      <c r="L324" s="10" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="12" t="n"/>
@@ -19700,8 +20372,10 @@
       <c r="F325" s="10" t="n"/>
       <c r="G325" s="10" t="n"/>
       <c r="H325" s="10" t="n"/>
-      <c r="I325" s="12" t="n"/>
+      <c r="I325" s="10" t="n"/>
       <c r="J325" s="10" t="n"/>
+      <c r="K325" s="12" t="n"/>
+      <c r="L325" s="10" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="12" t="n"/>
@@ -19712,8 +20386,10 @@
       <c r="F326" s="10" t="n"/>
       <c r="G326" s="10" t="n"/>
       <c r="H326" s="10" t="n"/>
-      <c r="I326" s="12" t="n"/>
+      <c r="I326" s="10" t="n"/>
       <c r="J326" s="10" t="n"/>
+      <c r="K326" s="12" t="n"/>
+      <c r="L326" s="10" t="n"/>
     </row>
     <row r="327">
       <c r="A327" s="12" t="n"/>
@@ -19724,8 +20400,10 @@
       <c r="F327" s="10" t="n"/>
       <c r="G327" s="10" t="n"/>
       <c r="H327" s="10" t="n"/>
-      <c r="I327" s="12" t="n"/>
+      <c r="I327" s="10" t="n"/>
       <c r="J327" s="10" t="n"/>
+      <c r="K327" s="12" t="n"/>
+      <c r="L327" s="10" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="12" t="n"/>
@@ -19736,8 +20414,10 @@
       <c r="F328" s="10" t="n"/>
       <c r="G328" s="10" t="n"/>
       <c r="H328" s="10" t="n"/>
-      <c r="I328" s="12" t="n"/>
+      <c r="I328" s="10" t="n"/>
       <c r="J328" s="10" t="n"/>
+      <c r="K328" s="12" t="n"/>
+      <c r="L328" s="10" t="n"/>
     </row>
     <row r="329">
       <c r="A329" s="12" t="n"/>
@@ -19748,8 +20428,10 @@
       <c r="F329" s="10" t="n"/>
       <c r="G329" s="10" t="n"/>
       <c r="H329" s="10" t="n"/>
-      <c r="I329" s="12" t="n"/>
+      <c r="I329" s="10" t="n"/>
       <c r="J329" s="10" t="n"/>
+      <c r="K329" s="12" t="n"/>
+      <c r="L329" s="10" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="12" t="n"/>
@@ -19760,8 +20442,10 @@
       <c r="F330" s="10" t="n"/>
       <c r="G330" s="10" t="n"/>
       <c r="H330" s="10" t="n"/>
-      <c r="I330" s="12" t="n"/>
+      <c r="I330" s="10" t="n"/>
       <c r="J330" s="10" t="n"/>
+      <c r="K330" s="12" t="n"/>
+      <c r="L330" s="10" t="n"/>
     </row>
     <row r="331">
       <c r="A331" s="12" t="n"/>
@@ -19772,8 +20456,10 @@
       <c r="F331" s="10" t="n"/>
       <c r="G331" s="10" t="n"/>
       <c r="H331" s="10" t="n"/>
-      <c r="I331" s="12" t="n"/>
+      <c r="I331" s="10" t="n"/>
       <c r="J331" s="10" t="n"/>
+      <c r="K331" s="12" t="n"/>
+      <c r="L331" s="10" t="n"/>
     </row>
     <row r="332">
       <c r="A332" s="12" t="n"/>
@@ -19784,8 +20470,10 @@
       <c r="F332" s="10" t="n"/>
       <c r="G332" s="10" t="n"/>
       <c r="H332" s="10" t="n"/>
-      <c r="I332" s="12" t="n"/>
+      <c r="I332" s="10" t="n"/>
       <c r="J332" s="10" t="n"/>
+      <c r="K332" s="12" t="n"/>
+      <c r="L332" s="10" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="12" t="n"/>
@@ -19796,8 +20484,10 @@
       <c r="F333" s="10" t="n"/>
       <c r="G333" s="10" t="n"/>
       <c r="H333" s="10" t="n"/>
-      <c r="I333" s="12" t="n"/>
+      <c r="I333" s="10" t="n"/>
       <c r="J333" s="10" t="n"/>
+      <c r="K333" s="12" t="n"/>
+      <c r="L333" s="10" t="n"/>
     </row>
     <row r="334">
       <c r="A334" s="12" t="n"/>
@@ -19808,8 +20498,10 @@
       <c r="F334" s="10" t="n"/>
       <c r="G334" s="10" t="n"/>
       <c r="H334" s="10" t="n"/>
-      <c r="I334" s="12" t="n"/>
+      <c r="I334" s="10" t="n"/>
       <c r="J334" s="10" t="n"/>
+      <c r="K334" s="12" t="n"/>
+      <c r="L334" s="10" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="12" t="n"/>
@@ -19820,8 +20512,10 @@
       <c r="F335" s="10" t="n"/>
       <c r="G335" s="10" t="n"/>
       <c r="H335" s="10" t="n"/>
-      <c r="I335" s="12" t="n"/>
+      <c r="I335" s="10" t="n"/>
       <c r="J335" s="10" t="n"/>
+      <c r="K335" s="12" t="n"/>
+      <c r="L335" s="10" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="12" t="n"/>
@@ -19832,8 +20526,10 @@
       <c r="F336" s="10" t="n"/>
       <c r="G336" s="10" t="n"/>
       <c r="H336" s="10" t="n"/>
-      <c r="I336" s="12" t="n"/>
+      <c r="I336" s="10" t="n"/>
       <c r="J336" s="10" t="n"/>
+      <c r="K336" s="12" t="n"/>
+      <c r="L336" s="10" t="n"/>
     </row>
     <row r="337">
       <c r="A337" s="12" t="n"/>
@@ -19844,8 +20540,10 @@
       <c r="F337" s="10" t="n"/>
       <c r="G337" s="10" t="n"/>
       <c r="H337" s="10" t="n"/>
-      <c r="I337" s="12" t="n"/>
+      <c r="I337" s="10" t="n"/>
       <c r="J337" s="10" t="n"/>
+      <c r="K337" s="12" t="n"/>
+      <c r="L337" s="10" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="12" t="n"/>
@@ -19856,8 +20554,10 @@
       <c r="F338" s="10" t="n"/>
       <c r="G338" s="10" t="n"/>
       <c r="H338" s="10" t="n"/>
-      <c r="I338" s="12" t="n"/>
+      <c r="I338" s="10" t="n"/>
       <c r="J338" s="10" t="n"/>
+      <c r="K338" s="12" t="n"/>
+      <c r="L338" s="10" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="12" t="n"/>
@@ -19868,8 +20568,10 @@
       <c r="F339" s="10" t="n"/>
       <c r="G339" s="10" t="n"/>
       <c r="H339" s="10" t="n"/>
-      <c r="I339" s="12" t="n"/>
+      <c r="I339" s="10" t="n"/>
       <c r="J339" s="10" t="n"/>
+      <c r="K339" s="12" t="n"/>
+      <c r="L339" s="10" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="12" t="n"/>
@@ -19880,8 +20582,10 @@
       <c r="F340" s="10" t="n"/>
       <c r="G340" s="10" t="n"/>
       <c r="H340" s="10" t="n"/>
-      <c r="I340" s="12" t="n"/>
+      <c r="I340" s="10" t="n"/>
       <c r="J340" s="10" t="n"/>
+      <c r="K340" s="12" t="n"/>
+      <c r="L340" s="10" t="n"/>
     </row>
     <row r="341">
       <c r="A341" s="12" t="n"/>
@@ -19892,8 +20596,10 @@
       <c r="F341" s="10" t="n"/>
       <c r="G341" s="10" t="n"/>
       <c r="H341" s="10" t="n"/>
-      <c r="I341" s="12" t="n"/>
+      <c r="I341" s="10" t="n"/>
       <c r="J341" s="10" t="n"/>
+      <c r="K341" s="12" t="n"/>
+      <c r="L341" s="10" t="n"/>
     </row>
     <row r="342">
       <c r="A342" s="12" t="n"/>
@@ -19904,8 +20610,10 @@
       <c r="F342" s="10" t="n"/>
       <c r="G342" s="10" t="n"/>
       <c r="H342" s="10" t="n"/>
-      <c r="I342" s="12" t="n"/>
+      <c r="I342" s="10" t="n"/>
       <c r="J342" s="10" t="n"/>
+      <c r="K342" s="12" t="n"/>
+      <c r="L342" s="10" t="n"/>
     </row>
     <row r="343">
       <c r="A343" s="12" t="n"/>
@@ -19916,8 +20624,10 @@
       <c r="F343" s="10" t="n"/>
       <c r="G343" s="10" t="n"/>
       <c r="H343" s="10" t="n"/>
-      <c r="I343" s="12" t="n"/>
+      <c r="I343" s="10" t="n"/>
       <c r="J343" s="10" t="n"/>
+      <c r="K343" s="12" t="n"/>
+      <c r="L343" s="10" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="12" t="n"/>
@@ -19928,8 +20638,10 @@
       <c r="F344" s="10" t="n"/>
       <c r="G344" s="10" t="n"/>
       <c r="H344" s="10" t="n"/>
-      <c r="I344" s="12" t="n"/>
+      <c r="I344" s="10" t="n"/>
       <c r="J344" s="10" t="n"/>
+      <c r="K344" s="12" t="n"/>
+      <c r="L344" s="10" t="n"/>
     </row>
     <row r="345">
       <c r="A345" s="12" t="n"/>
@@ -19940,8 +20652,10 @@
       <c r="F345" s="10" t="n"/>
       <c r="G345" s="10" t="n"/>
       <c r="H345" s="10" t="n"/>
-      <c r="I345" s="12" t="n"/>
+      <c r="I345" s="10" t="n"/>
       <c r="J345" s="10" t="n"/>
+      <c r="K345" s="12" t="n"/>
+      <c r="L345" s="10" t="n"/>
     </row>
     <row r="346">
       <c r="A346" s="12" t="n"/>
@@ -19952,8 +20666,10 @@
       <c r="F346" s="10" t="n"/>
       <c r="G346" s="10" t="n"/>
       <c r="H346" s="10" t="n"/>
-      <c r="I346" s="12" t="n"/>
+      <c r="I346" s="10" t="n"/>
       <c r="J346" s="10" t="n"/>
+      <c r="K346" s="12" t="n"/>
+      <c r="L346" s="10" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="12" t="n"/>
@@ -19964,8 +20680,10 @@
       <c r="F347" s="10" t="n"/>
       <c r="G347" s="10" t="n"/>
       <c r="H347" s="10" t="n"/>
-      <c r="I347" s="12" t="n"/>
+      <c r="I347" s="10" t="n"/>
       <c r="J347" s="10" t="n"/>
+      <c r="K347" s="12" t="n"/>
+      <c r="L347" s="10" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="12" t="n"/>
@@ -19976,8 +20694,10 @@
       <c r="F348" s="10" t="n"/>
       <c r="G348" s="10" t="n"/>
       <c r="H348" s="10" t="n"/>
-      <c r="I348" s="12" t="n"/>
+      <c r="I348" s="10" t="n"/>
       <c r="J348" s="10" t="n"/>
+      <c r="K348" s="12" t="n"/>
+      <c r="L348" s="10" t="n"/>
     </row>
     <row r="349">
       <c r="A349" s="12" t="n"/>
@@ -19988,8 +20708,10 @@
       <c r="F349" s="10" t="n"/>
       <c r="G349" s="10" t="n"/>
       <c r="H349" s="10" t="n"/>
-      <c r="I349" s="12" t="n"/>
+      <c r="I349" s="10" t="n"/>
       <c r="J349" s="10" t="n"/>
+      <c r="K349" s="12" t="n"/>
+      <c r="L349" s="10" t="n"/>
     </row>
     <row r="350">
       <c r="A350" s="12" t="n"/>
@@ -20000,8 +20722,10 @@
       <c r="F350" s="10" t="n"/>
       <c r="G350" s="10" t="n"/>
       <c r="H350" s="10" t="n"/>
-      <c r="I350" s="12" t="n"/>
+      <c r="I350" s="10" t="n"/>
       <c r="J350" s="10" t="n"/>
+      <c r="K350" s="12" t="n"/>
+      <c r="L350" s="10" t="n"/>
     </row>
     <row r="351">
       <c r="A351" s="12" t="n"/>
@@ -20012,8 +20736,10 @@
       <c r="F351" s="10" t="n"/>
       <c r="G351" s="10" t="n"/>
       <c r="H351" s="10" t="n"/>
-      <c r="I351" s="12" t="n"/>
+      <c r="I351" s="10" t="n"/>
       <c r="J351" s="10" t="n"/>
+      <c r="K351" s="12" t="n"/>
+      <c r="L351" s="10" t="n"/>
     </row>
     <row r="352">
       <c r="A352" s="12" t="n"/>
@@ -20024,8 +20750,10 @@
       <c r="F352" s="10" t="n"/>
       <c r="G352" s="10" t="n"/>
       <c r="H352" s="10" t="n"/>
-      <c r="I352" s="12" t="n"/>
+      <c r="I352" s="10" t="n"/>
       <c r="J352" s="10" t="n"/>
+      <c r="K352" s="12" t="n"/>
+      <c r="L352" s="10" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="12" t="n"/>
@@ -20036,8 +20764,10 @@
       <c r="F353" s="10" t="n"/>
       <c r="G353" s="10" t="n"/>
       <c r="H353" s="10" t="n"/>
-      <c r="I353" s="12" t="n"/>
+      <c r="I353" s="10" t="n"/>
       <c r="J353" s="10" t="n"/>
+      <c r="K353" s="12" t="n"/>
+      <c r="L353" s="10" t="n"/>
     </row>
     <row r="354">
       <c r="A354" s="12" t="n"/>
@@ -20048,8 +20778,10 @@
       <c r="F354" s="10" t="n"/>
       <c r="G354" s="10" t="n"/>
       <c r="H354" s="10" t="n"/>
-      <c r="I354" s="12" t="n"/>
+      <c r="I354" s="10" t="n"/>
       <c r="J354" s="10" t="n"/>
+      <c r="K354" s="12" t="n"/>
+      <c r="L354" s="10" t="n"/>
     </row>
     <row r="355">
       <c r="A355" s="12" t="n"/>
@@ -20060,8 +20792,10 @@
       <c r="F355" s="10" t="n"/>
       <c r="G355" s="10" t="n"/>
       <c r="H355" s="10" t="n"/>
-      <c r="I355" s="12" t="n"/>
+      <c r="I355" s="10" t="n"/>
       <c r="J355" s="10" t="n"/>
+      <c r="K355" s="12" t="n"/>
+      <c r="L355" s="10" t="n"/>
     </row>
     <row r="356">
       <c r="A356" s="12" t="n"/>
@@ -20072,8 +20806,10 @@
       <c r="F356" s="10" t="n"/>
       <c r="G356" s="10" t="n"/>
       <c r="H356" s="10" t="n"/>
-      <c r="I356" s="12" t="n"/>
+      <c r="I356" s="10" t="n"/>
       <c r="J356" s="10" t="n"/>
+      <c r="K356" s="12" t="n"/>
+      <c r="L356" s="10" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="12" t="n"/>
@@ -20084,8 +20820,10 @@
       <c r="F357" s="10" t="n"/>
       <c r="G357" s="10" t="n"/>
       <c r="H357" s="10" t="n"/>
-      <c r="I357" s="12" t="n"/>
+      <c r="I357" s="10" t="n"/>
       <c r="J357" s="10" t="n"/>
+      <c r="K357" s="12" t="n"/>
+      <c r="L357" s="10" t="n"/>
     </row>
     <row r="358">
       <c r="A358" s="12" t="n"/>
@@ -20096,8 +20834,10 @@
       <c r="F358" s="10" t="n"/>
       <c r="G358" s="10" t="n"/>
       <c r="H358" s="10" t="n"/>
-      <c r="I358" s="12" t="n"/>
+      <c r="I358" s="10" t="n"/>
       <c r="J358" s="10" t="n"/>
+      <c r="K358" s="12" t="n"/>
+      <c r="L358" s="10" t="n"/>
     </row>
     <row r="359">
       <c r="A359" s="12" t="n"/>
@@ -20108,8 +20848,10 @@
       <c r="F359" s="10" t="n"/>
       <c r="G359" s="10" t="n"/>
       <c r="H359" s="10" t="n"/>
-      <c r="I359" s="12" t="n"/>
+      <c r="I359" s="10" t="n"/>
       <c r="J359" s="10" t="n"/>
+      <c r="K359" s="12" t="n"/>
+      <c r="L359" s="10" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="12" t="n"/>
@@ -20120,8 +20862,10 @@
       <c r="F360" s="10" t="n"/>
       <c r="G360" s="10" t="n"/>
       <c r="H360" s="10" t="n"/>
-      <c r="I360" s="12" t="n"/>
+      <c r="I360" s="10" t="n"/>
       <c r="J360" s="10" t="n"/>
+      <c r="K360" s="12" t="n"/>
+      <c r="L360" s="10" t="n"/>
     </row>
     <row r="361">
       <c r="A361" s="12" t="n"/>
@@ -20132,8 +20876,10 @@
       <c r="F361" s="10" t="n"/>
       <c r="G361" s="10" t="n"/>
       <c r="H361" s="10" t="n"/>
-      <c r="I361" s="12" t="n"/>
+      <c r="I361" s="10" t="n"/>
       <c r="J361" s="10" t="n"/>
+      <c r="K361" s="12" t="n"/>
+      <c r="L361" s="10" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="12" t="n"/>
@@ -20144,8 +20890,10 @@
       <c r="F362" s="10" t="n"/>
       <c r="G362" s="10" t="n"/>
       <c r="H362" s="10" t="n"/>
-      <c r="I362" s="12" t="n"/>
+      <c r="I362" s="10" t="n"/>
       <c r="J362" s="10" t="n"/>
+      <c r="K362" s="12" t="n"/>
+      <c r="L362" s="10" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="12" t="n"/>
@@ -20156,8 +20904,10 @@
       <c r="F363" s="10" t="n"/>
       <c r="G363" s="10" t="n"/>
       <c r="H363" s="10" t="n"/>
-      <c r="I363" s="12" t="n"/>
+      <c r="I363" s="10" t="n"/>
       <c r="J363" s="10" t="n"/>
+      <c r="K363" s="12" t="n"/>
+      <c r="L363" s="10" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="12" t="n"/>
@@ -20168,8 +20918,10 @@
       <c r="F364" s="10" t="n"/>
       <c r="G364" s="10" t="n"/>
       <c r="H364" s="10" t="n"/>
-      <c r="I364" s="12" t="n"/>
+      <c r="I364" s="10" t="n"/>
       <c r="J364" s="10" t="n"/>
+      <c r="K364" s="12" t="n"/>
+      <c r="L364" s="10" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="12" t="n"/>
@@ -20180,8 +20932,10 @@
       <c r="F365" s="10" t="n"/>
       <c r="G365" s="10" t="n"/>
       <c r="H365" s="10" t="n"/>
-      <c r="I365" s="12" t="n"/>
+      <c r="I365" s="10" t="n"/>
       <c r="J365" s="10" t="n"/>
+      <c r="K365" s="12" t="n"/>
+      <c r="L365" s="10" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="12" t="n"/>
@@ -20192,8 +20946,10 @@
       <c r="F366" s="10" t="n"/>
       <c r="G366" s="10" t="n"/>
       <c r="H366" s="10" t="n"/>
-      <c r="I366" s="12" t="n"/>
+      <c r="I366" s="10" t="n"/>
       <c r="J366" s="10" t="n"/>
+      <c r="K366" s="12" t="n"/>
+      <c r="L366" s="10" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="12" t="n"/>
@@ -20204,8 +20960,10 @@
       <c r="F367" s="10" t="n"/>
       <c r="G367" s="10" t="n"/>
       <c r="H367" s="10" t="n"/>
-      <c r="I367" s="12" t="n"/>
+      <c r="I367" s="10" t="n"/>
       <c r="J367" s="10" t="n"/>
+      <c r="K367" s="12" t="n"/>
+      <c r="L367" s="10" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="12" t="n"/>
@@ -20216,8 +20974,10 @@
       <c r="F368" s="10" t="n"/>
       <c r="G368" s="10" t="n"/>
       <c r="H368" s="10" t="n"/>
-      <c r="I368" s="12" t="n"/>
+      <c r="I368" s="10" t="n"/>
       <c r="J368" s="10" t="n"/>
+      <c r="K368" s="12" t="n"/>
+      <c r="L368" s="10" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="12" t="n"/>
@@ -20228,8 +20988,10 @@
       <c r="F369" s="10" t="n"/>
       <c r="G369" s="10" t="n"/>
       <c r="H369" s="10" t="n"/>
-      <c r="I369" s="12" t="n"/>
+      <c r="I369" s="10" t="n"/>
       <c r="J369" s="10" t="n"/>
+      <c r="K369" s="12" t="n"/>
+      <c r="L369" s="10" t="n"/>
     </row>
     <row r="370">
       <c r="A370" s="12" t="n"/>
@@ -20240,8 +21002,10 @@
       <c r="F370" s="10" t="n"/>
       <c r="G370" s="10" t="n"/>
       <c r="H370" s="10" t="n"/>
-      <c r="I370" s="12" t="n"/>
+      <c r="I370" s="10" t="n"/>
       <c r="J370" s="10" t="n"/>
+      <c r="K370" s="12" t="n"/>
+      <c r="L370" s="10" t="n"/>
     </row>
     <row r="371">
       <c r="A371" s="12" t="n"/>
@@ -20252,8 +21016,10 @@
       <c r="F371" s="10" t="n"/>
       <c r="G371" s="10" t="n"/>
       <c r="H371" s="10" t="n"/>
-      <c r="I371" s="12" t="n"/>
+      <c r="I371" s="10" t="n"/>
       <c r="J371" s="10" t="n"/>
+      <c r="K371" s="12" t="n"/>
+      <c r="L371" s="10" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="12" t="n"/>
@@ -20264,8 +21030,10 @@
       <c r="F372" s="10" t="n"/>
       <c r="G372" s="10" t="n"/>
       <c r="H372" s="10" t="n"/>
-      <c r="I372" s="12" t="n"/>
+      <c r="I372" s="10" t="n"/>
       <c r="J372" s="10" t="n"/>
+      <c r="K372" s="12" t="n"/>
+      <c r="L372" s="10" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="12" t="n"/>
@@ -20276,8 +21044,10 @@
       <c r="F373" s="10" t="n"/>
       <c r="G373" s="10" t="n"/>
       <c r="H373" s="10" t="n"/>
-      <c r="I373" s="12" t="n"/>
+      <c r="I373" s="10" t="n"/>
       <c r="J373" s="10" t="n"/>
+      <c r="K373" s="12" t="n"/>
+      <c r="L373" s="10" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="12" t="n"/>
@@ -20288,8 +21058,10 @@
       <c r="F374" s="10" t="n"/>
       <c r="G374" s="10" t="n"/>
       <c r="H374" s="10" t="n"/>
-      <c r="I374" s="12" t="n"/>
+      <c r="I374" s="10" t="n"/>
       <c r="J374" s="10" t="n"/>
+      <c r="K374" s="12" t="n"/>
+      <c r="L374" s="10" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="12" t="n"/>
@@ -20300,8 +21072,10 @@
       <c r="F375" s="10" t="n"/>
       <c r="G375" s="10" t="n"/>
       <c r="H375" s="10" t="n"/>
-      <c r="I375" s="12" t="n"/>
+      <c r="I375" s="10" t="n"/>
       <c r="J375" s="10" t="n"/>
+      <c r="K375" s="12" t="n"/>
+      <c r="L375" s="10" t="n"/>
     </row>
     <row r="376">
       <c r="A376" s="12" t="n"/>
@@ -20312,8 +21086,10 @@
       <c r="F376" s="10" t="n"/>
       <c r="G376" s="10" t="n"/>
       <c r="H376" s="10" t="n"/>
-      <c r="I376" s="12" t="n"/>
+      <c r="I376" s="10" t="n"/>
       <c r="J376" s="10" t="n"/>
+      <c r="K376" s="12" t="n"/>
+      <c r="L376" s="10" t="n"/>
     </row>
     <row r="377">
       <c r="A377" s="12" t="n"/>
@@ -20324,8 +21100,10 @@
       <c r="F377" s="10" t="n"/>
       <c r="G377" s="10" t="n"/>
       <c r="H377" s="10" t="n"/>
-      <c r="I377" s="12" t="n"/>
+      <c r="I377" s="10" t="n"/>
       <c r="J377" s="10" t="n"/>
+      <c r="K377" s="12" t="n"/>
+      <c r="L377" s="10" t="n"/>
     </row>
     <row r="378">
       <c r="A378" s="12" t="n"/>
@@ -20336,8 +21114,10 @@
       <c r="F378" s="10" t="n"/>
       <c r="G378" s="10" t="n"/>
       <c r="H378" s="10" t="n"/>
-      <c r="I378" s="12" t="n"/>
+      <c r="I378" s="10" t="n"/>
       <c r="J378" s="10" t="n"/>
+      <c r="K378" s="12" t="n"/>
+      <c r="L378" s="10" t="n"/>
     </row>
     <row r="379">
       <c r="A379" s="12" t="n"/>
@@ -20348,8 +21128,10 @@
       <c r="F379" s="10" t="n"/>
       <c r="G379" s="10" t="n"/>
       <c r="H379" s="10" t="n"/>
-      <c r="I379" s="12" t="n"/>
+      <c r="I379" s="10" t="n"/>
       <c r="J379" s="10" t="n"/>
+      <c r="K379" s="12" t="n"/>
+      <c r="L379" s="10" t="n"/>
     </row>
     <row r="380">
       <c r="A380" s="12" t="n"/>
@@ -20360,8 +21142,10 @@
       <c r="F380" s="10" t="n"/>
       <c r="G380" s="10" t="n"/>
       <c r="H380" s="10" t="n"/>
-      <c r="I380" s="12" t="n"/>
+      <c r="I380" s="10" t="n"/>
       <c r="J380" s="10" t="n"/>
+      <c r="K380" s="12" t="n"/>
+      <c r="L380" s="10" t="n"/>
     </row>
     <row r="381">
       <c r="A381" s="12" t="n"/>
@@ -20372,8 +21156,10 @@
       <c r="F381" s="10" t="n"/>
       <c r="G381" s="10" t="n"/>
       <c r="H381" s="10" t="n"/>
-      <c r="I381" s="12" t="n"/>
+      <c r="I381" s="10" t="n"/>
       <c r="J381" s="10" t="n"/>
+      <c r="K381" s="12" t="n"/>
+      <c r="L381" s="10" t="n"/>
     </row>
     <row r="382">
       <c r="A382" s="12" t="n"/>
@@ -20384,8 +21170,10 @@
       <c r="F382" s="10" t="n"/>
       <c r="G382" s="10" t="n"/>
       <c r="H382" s="10" t="n"/>
-      <c r="I382" s="12" t="n"/>
+      <c r="I382" s="10" t="n"/>
       <c r="J382" s="10" t="n"/>
+      <c r="K382" s="12" t="n"/>
+      <c r="L382" s="10" t="n"/>
     </row>
     <row r="383">
       <c r="A383" s="12" t="n"/>
@@ -20396,8 +21184,10 @@
       <c r="F383" s="10" t="n"/>
       <c r="G383" s="10" t="n"/>
       <c r="H383" s="10" t="n"/>
-      <c r="I383" s="12" t="n"/>
+      <c r="I383" s="10" t="n"/>
       <c r="J383" s="10" t="n"/>
+      <c r="K383" s="12" t="n"/>
+      <c r="L383" s="10" t="n"/>
     </row>
     <row r="384">
       <c r="A384" s="12" t="n"/>
@@ -20408,8 +21198,10 @@
       <c r="F384" s="10" t="n"/>
       <c r="G384" s="10" t="n"/>
       <c r="H384" s="10" t="n"/>
-      <c r="I384" s="12" t="n"/>
+      <c r="I384" s="10" t="n"/>
       <c r="J384" s="10" t="n"/>
+      <c r="K384" s="12" t="n"/>
+      <c r="L384" s="10" t="n"/>
     </row>
     <row r="385">
       <c r="A385" s="12" t="n"/>
@@ -20420,8 +21212,10 @@
       <c r="F385" s="10" t="n"/>
       <c r="G385" s="10" t="n"/>
       <c r="H385" s="10" t="n"/>
-      <c r="I385" s="12" t="n"/>
+      <c r="I385" s="10" t="n"/>
       <c r="J385" s="10" t="n"/>
+      <c r="K385" s="12" t="n"/>
+      <c r="L385" s="10" t="n"/>
     </row>
     <row r="386">
       <c r="A386" s="12" t="n"/>
@@ -20432,8 +21226,10 @@
       <c r="F386" s="10" t="n"/>
       <c r="G386" s="10" t="n"/>
       <c r="H386" s="10" t="n"/>
-      <c r="I386" s="12" t="n"/>
+      <c r="I386" s="10" t="n"/>
       <c r="J386" s="10" t="n"/>
+      <c r="K386" s="12" t="n"/>
+      <c r="L386" s="10" t="n"/>
     </row>
     <row r="387">
       <c r="A387" s="12" t="n"/>
@@ -20444,8 +21240,10 @@
       <c r="F387" s="10" t="n"/>
       <c r="G387" s="10" t="n"/>
       <c r="H387" s="10" t="n"/>
-      <c r="I387" s="12" t="n"/>
+      <c r="I387" s="10" t="n"/>
       <c r="J387" s="10" t="n"/>
+      <c r="K387" s="12" t="n"/>
+      <c r="L387" s="10" t="n"/>
     </row>
     <row r="388">
       <c r="A388" s="12" t="n"/>
@@ -20456,8 +21254,10 @@
       <c r="F388" s="10" t="n"/>
       <c r="G388" s="10" t="n"/>
       <c r="H388" s="10" t="n"/>
-      <c r="I388" s="12" t="n"/>
+      <c r="I388" s="10" t="n"/>
       <c r="J388" s="10" t="n"/>
+      <c r="K388" s="12" t="n"/>
+      <c r="L388" s="10" t="n"/>
     </row>
     <row r="389">
       <c r="A389" s="12" t="n"/>
@@ -20468,8 +21268,10 @@
       <c r="F389" s="10" t="n"/>
       <c r="G389" s="10" t="n"/>
       <c r="H389" s="10" t="n"/>
-      <c r="I389" s="12" t="n"/>
+      <c r="I389" s="10" t="n"/>
       <c r="J389" s="10" t="n"/>
+      <c r="K389" s="12" t="n"/>
+      <c r="L389" s="10" t="n"/>
     </row>
     <row r="390">
       <c r="A390" s="12" t="n"/>
@@ -20480,8 +21282,10 @@
       <c r="F390" s="10" t="n"/>
       <c r="G390" s="10" t="n"/>
       <c r="H390" s="10" t="n"/>
-      <c r="I390" s="12" t="n"/>
+      <c r="I390" s="10" t="n"/>
       <c r="J390" s="10" t="n"/>
+      <c r="K390" s="12" t="n"/>
+      <c r="L390" s="10" t="n"/>
     </row>
     <row r="391">
       <c r="A391" s="12" t="n"/>
@@ -20492,8 +21296,10 @@
       <c r="F391" s="10" t="n"/>
       <c r="G391" s="10" t="n"/>
       <c r="H391" s="10" t="n"/>
-      <c r="I391" s="12" t="n"/>
+      <c r="I391" s="10" t="n"/>
       <c r="J391" s="10" t="n"/>
+      <c r="K391" s="12" t="n"/>
+      <c r="L391" s="10" t="n"/>
     </row>
     <row r="392">
       <c r="A392" s="12" t="n"/>
@@ -20504,8 +21310,10 @@
       <c r="F392" s="10" t="n"/>
       <c r="G392" s="10" t="n"/>
       <c r="H392" s="10" t="n"/>
-      <c r="I392" s="12" t="n"/>
+      <c r="I392" s="10" t="n"/>
       <c r="J392" s="10" t="n"/>
+      <c r="K392" s="12" t="n"/>
+      <c r="L392" s="10" t="n"/>
     </row>
     <row r="393">
       <c r="A393" s="12" t="n"/>
@@ -20516,8 +21324,10 @@
       <c r="F393" s="10" t="n"/>
       <c r="G393" s="10" t="n"/>
       <c r="H393" s="10" t="n"/>
-      <c r="I393" s="12" t="n"/>
+      <c r="I393" s="10" t="n"/>
       <c r="J393" s="10" t="n"/>
+      <c r="K393" s="12" t="n"/>
+      <c r="L393" s="10" t="n"/>
     </row>
     <row r="394">
       <c r="A394" s="12" t="n"/>
@@ -20528,8 +21338,10 @@
       <c r="F394" s="10" t="n"/>
       <c r="G394" s="10" t="n"/>
       <c r="H394" s="10" t="n"/>
-      <c r="I394" s="12" t="n"/>
+      <c r="I394" s="10" t="n"/>
       <c r="J394" s="10" t="n"/>
+      <c r="K394" s="12" t="n"/>
+      <c r="L394" s="10" t="n"/>
     </row>
     <row r="395">
       <c r="A395" s="12" t="n"/>
@@ -20540,8 +21352,10 @@
       <c r="F395" s="10" t="n"/>
       <c r="G395" s="10" t="n"/>
       <c r="H395" s="10" t="n"/>
-      <c r="I395" s="12" t="n"/>
+      <c r="I395" s="10" t="n"/>
       <c r="J395" s="10" t="n"/>
+      <c r="K395" s="12" t="n"/>
+      <c r="L395" s="10" t="n"/>
     </row>
     <row r="396">
       <c r="A396" s="12" t="n"/>
@@ -20552,8 +21366,10 @@
       <c r="F396" s="10" t="n"/>
       <c r="G396" s="10" t="n"/>
       <c r="H396" s="10" t="n"/>
-      <c r="I396" s="12" t="n"/>
+      <c r="I396" s="10" t="n"/>
       <c r="J396" s="10" t="n"/>
+      <c r="K396" s="12" t="n"/>
+      <c r="L396" s="10" t="n"/>
     </row>
     <row r="397">
       <c r="A397" s="12" t="n"/>
@@ -20564,8 +21380,10 @@
       <c r="F397" s="10" t="n"/>
       <c r="G397" s="10" t="n"/>
       <c r="H397" s="10" t="n"/>
-      <c r="I397" s="12" t="n"/>
+      <c r="I397" s="10" t="n"/>
       <c r="J397" s="10" t="n"/>
+      <c r="K397" s="12" t="n"/>
+      <c r="L397" s="10" t="n"/>
     </row>
     <row r="398">
       <c r="A398" s="12" t="n"/>
@@ -20576,8 +21394,10 @@
       <c r="F398" s="10" t="n"/>
       <c r="G398" s="10" t="n"/>
       <c r="H398" s="10" t="n"/>
-      <c r="I398" s="12" t="n"/>
+      <c r="I398" s="10" t="n"/>
       <c r="J398" s="10" t="n"/>
+      <c r="K398" s="12" t="n"/>
+      <c r="L398" s="10" t="n"/>
     </row>
     <row r="399">
       <c r="A399" s="12" t="n"/>
@@ -20588,8 +21408,10 @@
       <c r="F399" s="10" t="n"/>
       <c r="G399" s="10" t="n"/>
       <c r="H399" s="10" t="n"/>
-      <c r="I399" s="12" t="n"/>
+      <c r="I399" s="10" t="n"/>
       <c r="J399" s="10" t="n"/>
+      <c r="K399" s="12" t="n"/>
+      <c r="L399" s="10" t="n"/>
     </row>
     <row r="400">
       <c r="A400" s="12" t="n"/>
@@ -20600,18 +21422,23 @@
       <c r="F400" s="10" t="n"/>
       <c r="G400" s="10" t="n"/>
       <c r="H400" s="10" t="n"/>
-      <c r="I400" s="12" t="n"/>
+      <c r="I400" s="10" t="n"/>
       <c r="J400" s="10" t="n"/>
+      <c r="K400" s="12" t="n"/>
+      <c r="L400" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="F3:F400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="B3:B400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Warm list,Tier 4 referral,Referral partner,Inbound - page,Inbound - social,Event"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H3:H400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="G3:G400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I3:I400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sent,Jeremy contacted,In progress,Closed won,Closed lost,No response"</formula1>
     </dataValidation>
   </dataValidations>
@@ -23990,7 +24817,4523 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:J21"/>
+  <dimension ref="A1:N200"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>People who already walk into the businesses you cannot reach. One liquor rep touches 15 accounts a week. Give before you ask - column K is the discipline, not a nicety. Priority fills itself from Type.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Partner name</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>How I know them</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>Accounts they touch</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>Last contact</t>
+        </is>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>Last thing I gave them</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>Date I gave it</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>Referrals received</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Dani Restrepo</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Liquor / food rep</t>
+        </is>
+      </c>
+      <c r="C3" s="8">
+        <f>IF(B3="","",IF(B3="Business broker","1 - Highest",IF(OR(B3="POS installer",B3="Bookkeeper / CPA"),"2 - High",IF(OR(B3="Liquor / food rep",B3="Consultant"),"3 - Strong",IF(B3="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Comped her table at LIV for years</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>305-555-0178</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>dani@example.com</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>15/wk</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Agreed to refer</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr"/>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>Sent her Marco's number for a tasting</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr"/>
+      <c r="M3" s="8">
+        <f>IF(A3="","",COUNTIF('Referral Log'!$C$4:$C$400,A3))</f>
+        <v/>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>Asked her to flag any spot changing hands</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="11">
+        <f>IF(B4="","",IF(B4="Business broker","1 - Highest",IF(OR(B4="POS installer",B4="Bookkeeper / CPA"),"2 - High",IF(OR(B4="Liquor / food rep",B4="Consultant"),"3 - Strong",IF(B4="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="12" t="n"/>
+      <c r="M4" s="11">
+        <f>IF(A4="","",COUNTIF('Referral Log'!$C$4:$C$400,A4))</f>
+        <v/>
+      </c>
+      <c r="N4" s="10" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="11">
+        <f>IF(B5="","",IF(B5="Business broker","1 - Highest",IF(OR(B5="POS installer",B5="Bookkeeper / CPA"),"2 - High",IF(OR(B5="Liquor / food rep",B5="Consultant"),"3 - Strong",IF(B5="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="12" t="n"/>
+      <c r="K5" s="10" t="n"/>
+      <c r="L5" s="12" t="n"/>
+      <c r="M5" s="11">
+        <f>IF(A5="","",COUNTIF('Referral Log'!$C$4:$C$400,A5))</f>
+        <v/>
+      </c>
+      <c r="N5" s="10" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="11">
+        <f>IF(B6="","",IF(B6="Business broker","1 - Highest",IF(OR(B6="POS installer",B6="Bookkeeper / CPA"),"2 - High",IF(OR(B6="Liquor / food rep",B6="Consultant"),"3 - Strong",IF(B6="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="10" t="n"/>
+      <c r="L6" s="12" t="n"/>
+      <c r="M6" s="11">
+        <f>IF(A6="","",COUNTIF('Referral Log'!$C$4:$C$400,A6))</f>
+        <v/>
+      </c>
+      <c r="N6" s="10" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="11">
+        <f>IF(B7="","",IF(B7="Business broker","1 - Highest",IF(OR(B7="POS installer",B7="Bookkeeper / CPA"),"2 - High",IF(OR(B7="Liquor / food rep",B7="Consultant"),"3 - Strong",IF(B7="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="12" t="n"/>
+      <c r="M7" s="11">
+        <f>IF(A7="","",COUNTIF('Referral Log'!$C$4:$C$400,A7))</f>
+        <v/>
+      </c>
+      <c r="N7" s="10" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="11">
+        <f>IF(B8="","",IF(B8="Business broker","1 - Highest",IF(OR(B8="POS installer",B8="Bookkeeper / CPA"),"2 - High",IF(OR(B8="Liquor / food rep",B8="Consultant"),"3 - Strong",IF(B8="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="10" t="n"/>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="12" t="n"/>
+      <c r="M8" s="11">
+        <f>IF(A8="","",COUNTIF('Referral Log'!$C$4:$C$400,A8))</f>
+        <v/>
+      </c>
+      <c r="N8" s="10" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="11">
+        <f>IF(B9="","",IF(B9="Business broker","1 - Highest",IF(OR(B9="POS installer",B9="Bookkeeper / CPA"),"2 - High",IF(OR(B9="Liquor / food rep",B9="Consultant"),"3 - Strong",IF(B9="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="11">
+        <f>IF(A9="","",COUNTIF('Referral Log'!$C$4:$C$400,A9))</f>
+        <v/>
+      </c>
+      <c r="N9" s="10" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="11">
+        <f>IF(B10="","",IF(B10="Business broker","1 - Highest",IF(OR(B10="POS installer",B10="Bookkeeper / CPA"),"2 - High",IF(OR(B10="Liquor / food rep",B10="Consultant"),"3 - Strong",IF(B10="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="11">
+        <f>IF(A10="","",COUNTIF('Referral Log'!$C$4:$C$400,A10))</f>
+        <v/>
+      </c>
+      <c r="N10" s="10" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="11">
+        <f>IF(B11="","",IF(B11="Business broker","1 - Highest",IF(OR(B11="POS installer",B11="Bookkeeper / CPA"),"2 - High",IF(OR(B11="Liquor / food rep",B11="Consultant"),"3 - Strong",IF(B11="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="12" t="n"/>
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="12" t="n"/>
+      <c r="M11" s="11">
+        <f>IF(A11="","",COUNTIF('Referral Log'!$C$4:$C$400,A11))</f>
+        <v/>
+      </c>
+      <c r="N11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="11">
+        <f>IF(B12="","",IF(B12="Business broker","1 - Highest",IF(OR(B12="POS installer",B12="Bookkeeper / CPA"),"2 - High",IF(OR(B12="Liquor / food rep",B12="Consultant"),"3 - Strong",IF(B12="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="10" t="n"/>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="12" t="n"/>
+      <c r="M12" s="11">
+        <f>IF(A12="","",COUNTIF('Referral Log'!$C$4:$C$400,A12))</f>
+        <v/>
+      </c>
+      <c r="N12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="11">
+        <f>IF(B13="","",IF(B13="Business broker","1 - Highest",IF(OR(B13="POS installer",B13="Bookkeeper / CPA"),"2 - High",IF(OR(B13="Liquor / food rep",B13="Consultant"),"3 - Strong",IF(B13="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="12" t="n"/>
+      <c r="M13" s="11">
+        <f>IF(A13="","",COUNTIF('Referral Log'!$C$4:$C$400,A13))</f>
+        <v/>
+      </c>
+      <c r="N13" s="10" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="11">
+        <f>IF(B14="","",IF(B14="Business broker","1 - Highest",IF(OR(B14="POS installer",B14="Bookkeeper / CPA"),"2 - High",IF(OR(B14="Liquor / food rep",B14="Consultant"),"3 - Strong",IF(B14="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="12" t="n"/>
+      <c r="M14" s="11">
+        <f>IF(A14="","",COUNTIF('Referral Log'!$C$4:$C$400,A14))</f>
+        <v/>
+      </c>
+      <c r="N14" s="10" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="11">
+        <f>IF(B15="","",IF(B15="Business broker","1 - Highest",IF(OR(B15="POS installer",B15="Bookkeeper / CPA"),"2 - High",IF(OR(B15="Liquor / food rep",B15="Consultant"),"3 - Strong",IF(B15="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n"/>
+      <c r="I15" s="10" t="n"/>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="11">
+        <f>IF(A15="","",COUNTIF('Referral Log'!$C$4:$C$400,A15))</f>
+        <v/>
+      </c>
+      <c r="N15" s="10" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="11">
+        <f>IF(B16="","",IF(B16="Business broker","1 - Highest",IF(OR(B16="POS installer",B16="Bookkeeper / CPA"),"2 - High",IF(OR(B16="Liquor / food rep",B16="Consultant"),"3 - Strong",IF(B16="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="10" t="n"/>
+      <c r="I16" s="10" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="10" t="n"/>
+      <c r="L16" s="12" t="n"/>
+      <c r="M16" s="11">
+        <f>IF(A16="","",COUNTIF('Referral Log'!$C$4:$C$400,A16))</f>
+        <v/>
+      </c>
+      <c r="N16" s="10" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="11">
+        <f>IF(B17="","",IF(B17="Business broker","1 - Highest",IF(OR(B17="POS installer",B17="Bookkeeper / CPA"),"2 - High",IF(OR(B17="Liquor / food rep",B17="Consultant"),"3 - Strong",IF(B17="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="10" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="11">
+        <f>IF(A17="","",COUNTIF('Referral Log'!$C$4:$C$400,A17))</f>
+        <v/>
+      </c>
+      <c r="N17" s="10" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="11">
+        <f>IF(B18="","",IF(B18="Business broker","1 - Highest",IF(OR(B18="POS installer",B18="Bookkeeper / CPA"),"2 - High",IF(OR(B18="Liquor / food rep",B18="Consultant"),"3 - Strong",IF(B18="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="10" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="10" t="n"/>
+      <c r="L18" s="12" t="n"/>
+      <c r="M18" s="11">
+        <f>IF(A18="","",COUNTIF('Referral Log'!$C$4:$C$400,A18))</f>
+        <v/>
+      </c>
+      <c r="N18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="11">
+        <f>IF(B19="","",IF(B19="Business broker","1 - Highest",IF(OR(B19="POS installer",B19="Bookkeeper / CPA"),"2 - High",IF(OR(B19="Liquor / food rep",B19="Consultant"),"3 - Strong",IF(B19="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="11">
+        <f>IF(A19="","",COUNTIF('Referral Log'!$C$4:$C$400,A19))</f>
+        <v/>
+      </c>
+      <c r="N19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="11">
+        <f>IF(B20="","",IF(B20="Business broker","1 - Highest",IF(OR(B20="POS installer",B20="Bookkeeper / CPA"),"2 - High",IF(OR(B20="Liquor / food rep",B20="Consultant"),"3 - Strong",IF(B20="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="10" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="10" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="11">
+        <f>IF(A20="","",COUNTIF('Referral Log'!$C$4:$C$400,A20))</f>
+        <v/>
+      </c>
+      <c r="N20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="11">
+        <f>IF(B21="","",IF(B21="Business broker","1 - Highest",IF(OR(B21="POS installer",B21="Bookkeeper / CPA"),"2 - High",IF(OR(B21="Liquor / food rep",B21="Consultant"),"3 - Strong",IF(B21="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="10" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="11">
+        <f>IF(A21="","",COUNTIF('Referral Log'!$C$4:$C$400,A21))</f>
+        <v/>
+      </c>
+      <c r="N21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="11">
+        <f>IF(B22="","",IF(B22="Business broker","1 - Highest",IF(OR(B22="POS installer",B22="Bookkeeper / CPA"),"2 - High",IF(OR(B22="Liquor / food rep",B22="Consultant"),"3 - Strong",IF(B22="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="10" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="11">
+        <f>IF(A22="","",COUNTIF('Referral Log'!$C$4:$C$400,A22))</f>
+        <v/>
+      </c>
+      <c r="N22" s="10" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="11">
+        <f>IF(B23="","",IF(B23="Business broker","1 - Highest",IF(OR(B23="POS installer",B23="Bookkeeper / CPA"),"2 - High",IF(OR(B23="Liquor / food rep",B23="Consultant"),"3 - Strong",IF(B23="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="10" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="10" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="11">
+        <f>IF(A23="","",COUNTIF('Referral Log'!$C$4:$C$400,A23))</f>
+        <v/>
+      </c>
+      <c r="N23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="11">
+        <f>IF(B24="","",IF(B24="Business broker","1 - Highest",IF(OR(B24="POS installer",B24="Bookkeeper / CPA"),"2 - High",IF(OR(B24="Liquor / food rep",B24="Consultant"),"3 - Strong",IF(B24="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="10" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="10" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="11">
+        <f>IF(A24="","",COUNTIF('Referral Log'!$C$4:$C$400,A24))</f>
+        <v/>
+      </c>
+      <c r="N24" s="10" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="11">
+        <f>IF(B25="","",IF(B25="Business broker","1 - Highest",IF(OR(B25="POS installer",B25="Bookkeeper / CPA"),"2 - High",IF(OR(B25="Liquor / food rep",B25="Consultant"),"3 - Strong",IF(B25="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="10" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="10" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="11">
+        <f>IF(A25="","",COUNTIF('Referral Log'!$C$4:$C$400,A25))</f>
+        <v/>
+      </c>
+      <c r="N25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="11">
+        <f>IF(B26="","",IF(B26="Business broker","1 - Highest",IF(OR(B26="POS installer",B26="Bookkeeper / CPA"),"2 - High",IF(OR(B26="Liquor / food rep",B26="Consultant"),"3 - Strong",IF(B26="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="10" t="n"/>
+      <c r="I26" s="10" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="10" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="11">
+        <f>IF(A26="","",COUNTIF('Referral Log'!$C$4:$C$400,A26))</f>
+        <v/>
+      </c>
+      <c r="N26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="11">
+        <f>IF(B27="","",IF(B27="Business broker","1 - Highest",IF(OR(B27="POS installer",B27="Bookkeeper / CPA"),"2 - High",IF(OR(B27="Liquor / food rep",B27="Consultant"),"3 - Strong",IF(B27="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
+      <c r="H27" s="10" t="n"/>
+      <c r="I27" s="10" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="10" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="11">
+        <f>IF(A27="","",COUNTIF('Referral Log'!$C$4:$C$400,A27))</f>
+        <v/>
+      </c>
+      <c r="N27" s="10" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="11">
+        <f>IF(B28="","",IF(B28="Business broker","1 - Highest",IF(OR(B28="POS installer",B28="Bookkeeper / CPA"),"2 - High",IF(OR(B28="Liquor / food rep",B28="Consultant"),"3 - Strong",IF(B28="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="10" t="n"/>
+      <c r="I28" s="10" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="10" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="11">
+        <f>IF(A28="","",COUNTIF('Referral Log'!$C$4:$C$400,A28))</f>
+        <v/>
+      </c>
+      <c r="N28" s="10" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="11">
+        <f>IF(B29="","",IF(B29="Business broker","1 - Highest",IF(OR(B29="POS installer",B29="Bookkeeper / CPA"),"2 - High",IF(OR(B29="Liquor / food rep",B29="Consultant"),"3 - Strong",IF(B29="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="10" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="10" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="11">
+        <f>IF(A29="","",COUNTIF('Referral Log'!$C$4:$C$400,A29))</f>
+        <v/>
+      </c>
+      <c r="N29" s="10" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="11">
+        <f>IF(B30="","",IF(B30="Business broker","1 - Highest",IF(OR(B30="POS installer",B30="Bookkeeper / CPA"),"2 - High",IF(OR(B30="Liquor / food rep",B30="Consultant"),"3 - Strong",IF(B30="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="10" t="n"/>
+      <c r="F30" s="10" t="n"/>
+      <c r="G30" s="10" t="n"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="10" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="10" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="11">
+        <f>IF(A30="","",COUNTIF('Referral Log'!$C$4:$C$400,A30))</f>
+        <v/>
+      </c>
+      <c r="N30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="11">
+        <f>IF(B31="","",IF(B31="Business broker","1 - Highest",IF(OR(B31="POS installer",B31="Bookkeeper / CPA"),"2 - High",IF(OR(B31="Liquor / food rep",B31="Consultant"),"3 - Strong",IF(B31="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+      <c r="H31" s="10" t="n"/>
+      <c r="I31" s="10" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="10" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="11">
+        <f>IF(A31="","",COUNTIF('Referral Log'!$C$4:$C$400,A31))</f>
+        <v/>
+      </c>
+      <c r="N31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="11">
+        <f>IF(B32="","",IF(B32="Business broker","1 - Highest",IF(OR(B32="POS installer",B32="Bookkeeper / CPA"),"2 - High",IF(OR(B32="Liquor / food rep",B32="Consultant"),"3 - Strong",IF(B32="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="10" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="11">
+        <f>IF(A32="","",COUNTIF('Referral Log'!$C$4:$C$400,A32))</f>
+        <v/>
+      </c>
+      <c r="N32" s="10" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="11">
+        <f>IF(B33="","",IF(B33="Business broker","1 - Highest",IF(OR(B33="POS installer",B33="Bookkeeper / CPA"),"2 - High",IF(OR(B33="Liquor / food rep",B33="Consultant"),"3 - Strong",IF(B33="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="10" t="n"/>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="10" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="10" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="11">
+        <f>IF(A33="","",COUNTIF('Referral Log'!$C$4:$C$400,A33))</f>
+        <v/>
+      </c>
+      <c r="N33" s="10" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="11">
+        <f>IF(B34="","",IF(B34="Business broker","1 - Highest",IF(OR(B34="POS installer",B34="Bookkeeper / CPA"),"2 - High",IF(OR(B34="Liquor / food rep",B34="Consultant"),"3 - Strong",IF(B34="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
+      <c r="I34" s="10" t="n"/>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="10" t="n"/>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="11">
+        <f>IF(A34="","",COUNTIF('Referral Log'!$C$4:$C$400,A34))</f>
+        <v/>
+      </c>
+      <c r="N34" s="10" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="11">
+        <f>IF(B35="","",IF(B35="Business broker","1 - Highest",IF(OR(B35="POS installer",B35="Bookkeeper / CPA"),"2 - High",IF(OR(B35="Liquor / food rep",B35="Consultant"),"3 - Strong",IF(B35="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="n"/>
+      <c r="J35" s="12" t="n"/>
+      <c r="K35" s="10" t="n"/>
+      <c r="L35" s="12" t="n"/>
+      <c r="M35" s="11">
+        <f>IF(A35="","",COUNTIF('Referral Log'!$C$4:$C$400,A35))</f>
+        <v/>
+      </c>
+      <c r="N35" s="10" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="11">
+        <f>IF(B36="","",IF(B36="Business broker","1 - Highest",IF(OR(B36="POS installer",B36="Bookkeeper / CPA"),"2 - High",IF(OR(B36="Liquor / food rep",B36="Consultant"),"3 - Strong",IF(B36="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="10" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="10" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="11">
+        <f>IF(A36="","",COUNTIF('Referral Log'!$C$4:$C$400,A36))</f>
+        <v/>
+      </c>
+      <c r="N36" s="10" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="11">
+        <f>IF(B37="","",IF(B37="Business broker","1 - Highest",IF(OR(B37="POS installer",B37="Bookkeeper / CPA"),"2 - High",IF(OR(B37="Liquor / food rep",B37="Consultant"),"3 - Strong",IF(B37="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+      <c r="G37" s="10" t="n"/>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="10" t="n"/>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="10" t="n"/>
+      <c r="L37" s="12" t="n"/>
+      <c r="M37" s="11">
+        <f>IF(A37="","",COUNTIF('Referral Log'!$C$4:$C$400,A37))</f>
+        <v/>
+      </c>
+      <c r="N37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="11">
+        <f>IF(B38="","",IF(B38="Business broker","1 - Highest",IF(OR(B38="POS installer",B38="Bookkeeper / CPA"),"2 - High",IF(OR(B38="Liquor / food rep",B38="Consultant"),"3 - Strong",IF(B38="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="10" t="n"/>
+      <c r="F38" s="10" t="n"/>
+      <c r="G38" s="10" t="n"/>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="12" t="n"/>
+      <c r="K38" s="10" t="n"/>
+      <c r="L38" s="12" t="n"/>
+      <c r="M38" s="11">
+        <f>IF(A38="","",COUNTIF('Referral Log'!$C$4:$C$400,A38))</f>
+        <v/>
+      </c>
+      <c r="N38" s="10" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="11">
+        <f>IF(B39="","",IF(B39="Business broker","1 - Highest",IF(OR(B39="POS installer",B39="Bookkeeper / CPA"),"2 - High",IF(OR(B39="Liquor / food rep",B39="Consultant"),"3 - Strong",IF(B39="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="10" t="n"/>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="10" t="n"/>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="10" t="n"/>
+      <c r="J39" s="12" t="n"/>
+      <c r="K39" s="10" t="n"/>
+      <c r="L39" s="12" t="n"/>
+      <c r="M39" s="11">
+        <f>IF(A39="","",COUNTIF('Referral Log'!$C$4:$C$400,A39))</f>
+        <v/>
+      </c>
+      <c r="N39" s="10" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="11">
+        <f>IF(B40="","",IF(B40="Business broker","1 - Highest",IF(OR(B40="POS installer",B40="Bookkeeper / CPA"),"2 - High",IF(OR(B40="Liquor / food rep",B40="Consultant"),"3 - Strong",IF(B40="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="12" t="n"/>
+      <c r="K40" s="10" t="n"/>
+      <c r="L40" s="12" t="n"/>
+      <c r="M40" s="11">
+        <f>IF(A40="","",COUNTIF('Referral Log'!$C$4:$C$400,A40))</f>
+        <v/>
+      </c>
+      <c r="N40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="11">
+        <f>IF(B41="","",IF(B41="Business broker","1 - Highest",IF(OR(B41="POS installer",B41="Bookkeeper / CPA"),"2 - High",IF(OR(B41="Liquor / food rep",B41="Consultant"),"3 - Strong",IF(B41="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="n"/>
+      <c r="J41" s="12" t="n"/>
+      <c r="K41" s="10" t="n"/>
+      <c r="L41" s="12" t="n"/>
+      <c r="M41" s="11">
+        <f>IF(A41="","",COUNTIF('Referral Log'!$C$4:$C$400,A41))</f>
+        <v/>
+      </c>
+      <c r="N41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="n"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="11">
+        <f>IF(B42="","",IF(B42="Business broker","1 - Highest",IF(OR(B42="POS installer",B42="Bookkeeper / CPA"),"2 - High",IF(OR(B42="Liquor / food rep",B42="Consultant"),"3 - Strong",IF(B42="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="10" t="n"/>
+      <c r="J42" s="12" t="n"/>
+      <c r="K42" s="10" t="n"/>
+      <c r="L42" s="12" t="n"/>
+      <c r="M42" s="11">
+        <f>IF(A42="","",COUNTIF('Referral Log'!$C$4:$C$400,A42))</f>
+        <v/>
+      </c>
+      <c r="N42" s="10" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="11">
+        <f>IF(B43="","",IF(B43="Business broker","1 - Highest",IF(OR(B43="POS installer",B43="Bookkeeper / CPA"),"2 - High",IF(OR(B43="Liquor / food rep",B43="Consultant"),"3 - Strong",IF(B43="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="10" t="n"/>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="10" t="n"/>
+      <c r="J43" s="12" t="n"/>
+      <c r="K43" s="10" t="n"/>
+      <c r="L43" s="12" t="n"/>
+      <c r="M43" s="11">
+        <f>IF(A43="","",COUNTIF('Referral Log'!$C$4:$C$400,A43))</f>
+        <v/>
+      </c>
+      <c r="N43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="11">
+        <f>IF(B44="","",IF(B44="Business broker","1 - Highest",IF(OR(B44="POS installer",B44="Bookkeeper / CPA"),"2 - High",IF(OR(B44="Liquor / food rep",B44="Consultant"),"3 - Strong",IF(B44="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="10" t="n"/>
+      <c r="F44" s="10" t="n"/>
+      <c r="G44" s="10" t="n"/>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="12" t="n"/>
+      <c r="K44" s="10" t="n"/>
+      <c r="L44" s="12" t="n"/>
+      <c r="M44" s="11">
+        <f>IF(A44="","",COUNTIF('Referral Log'!$C$4:$C$400,A44))</f>
+        <v/>
+      </c>
+      <c r="N44" s="10" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="n"/>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="11">
+        <f>IF(B45="","",IF(B45="Business broker","1 - Highest",IF(OR(B45="POS installer",B45="Bookkeeper / CPA"),"2 - High",IF(OR(B45="Liquor / food rep",B45="Consultant"),"3 - Strong",IF(B45="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="10" t="n"/>
+      <c r="F45" s="10" t="n"/>
+      <c r="G45" s="10" t="n"/>
+      <c r="H45" s="10" t="n"/>
+      <c r="I45" s="10" t="n"/>
+      <c r="J45" s="12" t="n"/>
+      <c r="K45" s="10" t="n"/>
+      <c r="L45" s="12" t="n"/>
+      <c r="M45" s="11">
+        <f>IF(A45="","",COUNTIF('Referral Log'!$C$4:$C$400,A45))</f>
+        <v/>
+      </c>
+      <c r="N45" s="10" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="n"/>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="11">
+        <f>IF(B46="","",IF(B46="Business broker","1 - Highest",IF(OR(B46="POS installer",B46="Bookkeeper / CPA"),"2 - High",IF(OR(B46="Liquor / food rep",B46="Consultant"),"3 - Strong",IF(B46="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="n"/>
+      <c r="J46" s="12" t="n"/>
+      <c r="K46" s="10" t="n"/>
+      <c r="L46" s="12" t="n"/>
+      <c r="M46" s="11">
+        <f>IF(A46="","",COUNTIF('Referral Log'!$C$4:$C$400,A46))</f>
+        <v/>
+      </c>
+      <c r="N46" s="10" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="n"/>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="11">
+        <f>IF(B47="","",IF(B47="Business broker","1 - Highest",IF(OR(B47="POS installer",B47="Bookkeeper / CPA"),"2 - High",IF(OR(B47="Liquor / food rep",B47="Consultant"),"3 - Strong",IF(B47="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="10" t="n"/>
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="10" t="n"/>
+      <c r="J47" s="12" t="n"/>
+      <c r="K47" s="10" t="n"/>
+      <c r="L47" s="12" t="n"/>
+      <c r="M47" s="11">
+        <f>IF(A47="","",COUNTIF('Referral Log'!$C$4:$C$400,A47))</f>
+        <v/>
+      </c>
+      <c r="N47" s="10" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="n"/>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="11">
+        <f>IF(B48="","",IF(B48="Business broker","1 - Highest",IF(OR(B48="POS installer",B48="Bookkeeper / CPA"),"2 - High",IF(OR(B48="Liquor / food rep",B48="Consultant"),"3 - Strong",IF(B48="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="10" t="n"/>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="10" t="n"/>
+      <c r="J48" s="12" t="n"/>
+      <c r="K48" s="10" t="n"/>
+      <c r="L48" s="12" t="n"/>
+      <c r="M48" s="11">
+        <f>IF(A48="","",COUNTIF('Referral Log'!$C$4:$C$400,A48))</f>
+        <v/>
+      </c>
+      <c r="N48" s="10" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="n"/>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="11">
+        <f>IF(B49="","",IF(B49="Business broker","1 - Highest",IF(OR(B49="POS installer",B49="Bookkeeper / CPA"),"2 - High",IF(OR(B49="Liquor / food rep",B49="Consultant"),"3 - Strong",IF(B49="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="10" t="n"/>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="10" t="n"/>
+      <c r="J49" s="12" t="n"/>
+      <c r="K49" s="10" t="n"/>
+      <c r="L49" s="12" t="n"/>
+      <c r="M49" s="11">
+        <f>IF(A49="","",COUNTIF('Referral Log'!$C$4:$C$400,A49))</f>
+        <v/>
+      </c>
+      <c r="N49" s="10" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="n"/>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="11">
+        <f>IF(B50="","",IF(B50="Business broker","1 - Highest",IF(OR(B50="POS installer",B50="Bookkeeper / CPA"),"2 - High",IF(OR(B50="Liquor / food rep",B50="Consultant"),"3 - Strong",IF(B50="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="10" t="n"/>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
+      <c r="I50" s="10" t="n"/>
+      <c r="J50" s="12" t="n"/>
+      <c r="K50" s="10" t="n"/>
+      <c r="L50" s="12" t="n"/>
+      <c r="M50" s="11">
+        <f>IF(A50="","",COUNTIF('Referral Log'!$C$4:$C$400,A50))</f>
+        <v/>
+      </c>
+      <c r="N50" s="10" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="11">
+        <f>IF(B51="","",IF(B51="Business broker","1 - Highest",IF(OR(B51="POS installer",B51="Bookkeeper / CPA"),"2 - High",IF(OR(B51="Liquor / food rep",B51="Consultant"),"3 - Strong",IF(B51="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="10" t="n"/>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
+      <c r="I51" s="10" t="n"/>
+      <c r="J51" s="12" t="n"/>
+      <c r="K51" s="10" t="n"/>
+      <c r="L51" s="12" t="n"/>
+      <c r="M51" s="11">
+        <f>IF(A51="","",COUNTIF('Referral Log'!$C$4:$C$400,A51))</f>
+        <v/>
+      </c>
+      <c r="N51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="n"/>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="11">
+        <f>IF(B52="","",IF(B52="Business broker","1 - Highest",IF(OR(B52="POS installer",B52="Bookkeeper / CPA"),"2 - High",IF(OR(B52="Liquor / food rep",B52="Consultant"),"3 - Strong",IF(B52="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
+      <c r="I52" s="10" t="n"/>
+      <c r="J52" s="12" t="n"/>
+      <c r="K52" s="10" t="n"/>
+      <c r="L52" s="12" t="n"/>
+      <c r="M52" s="11">
+        <f>IF(A52="","",COUNTIF('Referral Log'!$C$4:$C$400,A52))</f>
+        <v/>
+      </c>
+      <c r="N52" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="n"/>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="11">
+        <f>IF(B53="","",IF(B53="Business broker","1 - Highest",IF(OR(B53="POS installer",B53="Bookkeeper / CPA"),"2 - High",IF(OR(B53="Liquor / food rep",B53="Consultant"),"3 - Strong",IF(B53="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="10" t="n"/>
+      <c r="F53" s="10" t="n"/>
+      <c r="G53" s="10" t="n"/>
+      <c r="H53" s="10" t="n"/>
+      <c r="I53" s="10" t="n"/>
+      <c r="J53" s="12" t="n"/>
+      <c r="K53" s="10" t="n"/>
+      <c r="L53" s="12" t="n"/>
+      <c r="M53" s="11">
+        <f>IF(A53="","",COUNTIF('Referral Log'!$C$4:$C$400,A53))</f>
+        <v/>
+      </c>
+      <c r="N53" s="10" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="n"/>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="11">
+        <f>IF(B54="","",IF(B54="Business broker","1 - Highest",IF(OR(B54="POS installer",B54="Bookkeeper / CPA"),"2 - High",IF(OR(B54="Liquor / food rep",B54="Consultant"),"3 - Strong",IF(B54="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="10" t="n"/>
+      <c r="F54" s="10" t="n"/>
+      <c r="G54" s="10" t="n"/>
+      <c r="H54" s="10" t="n"/>
+      <c r="I54" s="10" t="n"/>
+      <c r="J54" s="12" t="n"/>
+      <c r="K54" s="10" t="n"/>
+      <c r="L54" s="12" t="n"/>
+      <c r="M54" s="11">
+        <f>IF(A54="","",COUNTIF('Referral Log'!$C$4:$C$400,A54))</f>
+        <v/>
+      </c>
+      <c r="N54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="n"/>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="11">
+        <f>IF(B55="","",IF(B55="Business broker","1 - Highest",IF(OR(B55="POS installer",B55="Bookkeeper / CPA"),"2 - High",IF(OR(B55="Liquor / food rep",B55="Consultant"),"3 - Strong",IF(B55="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="10" t="n"/>
+      <c r="F55" s="10" t="n"/>
+      <c r="G55" s="10" t="n"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="10" t="n"/>
+      <c r="J55" s="12" t="n"/>
+      <c r="K55" s="10" t="n"/>
+      <c r="L55" s="12" t="n"/>
+      <c r="M55" s="11">
+        <f>IF(A55="","",COUNTIF('Referral Log'!$C$4:$C$400,A55))</f>
+        <v/>
+      </c>
+      <c r="N55" s="10" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="n"/>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="11">
+        <f>IF(B56="","",IF(B56="Business broker","1 - Highest",IF(OR(B56="POS installer",B56="Bookkeeper / CPA"),"2 - High",IF(OR(B56="Liquor / food rep",B56="Consultant"),"3 - Strong",IF(B56="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="10" t="n"/>
+      <c r="F56" s="10" t="n"/>
+      <c r="G56" s="10" t="n"/>
+      <c r="H56" s="10" t="n"/>
+      <c r="I56" s="10" t="n"/>
+      <c r="J56" s="12" t="n"/>
+      <c r="K56" s="10" t="n"/>
+      <c r="L56" s="12" t="n"/>
+      <c r="M56" s="11">
+        <f>IF(A56="","",COUNTIF('Referral Log'!$C$4:$C$400,A56))</f>
+        <v/>
+      </c>
+      <c r="N56" s="10" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="n"/>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="11">
+        <f>IF(B57="","",IF(B57="Business broker","1 - Highest",IF(OR(B57="POS installer",B57="Bookkeeper / CPA"),"2 - High",IF(OR(B57="Liquor / food rep",B57="Consultant"),"3 - Strong",IF(B57="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="10" t="n"/>
+      <c r="F57" s="10" t="n"/>
+      <c r="G57" s="10" t="n"/>
+      <c r="H57" s="10" t="n"/>
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="12" t="n"/>
+      <c r="K57" s="10" t="n"/>
+      <c r="L57" s="12" t="n"/>
+      <c r="M57" s="11">
+        <f>IF(A57="","",COUNTIF('Referral Log'!$C$4:$C$400,A57))</f>
+        <v/>
+      </c>
+      <c r="N57" s="10" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="n"/>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="11">
+        <f>IF(B58="","",IF(B58="Business broker","1 - Highest",IF(OR(B58="POS installer",B58="Bookkeeper / CPA"),"2 - High",IF(OR(B58="Liquor / food rep",B58="Consultant"),"3 - Strong",IF(B58="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="10" t="n"/>
+      <c r="F58" s="10" t="n"/>
+      <c r="G58" s="10" t="n"/>
+      <c r="H58" s="10" t="n"/>
+      <c r="I58" s="10" t="n"/>
+      <c r="J58" s="12" t="n"/>
+      <c r="K58" s="10" t="n"/>
+      <c r="L58" s="12" t="n"/>
+      <c r="M58" s="11">
+        <f>IF(A58="","",COUNTIF('Referral Log'!$C$4:$C$400,A58))</f>
+        <v/>
+      </c>
+      <c r="N58" s="10" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="n"/>
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="11">
+        <f>IF(B59="","",IF(B59="Business broker","1 - Highest",IF(OR(B59="POS installer",B59="Bookkeeper / CPA"),"2 - High",IF(OR(B59="Liquor / food rep",B59="Consultant"),"3 - Strong",IF(B59="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="10" t="n"/>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="10" t="n"/>
+      <c r="J59" s="12" t="n"/>
+      <c r="K59" s="10" t="n"/>
+      <c r="L59" s="12" t="n"/>
+      <c r="M59" s="11">
+        <f>IF(A59="","",COUNTIF('Referral Log'!$C$4:$C$400,A59))</f>
+        <v/>
+      </c>
+      <c r="N59" s="10" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="n"/>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="11">
+        <f>IF(B60="","",IF(B60="Business broker","1 - Highest",IF(OR(B60="POS installer",B60="Bookkeeper / CPA"),"2 - High",IF(OR(B60="Liquor / food rep",B60="Consultant"),"3 - Strong",IF(B60="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="10" t="n"/>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="10" t="n"/>
+      <c r="J60" s="12" t="n"/>
+      <c r="K60" s="10" t="n"/>
+      <c r="L60" s="12" t="n"/>
+      <c r="M60" s="11">
+        <f>IF(A60="","",COUNTIF('Referral Log'!$C$4:$C$400,A60))</f>
+        <v/>
+      </c>
+      <c r="N60" s="10" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="n"/>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="11">
+        <f>IF(B61="","",IF(B61="Business broker","1 - Highest",IF(OR(B61="POS installer",B61="Bookkeeper / CPA"),"2 - High",IF(OR(B61="Liquor / food rep",B61="Consultant"),"3 - Strong",IF(B61="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="10" t="n"/>
+      <c r="F61" s="10" t="n"/>
+      <c r="G61" s="10" t="n"/>
+      <c r="H61" s="10" t="n"/>
+      <c r="I61" s="10" t="n"/>
+      <c r="J61" s="12" t="n"/>
+      <c r="K61" s="10" t="n"/>
+      <c r="L61" s="12" t="n"/>
+      <c r="M61" s="11">
+        <f>IF(A61="","",COUNTIF('Referral Log'!$C$4:$C$400,A61))</f>
+        <v/>
+      </c>
+      <c r="N61" s="10" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="n"/>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="11">
+        <f>IF(B62="","",IF(B62="Business broker","1 - Highest",IF(OR(B62="POS installer",B62="Bookkeeper / CPA"),"2 - High",IF(OR(B62="Liquor / food rep",B62="Consultant"),"3 - Strong",IF(B62="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="10" t="n"/>
+      <c r="F62" s="10" t="n"/>
+      <c r="G62" s="10" t="n"/>
+      <c r="H62" s="10" t="n"/>
+      <c r="I62" s="10" t="n"/>
+      <c r="J62" s="12" t="n"/>
+      <c r="K62" s="10" t="n"/>
+      <c r="L62" s="12" t="n"/>
+      <c r="M62" s="11">
+        <f>IF(A62="","",COUNTIF('Referral Log'!$C$4:$C$400,A62))</f>
+        <v/>
+      </c>
+      <c r="N62" s="10" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="n"/>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="11">
+        <f>IF(B63="","",IF(B63="Business broker","1 - Highest",IF(OR(B63="POS installer",B63="Bookkeeper / CPA"),"2 - High",IF(OR(B63="Liquor / food rep",B63="Consultant"),"3 - Strong",IF(B63="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="10" t="n"/>
+      <c r="F63" s="10" t="n"/>
+      <c r="G63" s="10" t="n"/>
+      <c r="H63" s="10" t="n"/>
+      <c r="I63" s="10" t="n"/>
+      <c r="J63" s="12" t="n"/>
+      <c r="K63" s="10" t="n"/>
+      <c r="L63" s="12" t="n"/>
+      <c r="M63" s="11">
+        <f>IF(A63="","",COUNTIF('Referral Log'!$C$4:$C$400,A63))</f>
+        <v/>
+      </c>
+      <c r="N63" s="10" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="n"/>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="11">
+        <f>IF(B64="","",IF(B64="Business broker","1 - Highest",IF(OR(B64="POS installer",B64="Bookkeeper / CPA"),"2 - High",IF(OR(B64="Liquor / food rep",B64="Consultant"),"3 - Strong",IF(B64="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="10" t="n"/>
+      <c r="F64" s="10" t="n"/>
+      <c r="G64" s="10" t="n"/>
+      <c r="H64" s="10" t="n"/>
+      <c r="I64" s="10" t="n"/>
+      <c r="J64" s="12" t="n"/>
+      <c r="K64" s="10" t="n"/>
+      <c r="L64" s="12" t="n"/>
+      <c r="M64" s="11">
+        <f>IF(A64="","",COUNTIF('Referral Log'!$C$4:$C$400,A64))</f>
+        <v/>
+      </c>
+      <c r="N64" s="10" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="n"/>
+      <c r="B65" s="10" t="n"/>
+      <c r="C65" s="11">
+        <f>IF(B65="","",IF(B65="Business broker","1 - Highest",IF(OR(B65="POS installer",B65="Bookkeeper / CPA"),"2 - High",IF(OR(B65="Liquor / food rep",B65="Consultant"),"3 - Strong",IF(B65="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D65" s="10" t="n"/>
+      <c r="E65" s="10" t="n"/>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="10" t="n"/>
+      <c r="J65" s="12" t="n"/>
+      <c r="K65" s="10" t="n"/>
+      <c r="L65" s="12" t="n"/>
+      <c r="M65" s="11">
+        <f>IF(A65="","",COUNTIF('Referral Log'!$C$4:$C$400,A65))</f>
+        <v/>
+      </c>
+      <c r="N65" s="10" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="n"/>
+      <c r="B66" s="10" t="n"/>
+      <c r="C66" s="11">
+        <f>IF(B66="","",IF(B66="Business broker","1 - Highest",IF(OR(B66="POS installer",B66="Bookkeeper / CPA"),"2 - High",IF(OR(B66="Liquor / food rep",B66="Consultant"),"3 - Strong",IF(B66="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="10" t="n"/>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="10" t="n"/>
+      <c r="J66" s="12" t="n"/>
+      <c r="K66" s="10" t="n"/>
+      <c r="L66" s="12" t="n"/>
+      <c r="M66" s="11">
+        <f>IF(A66="","",COUNTIF('Referral Log'!$C$4:$C$400,A66))</f>
+        <v/>
+      </c>
+      <c r="N66" s="10" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="n"/>
+      <c r="B67" s="10" t="n"/>
+      <c r="C67" s="11">
+        <f>IF(B67="","",IF(B67="Business broker","1 - Highest",IF(OR(B67="POS installer",B67="Bookkeeper / CPA"),"2 - High",IF(OR(B67="Liquor / food rep",B67="Consultant"),"3 - Strong",IF(B67="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="10" t="n"/>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="10" t="n"/>
+      <c r="J67" s="12" t="n"/>
+      <c r="K67" s="10" t="n"/>
+      <c r="L67" s="12" t="n"/>
+      <c r="M67" s="11">
+        <f>IF(A67="","",COUNTIF('Referral Log'!$C$4:$C$400,A67))</f>
+        <v/>
+      </c>
+      <c r="N67" s="10" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="n"/>
+      <c r="B68" s="10" t="n"/>
+      <c r="C68" s="11">
+        <f>IF(B68="","",IF(B68="Business broker","1 - Highest",IF(OR(B68="POS installer",B68="Bookkeeper / CPA"),"2 - High",IF(OR(B68="Liquor / food rep",B68="Consultant"),"3 - Strong",IF(B68="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="10" t="n"/>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="10" t="n"/>
+      <c r="J68" s="12" t="n"/>
+      <c r="K68" s="10" t="n"/>
+      <c r="L68" s="12" t="n"/>
+      <c r="M68" s="11">
+        <f>IF(A68="","",COUNTIF('Referral Log'!$C$4:$C$400,A68))</f>
+        <v/>
+      </c>
+      <c r="N68" s="10" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="n"/>
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="11">
+        <f>IF(B69="","",IF(B69="Business broker","1 - Highest",IF(OR(B69="POS installer",B69="Bookkeeper / CPA"),"2 - High",IF(OR(B69="Liquor / food rep",B69="Consultant"),"3 - Strong",IF(B69="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="10" t="n"/>
+      <c r="F69" s="10" t="n"/>
+      <c r="G69" s="10" t="n"/>
+      <c r="H69" s="10" t="n"/>
+      <c r="I69" s="10" t="n"/>
+      <c r="J69" s="12" t="n"/>
+      <c r="K69" s="10" t="n"/>
+      <c r="L69" s="12" t="n"/>
+      <c r="M69" s="11">
+        <f>IF(A69="","",COUNTIF('Referral Log'!$C$4:$C$400,A69))</f>
+        <v/>
+      </c>
+      <c r="N69" s="10" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="n"/>
+      <c r="B70" s="10" t="n"/>
+      <c r="C70" s="11">
+        <f>IF(B70="","",IF(B70="Business broker","1 - Highest",IF(OR(B70="POS installer",B70="Bookkeeper / CPA"),"2 - High",IF(OR(B70="Liquor / food rep",B70="Consultant"),"3 - Strong",IF(B70="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="10" t="n"/>
+      <c r="F70" s="10" t="n"/>
+      <c r="G70" s="10" t="n"/>
+      <c r="H70" s="10" t="n"/>
+      <c r="I70" s="10" t="n"/>
+      <c r="J70" s="12" t="n"/>
+      <c r="K70" s="10" t="n"/>
+      <c r="L70" s="12" t="n"/>
+      <c r="M70" s="11">
+        <f>IF(A70="","",COUNTIF('Referral Log'!$C$4:$C$400,A70))</f>
+        <v/>
+      </c>
+      <c r="N70" s="10" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="n"/>
+      <c r="B71" s="10" t="n"/>
+      <c r="C71" s="11">
+        <f>IF(B71="","",IF(B71="Business broker","1 - Highest",IF(OR(B71="POS installer",B71="Bookkeeper / CPA"),"2 - High",IF(OR(B71="Liquor / food rep",B71="Consultant"),"3 - Strong",IF(B71="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="10" t="n"/>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="10" t="n"/>
+      <c r="J71" s="12" t="n"/>
+      <c r="K71" s="10" t="n"/>
+      <c r="L71" s="12" t="n"/>
+      <c r="M71" s="11">
+        <f>IF(A71="","",COUNTIF('Referral Log'!$C$4:$C$400,A71))</f>
+        <v/>
+      </c>
+      <c r="N71" s="10" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="n"/>
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="11">
+        <f>IF(B72="","",IF(B72="Business broker","1 - Highest",IF(OR(B72="POS installer",B72="Bookkeeper / CPA"),"2 - High",IF(OR(B72="Liquor / food rep",B72="Consultant"),"3 - Strong",IF(B72="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="10" t="n"/>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="10" t="n"/>
+      <c r="J72" s="12" t="n"/>
+      <c r="K72" s="10" t="n"/>
+      <c r="L72" s="12" t="n"/>
+      <c r="M72" s="11">
+        <f>IF(A72="","",COUNTIF('Referral Log'!$C$4:$C$400,A72))</f>
+        <v/>
+      </c>
+      <c r="N72" s="10" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="n"/>
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="11">
+        <f>IF(B73="","",IF(B73="Business broker","1 - Highest",IF(OR(B73="POS installer",B73="Bookkeeper / CPA"),"2 - High",IF(OR(B73="Liquor / food rep",B73="Consultant"),"3 - Strong",IF(B73="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D73" s="10" t="n"/>
+      <c r="E73" s="10" t="n"/>
+      <c r="F73" s="10" t="n"/>
+      <c r="G73" s="10" t="n"/>
+      <c r="H73" s="10" t="n"/>
+      <c r="I73" s="10" t="n"/>
+      <c r="J73" s="12" t="n"/>
+      <c r="K73" s="10" t="n"/>
+      <c r="L73" s="12" t="n"/>
+      <c r="M73" s="11">
+        <f>IF(A73="","",COUNTIF('Referral Log'!$C$4:$C$400,A73))</f>
+        <v/>
+      </c>
+      <c r="N73" s="10" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="n"/>
+      <c r="B74" s="10" t="n"/>
+      <c r="C74" s="11">
+        <f>IF(B74="","",IF(B74="Business broker","1 - Highest",IF(OR(B74="POS installer",B74="Bookkeeper / CPA"),"2 - High",IF(OR(B74="Liquor / food rep",B74="Consultant"),"3 - Strong",IF(B74="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D74" s="10" t="n"/>
+      <c r="E74" s="10" t="n"/>
+      <c r="F74" s="10" t="n"/>
+      <c r="G74" s="10" t="n"/>
+      <c r="H74" s="10" t="n"/>
+      <c r="I74" s="10" t="n"/>
+      <c r="J74" s="12" t="n"/>
+      <c r="K74" s="10" t="n"/>
+      <c r="L74" s="12" t="n"/>
+      <c r="M74" s="11">
+        <f>IF(A74="","",COUNTIF('Referral Log'!$C$4:$C$400,A74))</f>
+        <v/>
+      </c>
+      <c r="N74" s="10" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="n"/>
+      <c r="B75" s="10" t="n"/>
+      <c r="C75" s="11">
+        <f>IF(B75="","",IF(B75="Business broker","1 - Highest",IF(OR(B75="POS installer",B75="Bookkeeper / CPA"),"2 - High",IF(OR(B75="Liquor / food rep",B75="Consultant"),"3 - Strong",IF(B75="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="10" t="n"/>
+      <c r="F75" s="10" t="n"/>
+      <c r="G75" s="10" t="n"/>
+      <c r="H75" s="10" t="n"/>
+      <c r="I75" s="10" t="n"/>
+      <c r="J75" s="12" t="n"/>
+      <c r="K75" s="10" t="n"/>
+      <c r="L75" s="12" t="n"/>
+      <c r="M75" s="11">
+        <f>IF(A75="","",COUNTIF('Referral Log'!$C$4:$C$400,A75))</f>
+        <v/>
+      </c>
+      <c r="N75" s="10" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n"/>
+      <c r="B76" s="10" t="n"/>
+      <c r="C76" s="11">
+        <f>IF(B76="","",IF(B76="Business broker","1 - Highest",IF(OR(B76="POS installer",B76="Bookkeeper / CPA"),"2 - High",IF(OR(B76="Liquor / food rep",B76="Consultant"),"3 - Strong",IF(B76="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="10" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+      <c r="H76" s="10" t="n"/>
+      <c r="I76" s="10" t="n"/>
+      <c r="J76" s="12" t="n"/>
+      <c r="K76" s="10" t="n"/>
+      <c r="L76" s="12" t="n"/>
+      <c r="M76" s="11">
+        <f>IF(A76="","",COUNTIF('Referral Log'!$C$4:$C$400,A76))</f>
+        <v/>
+      </c>
+      <c r="N76" s="10" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="n"/>
+      <c r="B77" s="10" t="n"/>
+      <c r="C77" s="11">
+        <f>IF(B77="","",IF(B77="Business broker","1 - Highest",IF(OR(B77="POS installer",B77="Bookkeeper / CPA"),"2 - High",IF(OR(B77="Liquor / food rep",B77="Consultant"),"3 - Strong",IF(B77="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D77" s="10" t="n"/>
+      <c r="E77" s="10" t="n"/>
+      <c r="F77" s="10" t="n"/>
+      <c r="G77" s="10" t="n"/>
+      <c r="H77" s="10" t="n"/>
+      <c r="I77" s="10" t="n"/>
+      <c r="J77" s="12" t="n"/>
+      <c r="K77" s="10" t="n"/>
+      <c r="L77" s="12" t="n"/>
+      <c r="M77" s="11">
+        <f>IF(A77="","",COUNTIF('Referral Log'!$C$4:$C$400,A77))</f>
+        <v/>
+      </c>
+      <c r="N77" s="10" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="n"/>
+      <c r="B78" s="10" t="n"/>
+      <c r="C78" s="11">
+        <f>IF(B78="","",IF(B78="Business broker","1 - Highest",IF(OR(B78="POS installer",B78="Bookkeeper / CPA"),"2 - High",IF(OR(B78="Liquor / food rep",B78="Consultant"),"3 - Strong",IF(B78="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="10" t="n"/>
+      <c r="F78" s="10" t="n"/>
+      <c r="G78" s="10" t="n"/>
+      <c r="H78" s="10" t="n"/>
+      <c r="I78" s="10" t="n"/>
+      <c r="J78" s="12" t="n"/>
+      <c r="K78" s="10" t="n"/>
+      <c r="L78" s="12" t="n"/>
+      <c r="M78" s="11">
+        <f>IF(A78="","",COUNTIF('Referral Log'!$C$4:$C$400,A78))</f>
+        <v/>
+      </c>
+      <c r="N78" s="10" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="n"/>
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="11">
+        <f>IF(B79="","",IF(B79="Business broker","1 - Highest",IF(OR(B79="POS installer",B79="Bookkeeper / CPA"),"2 - High",IF(OR(B79="Liquor / food rep",B79="Consultant"),"3 - Strong",IF(B79="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+      <c r="H79" s="10" t="n"/>
+      <c r="I79" s="10" t="n"/>
+      <c r="J79" s="12" t="n"/>
+      <c r="K79" s="10" t="n"/>
+      <c r="L79" s="12" t="n"/>
+      <c r="M79" s="11">
+        <f>IF(A79="","",COUNTIF('Referral Log'!$C$4:$C$400,A79))</f>
+        <v/>
+      </c>
+      <c r="N79" s="10" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="n"/>
+      <c r="B80" s="10" t="n"/>
+      <c r="C80" s="11">
+        <f>IF(B80="","",IF(B80="Business broker","1 - Highest",IF(OR(B80="POS installer",B80="Bookkeeper / CPA"),"2 - High",IF(OR(B80="Liquor / food rep",B80="Consultant"),"3 - Strong",IF(B80="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D80" s="10" t="n"/>
+      <c r="E80" s="10" t="n"/>
+      <c r="F80" s="10" t="n"/>
+      <c r="G80" s="10" t="n"/>
+      <c r="H80" s="10" t="n"/>
+      <c r="I80" s="10" t="n"/>
+      <c r="J80" s="12" t="n"/>
+      <c r="K80" s="10" t="n"/>
+      <c r="L80" s="12" t="n"/>
+      <c r="M80" s="11">
+        <f>IF(A80="","",COUNTIF('Referral Log'!$C$4:$C$400,A80))</f>
+        <v/>
+      </c>
+      <c r="N80" s="10" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="n"/>
+      <c r="B81" s="10" t="n"/>
+      <c r="C81" s="11">
+        <f>IF(B81="","",IF(B81="Business broker","1 - Highest",IF(OR(B81="POS installer",B81="Bookkeeper / CPA"),"2 - High",IF(OR(B81="Liquor / food rep",B81="Consultant"),"3 - Strong",IF(B81="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D81" s="10" t="n"/>
+      <c r="E81" s="10" t="n"/>
+      <c r="F81" s="10" t="n"/>
+      <c r="G81" s="10" t="n"/>
+      <c r="H81" s="10" t="n"/>
+      <c r="I81" s="10" t="n"/>
+      <c r="J81" s="12" t="n"/>
+      <c r="K81" s="10" t="n"/>
+      <c r="L81" s="12" t="n"/>
+      <c r="M81" s="11">
+        <f>IF(A81="","",COUNTIF('Referral Log'!$C$4:$C$400,A81))</f>
+        <v/>
+      </c>
+      <c r="N81" s="10" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="n"/>
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="11">
+        <f>IF(B82="","",IF(B82="Business broker","1 - Highest",IF(OR(B82="POS installer",B82="Bookkeeper / CPA"),"2 - High",IF(OR(B82="Liquor / food rep",B82="Consultant"),"3 - Strong",IF(B82="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D82" s="10" t="n"/>
+      <c r="E82" s="10" t="n"/>
+      <c r="F82" s="10" t="n"/>
+      <c r="G82" s="10" t="n"/>
+      <c r="H82" s="10" t="n"/>
+      <c r="I82" s="10" t="n"/>
+      <c r="J82" s="12" t="n"/>
+      <c r="K82" s="10" t="n"/>
+      <c r="L82" s="12" t="n"/>
+      <c r="M82" s="11">
+        <f>IF(A82="","",COUNTIF('Referral Log'!$C$4:$C$400,A82))</f>
+        <v/>
+      </c>
+      <c r="N82" s="10" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="n"/>
+      <c r="B83" s="10" t="n"/>
+      <c r="C83" s="11">
+        <f>IF(B83="","",IF(B83="Business broker","1 - Highest",IF(OR(B83="POS installer",B83="Bookkeeper / CPA"),"2 - High",IF(OR(B83="Liquor / food rep",B83="Consultant"),"3 - Strong",IF(B83="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D83" s="10" t="n"/>
+      <c r="E83" s="10" t="n"/>
+      <c r="F83" s="10" t="n"/>
+      <c r="G83" s="10" t="n"/>
+      <c r="H83" s="10" t="n"/>
+      <c r="I83" s="10" t="n"/>
+      <c r="J83" s="12" t="n"/>
+      <c r="K83" s="10" t="n"/>
+      <c r="L83" s="12" t="n"/>
+      <c r="M83" s="11">
+        <f>IF(A83="","",COUNTIF('Referral Log'!$C$4:$C$400,A83))</f>
+        <v/>
+      </c>
+      <c r="N83" s="10" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="n"/>
+      <c r="B84" s="10" t="n"/>
+      <c r="C84" s="11">
+        <f>IF(B84="","",IF(B84="Business broker","1 - Highest",IF(OR(B84="POS installer",B84="Bookkeeper / CPA"),"2 - High",IF(OR(B84="Liquor / food rep",B84="Consultant"),"3 - Strong",IF(B84="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D84" s="10" t="n"/>
+      <c r="E84" s="10" t="n"/>
+      <c r="F84" s="10" t="n"/>
+      <c r="G84" s="10" t="n"/>
+      <c r="H84" s="10" t="n"/>
+      <c r="I84" s="10" t="n"/>
+      <c r="J84" s="12" t="n"/>
+      <c r="K84" s="10" t="n"/>
+      <c r="L84" s="12" t="n"/>
+      <c r="M84" s="11">
+        <f>IF(A84="","",COUNTIF('Referral Log'!$C$4:$C$400,A84))</f>
+        <v/>
+      </c>
+      <c r="N84" s="10" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="n"/>
+      <c r="B85" s="10" t="n"/>
+      <c r="C85" s="11">
+        <f>IF(B85="","",IF(B85="Business broker","1 - Highest",IF(OR(B85="POS installer",B85="Bookkeeper / CPA"),"2 - High",IF(OR(B85="Liquor / food rep",B85="Consultant"),"3 - Strong",IF(B85="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D85" s="10" t="n"/>
+      <c r="E85" s="10" t="n"/>
+      <c r="F85" s="10" t="n"/>
+      <c r="G85" s="10" t="n"/>
+      <c r="H85" s="10" t="n"/>
+      <c r="I85" s="10" t="n"/>
+      <c r="J85" s="12" t="n"/>
+      <c r="K85" s="10" t="n"/>
+      <c r="L85" s="12" t="n"/>
+      <c r="M85" s="11">
+        <f>IF(A85="","",COUNTIF('Referral Log'!$C$4:$C$400,A85))</f>
+        <v/>
+      </c>
+      <c r="N85" s="10" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="n"/>
+      <c r="B86" s="10" t="n"/>
+      <c r="C86" s="11">
+        <f>IF(B86="","",IF(B86="Business broker","1 - Highest",IF(OR(B86="POS installer",B86="Bookkeeper / CPA"),"2 - High",IF(OR(B86="Liquor / food rep",B86="Consultant"),"3 - Strong",IF(B86="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D86" s="10" t="n"/>
+      <c r="E86" s="10" t="n"/>
+      <c r="F86" s="10" t="n"/>
+      <c r="G86" s="10" t="n"/>
+      <c r="H86" s="10" t="n"/>
+      <c r="I86" s="10" t="n"/>
+      <c r="J86" s="12" t="n"/>
+      <c r="K86" s="10" t="n"/>
+      <c r="L86" s="12" t="n"/>
+      <c r="M86" s="11">
+        <f>IF(A86="","",COUNTIF('Referral Log'!$C$4:$C$400,A86))</f>
+        <v/>
+      </c>
+      <c r="N86" s="10" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="n"/>
+      <c r="B87" s="10" t="n"/>
+      <c r="C87" s="11">
+        <f>IF(B87="","",IF(B87="Business broker","1 - Highest",IF(OR(B87="POS installer",B87="Bookkeeper / CPA"),"2 - High",IF(OR(B87="Liquor / food rep",B87="Consultant"),"3 - Strong",IF(B87="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D87" s="10" t="n"/>
+      <c r="E87" s="10" t="n"/>
+      <c r="F87" s="10" t="n"/>
+      <c r="G87" s="10" t="n"/>
+      <c r="H87" s="10" t="n"/>
+      <c r="I87" s="10" t="n"/>
+      <c r="J87" s="12" t="n"/>
+      <c r="K87" s="10" t="n"/>
+      <c r="L87" s="12" t="n"/>
+      <c r="M87" s="11">
+        <f>IF(A87="","",COUNTIF('Referral Log'!$C$4:$C$400,A87))</f>
+        <v/>
+      </c>
+      <c r="N87" s="10" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="n"/>
+      <c r="B88" s="10" t="n"/>
+      <c r="C88" s="11">
+        <f>IF(B88="","",IF(B88="Business broker","1 - Highest",IF(OR(B88="POS installer",B88="Bookkeeper / CPA"),"2 - High",IF(OR(B88="Liquor / food rep",B88="Consultant"),"3 - Strong",IF(B88="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D88" s="10" t="n"/>
+      <c r="E88" s="10" t="n"/>
+      <c r="F88" s="10" t="n"/>
+      <c r="G88" s="10" t="n"/>
+      <c r="H88" s="10" t="n"/>
+      <c r="I88" s="10" t="n"/>
+      <c r="J88" s="12" t="n"/>
+      <c r="K88" s="10" t="n"/>
+      <c r="L88" s="12" t="n"/>
+      <c r="M88" s="11">
+        <f>IF(A88="","",COUNTIF('Referral Log'!$C$4:$C$400,A88))</f>
+        <v/>
+      </c>
+      <c r="N88" s="10" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="n"/>
+      <c r="B89" s="10" t="n"/>
+      <c r="C89" s="11">
+        <f>IF(B89="","",IF(B89="Business broker","1 - Highest",IF(OR(B89="POS installer",B89="Bookkeeper / CPA"),"2 - High",IF(OR(B89="Liquor / food rep",B89="Consultant"),"3 - Strong",IF(B89="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D89" s="10" t="n"/>
+      <c r="E89" s="10" t="n"/>
+      <c r="F89" s="10" t="n"/>
+      <c r="G89" s="10" t="n"/>
+      <c r="H89" s="10" t="n"/>
+      <c r="I89" s="10" t="n"/>
+      <c r="J89" s="12" t="n"/>
+      <c r="K89" s="10" t="n"/>
+      <c r="L89" s="12" t="n"/>
+      <c r="M89" s="11">
+        <f>IF(A89="","",COUNTIF('Referral Log'!$C$4:$C$400,A89))</f>
+        <v/>
+      </c>
+      <c r="N89" s="10" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="n"/>
+      <c r="B90" s="10" t="n"/>
+      <c r="C90" s="11">
+        <f>IF(B90="","",IF(B90="Business broker","1 - Highest",IF(OR(B90="POS installer",B90="Bookkeeper / CPA"),"2 - High",IF(OR(B90="Liquor / food rep",B90="Consultant"),"3 - Strong",IF(B90="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D90" s="10" t="n"/>
+      <c r="E90" s="10" t="n"/>
+      <c r="F90" s="10" t="n"/>
+      <c r="G90" s="10" t="n"/>
+      <c r="H90" s="10" t="n"/>
+      <c r="I90" s="10" t="n"/>
+      <c r="J90" s="12" t="n"/>
+      <c r="K90" s="10" t="n"/>
+      <c r="L90" s="12" t="n"/>
+      <c r="M90" s="11">
+        <f>IF(A90="","",COUNTIF('Referral Log'!$C$4:$C$400,A90))</f>
+        <v/>
+      </c>
+      <c r="N90" s="10" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="n"/>
+      <c r="B91" s="10" t="n"/>
+      <c r="C91" s="11">
+        <f>IF(B91="","",IF(B91="Business broker","1 - Highest",IF(OR(B91="POS installer",B91="Bookkeeper / CPA"),"2 - High",IF(OR(B91="Liquor / food rep",B91="Consultant"),"3 - Strong",IF(B91="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D91" s="10" t="n"/>
+      <c r="E91" s="10" t="n"/>
+      <c r="F91" s="10" t="n"/>
+      <c r="G91" s="10" t="n"/>
+      <c r="H91" s="10" t="n"/>
+      <c r="I91" s="10" t="n"/>
+      <c r="J91" s="12" t="n"/>
+      <c r="K91" s="10" t="n"/>
+      <c r="L91" s="12" t="n"/>
+      <c r="M91" s="11">
+        <f>IF(A91="","",COUNTIF('Referral Log'!$C$4:$C$400,A91))</f>
+        <v/>
+      </c>
+      <c r="N91" s="10" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="n"/>
+      <c r="B92" s="10" t="n"/>
+      <c r="C92" s="11">
+        <f>IF(B92="","",IF(B92="Business broker","1 - Highest",IF(OR(B92="POS installer",B92="Bookkeeper / CPA"),"2 - High",IF(OR(B92="Liquor / food rep",B92="Consultant"),"3 - Strong",IF(B92="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D92" s="10" t="n"/>
+      <c r="E92" s="10" t="n"/>
+      <c r="F92" s="10" t="n"/>
+      <c r="G92" s="10" t="n"/>
+      <c r="H92" s="10" t="n"/>
+      <c r="I92" s="10" t="n"/>
+      <c r="J92" s="12" t="n"/>
+      <c r="K92" s="10" t="n"/>
+      <c r="L92" s="12" t="n"/>
+      <c r="M92" s="11">
+        <f>IF(A92="","",COUNTIF('Referral Log'!$C$4:$C$400,A92))</f>
+        <v/>
+      </c>
+      <c r="N92" s="10" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="n"/>
+      <c r="B93" s="10" t="n"/>
+      <c r="C93" s="11">
+        <f>IF(B93="","",IF(B93="Business broker","1 - Highest",IF(OR(B93="POS installer",B93="Bookkeeper / CPA"),"2 - High",IF(OR(B93="Liquor / food rep",B93="Consultant"),"3 - Strong",IF(B93="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D93" s="10" t="n"/>
+      <c r="E93" s="10" t="n"/>
+      <c r="F93" s="10" t="n"/>
+      <c r="G93" s="10" t="n"/>
+      <c r="H93" s="10" t="n"/>
+      <c r="I93" s="10" t="n"/>
+      <c r="J93" s="12" t="n"/>
+      <c r="K93" s="10" t="n"/>
+      <c r="L93" s="12" t="n"/>
+      <c r="M93" s="11">
+        <f>IF(A93="","",COUNTIF('Referral Log'!$C$4:$C$400,A93))</f>
+        <v/>
+      </c>
+      <c r="N93" s="10" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="n"/>
+      <c r="B94" s="10" t="n"/>
+      <c r="C94" s="11">
+        <f>IF(B94="","",IF(B94="Business broker","1 - Highest",IF(OR(B94="POS installer",B94="Bookkeeper / CPA"),"2 - High",IF(OR(B94="Liquor / food rep",B94="Consultant"),"3 - Strong",IF(B94="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D94" s="10" t="n"/>
+      <c r="E94" s="10" t="n"/>
+      <c r="F94" s="10" t="n"/>
+      <c r="G94" s="10" t="n"/>
+      <c r="H94" s="10" t="n"/>
+      <c r="I94" s="10" t="n"/>
+      <c r="J94" s="12" t="n"/>
+      <c r="K94" s="10" t="n"/>
+      <c r="L94" s="12" t="n"/>
+      <c r="M94" s="11">
+        <f>IF(A94="","",COUNTIF('Referral Log'!$C$4:$C$400,A94))</f>
+        <v/>
+      </c>
+      <c r="N94" s="10" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="n"/>
+      <c r="B95" s="10" t="n"/>
+      <c r="C95" s="11">
+        <f>IF(B95="","",IF(B95="Business broker","1 - Highest",IF(OR(B95="POS installer",B95="Bookkeeper / CPA"),"2 - High",IF(OR(B95="Liquor / food rep",B95="Consultant"),"3 - Strong",IF(B95="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D95" s="10" t="n"/>
+      <c r="E95" s="10" t="n"/>
+      <c r="F95" s="10" t="n"/>
+      <c r="G95" s="10" t="n"/>
+      <c r="H95" s="10" t="n"/>
+      <c r="I95" s="10" t="n"/>
+      <c r="J95" s="12" t="n"/>
+      <c r="K95" s="10" t="n"/>
+      <c r="L95" s="12" t="n"/>
+      <c r="M95" s="11">
+        <f>IF(A95="","",COUNTIF('Referral Log'!$C$4:$C$400,A95))</f>
+        <v/>
+      </c>
+      <c r="N95" s="10" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="n"/>
+      <c r="B96" s="10" t="n"/>
+      <c r="C96" s="11">
+        <f>IF(B96="","",IF(B96="Business broker","1 - Highest",IF(OR(B96="POS installer",B96="Bookkeeper / CPA"),"2 - High",IF(OR(B96="Liquor / food rep",B96="Consultant"),"3 - Strong",IF(B96="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D96" s="10" t="n"/>
+      <c r="E96" s="10" t="n"/>
+      <c r="F96" s="10" t="n"/>
+      <c r="G96" s="10" t="n"/>
+      <c r="H96" s="10" t="n"/>
+      <c r="I96" s="10" t="n"/>
+      <c r="J96" s="12" t="n"/>
+      <c r="K96" s="10" t="n"/>
+      <c r="L96" s="12" t="n"/>
+      <c r="M96" s="11">
+        <f>IF(A96="","",COUNTIF('Referral Log'!$C$4:$C$400,A96))</f>
+        <v/>
+      </c>
+      <c r="N96" s="10" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="n"/>
+      <c r="B97" s="10" t="n"/>
+      <c r="C97" s="11">
+        <f>IF(B97="","",IF(B97="Business broker","1 - Highest",IF(OR(B97="POS installer",B97="Bookkeeper / CPA"),"2 - High",IF(OR(B97="Liquor / food rep",B97="Consultant"),"3 - Strong",IF(B97="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D97" s="10" t="n"/>
+      <c r="E97" s="10" t="n"/>
+      <c r="F97" s="10" t="n"/>
+      <c r="G97" s="10" t="n"/>
+      <c r="H97" s="10" t="n"/>
+      <c r="I97" s="10" t="n"/>
+      <c r="J97" s="12" t="n"/>
+      <c r="K97" s="10" t="n"/>
+      <c r="L97" s="12" t="n"/>
+      <c r="M97" s="11">
+        <f>IF(A97="","",COUNTIF('Referral Log'!$C$4:$C$400,A97))</f>
+        <v/>
+      </c>
+      <c r="N97" s="10" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="n"/>
+      <c r="B98" s="10" t="n"/>
+      <c r="C98" s="11">
+        <f>IF(B98="","",IF(B98="Business broker","1 - Highest",IF(OR(B98="POS installer",B98="Bookkeeper / CPA"),"2 - High",IF(OR(B98="Liquor / food rep",B98="Consultant"),"3 - Strong",IF(B98="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D98" s="10" t="n"/>
+      <c r="E98" s="10" t="n"/>
+      <c r="F98" s="10" t="n"/>
+      <c r="G98" s="10" t="n"/>
+      <c r="H98" s="10" t="n"/>
+      <c r="I98" s="10" t="n"/>
+      <c r="J98" s="12" t="n"/>
+      <c r="K98" s="10" t="n"/>
+      <c r="L98" s="12" t="n"/>
+      <c r="M98" s="11">
+        <f>IF(A98="","",COUNTIF('Referral Log'!$C$4:$C$400,A98))</f>
+        <v/>
+      </c>
+      <c r="N98" s="10" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="n"/>
+      <c r="B99" s="10" t="n"/>
+      <c r="C99" s="11">
+        <f>IF(B99="","",IF(B99="Business broker","1 - Highest",IF(OR(B99="POS installer",B99="Bookkeeper / CPA"),"2 - High",IF(OR(B99="Liquor / food rep",B99="Consultant"),"3 - Strong",IF(B99="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D99" s="10" t="n"/>
+      <c r="E99" s="10" t="n"/>
+      <c r="F99" s="10" t="n"/>
+      <c r="G99" s="10" t="n"/>
+      <c r="H99" s="10" t="n"/>
+      <c r="I99" s="10" t="n"/>
+      <c r="J99" s="12" t="n"/>
+      <c r="K99" s="10" t="n"/>
+      <c r="L99" s="12" t="n"/>
+      <c r="M99" s="11">
+        <f>IF(A99="","",COUNTIF('Referral Log'!$C$4:$C$400,A99))</f>
+        <v/>
+      </c>
+      <c r="N99" s="10" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="n"/>
+      <c r="B100" s="10" t="n"/>
+      <c r="C100" s="11">
+        <f>IF(B100="","",IF(B100="Business broker","1 - Highest",IF(OR(B100="POS installer",B100="Bookkeeper / CPA"),"2 - High",IF(OR(B100="Liquor / food rep",B100="Consultant"),"3 - Strong",IF(B100="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D100" s="10" t="n"/>
+      <c r="E100" s="10" t="n"/>
+      <c r="F100" s="10" t="n"/>
+      <c r="G100" s="10" t="n"/>
+      <c r="H100" s="10" t="n"/>
+      <c r="I100" s="10" t="n"/>
+      <c r="J100" s="12" t="n"/>
+      <c r="K100" s="10" t="n"/>
+      <c r="L100" s="12" t="n"/>
+      <c r="M100" s="11">
+        <f>IF(A100="","",COUNTIF('Referral Log'!$C$4:$C$400,A100))</f>
+        <v/>
+      </c>
+      <c r="N100" s="10" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="n"/>
+      <c r="B101" s="10" t="n"/>
+      <c r="C101" s="11">
+        <f>IF(B101="","",IF(B101="Business broker","1 - Highest",IF(OR(B101="POS installer",B101="Bookkeeper / CPA"),"2 - High",IF(OR(B101="Liquor / food rep",B101="Consultant"),"3 - Strong",IF(B101="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D101" s="10" t="n"/>
+      <c r="E101" s="10" t="n"/>
+      <c r="F101" s="10" t="n"/>
+      <c r="G101" s="10" t="n"/>
+      <c r="H101" s="10" t="n"/>
+      <c r="I101" s="10" t="n"/>
+      <c r="J101" s="12" t="n"/>
+      <c r="K101" s="10" t="n"/>
+      <c r="L101" s="12" t="n"/>
+      <c r="M101" s="11">
+        <f>IF(A101="","",COUNTIF('Referral Log'!$C$4:$C$400,A101))</f>
+        <v/>
+      </c>
+      <c r="N101" s="10" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="n"/>
+      <c r="B102" s="10" t="n"/>
+      <c r="C102" s="11">
+        <f>IF(B102="","",IF(B102="Business broker","1 - Highest",IF(OR(B102="POS installer",B102="Bookkeeper / CPA"),"2 - High",IF(OR(B102="Liquor / food rep",B102="Consultant"),"3 - Strong",IF(B102="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D102" s="10" t="n"/>
+      <c r="E102" s="10" t="n"/>
+      <c r="F102" s="10" t="n"/>
+      <c r="G102" s="10" t="n"/>
+      <c r="H102" s="10" t="n"/>
+      <c r="I102" s="10" t="n"/>
+      <c r="J102" s="12" t="n"/>
+      <c r="K102" s="10" t="n"/>
+      <c r="L102" s="12" t="n"/>
+      <c r="M102" s="11">
+        <f>IF(A102="","",COUNTIF('Referral Log'!$C$4:$C$400,A102))</f>
+        <v/>
+      </c>
+      <c r="N102" s="10" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="n"/>
+      <c r="B103" s="10" t="n"/>
+      <c r="C103" s="11">
+        <f>IF(B103="","",IF(B103="Business broker","1 - Highest",IF(OR(B103="POS installer",B103="Bookkeeper / CPA"),"2 - High",IF(OR(B103="Liquor / food rep",B103="Consultant"),"3 - Strong",IF(B103="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D103" s="10" t="n"/>
+      <c r="E103" s="10" t="n"/>
+      <c r="F103" s="10" t="n"/>
+      <c r="G103" s="10" t="n"/>
+      <c r="H103" s="10" t="n"/>
+      <c r="I103" s="10" t="n"/>
+      <c r="J103" s="12" t="n"/>
+      <c r="K103" s="10" t="n"/>
+      <c r="L103" s="12" t="n"/>
+      <c r="M103" s="11">
+        <f>IF(A103="","",COUNTIF('Referral Log'!$C$4:$C$400,A103))</f>
+        <v/>
+      </c>
+      <c r="N103" s="10" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="n"/>
+      <c r="B104" s="10" t="n"/>
+      <c r="C104" s="11">
+        <f>IF(B104="","",IF(B104="Business broker","1 - Highest",IF(OR(B104="POS installer",B104="Bookkeeper / CPA"),"2 - High",IF(OR(B104="Liquor / food rep",B104="Consultant"),"3 - Strong",IF(B104="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D104" s="10" t="n"/>
+      <c r="E104" s="10" t="n"/>
+      <c r="F104" s="10" t="n"/>
+      <c r="G104" s="10" t="n"/>
+      <c r="H104" s="10" t="n"/>
+      <c r="I104" s="10" t="n"/>
+      <c r="J104" s="12" t="n"/>
+      <c r="K104" s="10" t="n"/>
+      <c r="L104" s="12" t="n"/>
+      <c r="M104" s="11">
+        <f>IF(A104="","",COUNTIF('Referral Log'!$C$4:$C$400,A104))</f>
+        <v/>
+      </c>
+      <c r="N104" s="10" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="n"/>
+      <c r="B105" s="10" t="n"/>
+      <c r="C105" s="11">
+        <f>IF(B105="","",IF(B105="Business broker","1 - Highest",IF(OR(B105="POS installer",B105="Bookkeeper / CPA"),"2 - High",IF(OR(B105="Liquor / food rep",B105="Consultant"),"3 - Strong",IF(B105="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D105" s="10" t="n"/>
+      <c r="E105" s="10" t="n"/>
+      <c r="F105" s="10" t="n"/>
+      <c r="G105" s="10" t="n"/>
+      <c r="H105" s="10" t="n"/>
+      <c r="I105" s="10" t="n"/>
+      <c r="J105" s="12" t="n"/>
+      <c r="K105" s="10" t="n"/>
+      <c r="L105" s="12" t="n"/>
+      <c r="M105" s="11">
+        <f>IF(A105="","",COUNTIF('Referral Log'!$C$4:$C$400,A105))</f>
+        <v/>
+      </c>
+      <c r="N105" s="10" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="n"/>
+      <c r="B106" s="10" t="n"/>
+      <c r="C106" s="11">
+        <f>IF(B106="","",IF(B106="Business broker","1 - Highest",IF(OR(B106="POS installer",B106="Bookkeeper / CPA"),"2 - High",IF(OR(B106="Liquor / food rep",B106="Consultant"),"3 - Strong",IF(B106="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D106" s="10" t="n"/>
+      <c r="E106" s="10" t="n"/>
+      <c r="F106" s="10" t="n"/>
+      <c r="G106" s="10" t="n"/>
+      <c r="H106" s="10" t="n"/>
+      <c r="I106" s="10" t="n"/>
+      <c r="J106" s="12" t="n"/>
+      <c r="K106" s="10" t="n"/>
+      <c r="L106" s="12" t="n"/>
+      <c r="M106" s="11">
+        <f>IF(A106="","",COUNTIF('Referral Log'!$C$4:$C$400,A106))</f>
+        <v/>
+      </c>
+      <c r="N106" s="10" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="n"/>
+      <c r="B107" s="10" t="n"/>
+      <c r="C107" s="11">
+        <f>IF(B107="","",IF(B107="Business broker","1 - Highest",IF(OR(B107="POS installer",B107="Bookkeeper / CPA"),"2 - High",IF(OR(B107="Liquor / food rep",B107="Consultant"),"3 - Strong",IF(B107="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D107" s="10" t="n"/>
+      <c r="E107" s="10" t="n"/>
+      <c r="F107" s="10" t="n"/>
+      <c r="G107" s="10" t="n"/>
+      <c r="H107" s="10" t="n"/>
+      <c r="I107" s="10" t="n"/>
+      <c r="J107" s="12" t="n"/>
+      <c r="K107" s="10" t="n"/>
+      <c r="L107" s="12" t="n"/>
+      <c r="M107" s="11">
+        <f>IF(A107="","",COUNTIF('Referral Log'!$C$4:$C$400,A107))</f>
+        <v/>
+      </c>
+      <c r="N107" s="10" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="n"/>
+      <c r="B108" s="10" t="n"/>
+      <c r="C108" s="11">
+        <f>IF(B108="","",IF(B108="Business broker","1 - Highest",IF(OR(B108="POS installer",B108="Bookkeeper / CPA"),"2 - High",IF(OR(B108="Liquor / food rep",B108="Consultant"),"3 - Strong",IF(B108="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D108" s="10" t="n"/>
+      <c r="E108" s="10" t="n"/>
+      <c r="F108" s="10" t="n"/>
+      <c r="G108" s="10" t="n"/>
+      <c r="H108" s="10" t="n"/>
+      <c r="I108" s="10" t="n"/>
+      <c r="J108" s="12" t="n"/>
+      <c r="K108" s="10" t="n"/>
+      <c r="L108" s="12" t="n"/>
+      <c r="M108" s="11">
+        <f>IF(A108="","",COUNTIF('Referral Log'!$C$4:$C$400,A108))</f>
+        <v/>
+      </c>
+      <c r="N108" s="10" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="n"/>
+      <c r="B109" s="10" t="n"/>
+      <c r="C109" s="11">
+        <f>IF(B109="","",IF(B109="Business broker","1 - Highest",IF(OR(B109="POS installer",B109="Bookkeeper / CPA"),"2 - High",IF(OR(B109="Liquor / food rep",B109="Consultant"),"3 - Strong",IF(B109="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D109" s="10" t="n"/>
+      <c r="E109" s="10" t="n"/>
+      <c r="F109" s="10" t="n"/>
+      <c r="G109" s="10" t="n"/>
+      <c r="H109" s="10" t="n"/>
+      <c r="I109" s="10" t="n"/>
+      <c r="J109" s="12" t="n"/>
+      <c r="K109" s="10" t="n"/>
+      <c r="L109" s="12" t="n"/>
+      <c r="M109" s="11">
+        <f>IF(A109="","",COUNTIF('Referral Log'!$C$4:$C$400,A109))</f>
+        <v/>
+      </c>
+      <c r="N109" s="10" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="n"/>
+      <c r="B110" s="10" t="n"/>
+      <c r="C110" s="11">
+        <f>IF(B110="","",IF(B110="Business broker","1 - Highest",IF(OR(B110="POS installer",B110="Bookkeeper / CPA"),"2 - High",IF(OR(B110="Liquor / food rep",B110="Consultant"),"3 - Strong",IF(B110="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D110" s="10" t="n"/>
+      <c r="E110" s="10" t="n"/>
+      <c r="F110" s="10" t="n"/>
+      <c r="G110" s="10" t="n"/>
+      <c r="H110" s="10" t="n"/>
+      <c r="I110" s="10" t="n"/>
+      <c r="J110" s="12" t="n"/>
+      <c r="K110" s="10" t="n"/>
+      <c r="L110" s="12" t="n"/>
+      <c r="M110" s="11">
+        <f>IF(A110="","",COUNTIF('Referral Log'!$C$4:$C$400,A110))</f>
+        <v/>
+      </c>
+      <c r="N110" s="10" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="10" t="n"/>
+      <c r="B111" s="10" t="n"/>
+      <c r="C111" s="11">
+        <f>IF(B111="","",IF(B111="Business broker","1 - Highest",IF(OR(B111="POS installer",B111="Bookkeeper / CPA"),"2 - High",IF(OR(B111="Liquor / food rep",B111="Consultant"),"3 - Strong",IF(B111="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D111" s="10" t="n"/>
+      <c r="E111" s="10" t="n"/>
+      <c r="F111" s="10" t="n"/>
+      <c r="G111" s="10" t="n"/>
+      <c r="H111" s="10" t="n"/>
+      <c r="I111" s="10" t="n"/>
+      <c r="J111" s="12" t="n"/>
+      <c r="K111" s="10" t="n"/>
+      <c r="L111" s="12" t="n"/>
+      <c r="M111" s="11">
+        <f>IF(A111="","",COUNTIF('Referral Log'!$C$4:$C$400,A111))</f>
+        <v/>
+      </c>
+      <c r="N111" s="10" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="10" t="n"/>
+      <c r="B112" s="10" t="n"/>
+      <c r="C112" s="11">
+        <f>IF(B112="","",IF(B112="Business broker","1 - Highest",IF(OR(B112="POS installer",B112="Bookkeeper / CPA"),"2 - High",IF(OR(B112="Liquor / food rep",B112="Consultant"),"3 - Strong",IF(B112="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D112" s="10" t="n"/>
+      <c r="E112" s="10" t="n"/>
+      <c r="F112" s="10" t="n"/>
+      <c r="G112" s="10" t="n"/>
+      <c r="H112" s="10" t="n"/>
+      <c r="I112" s="10" t="n"/>
+      <c r="J112" s="12" t="n"/>
+      <c r="K112" s="10" t="n"/>
+      <c r="L112" s="12" t="n"/>
+      <c r="M112" s="11">
+        <f>IF(A112="","",COUNTIF('Referral Log'!$C$4:$C$400,A112))</f>
+        <v/>
+      </c>
+      <c r="N112" s="10" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="10" t="n"/>
+      <c r="B113" s="10" t="n"/>
+      <c r="C113" s="11">
+        <f>IF(B113="","",IF(B113="Business broker","1 - Highest",IF(OR(B113="POS installer",B113="Bookkeeper / CPA"),"2 - High",IF(OR(B113="Liquor / food rep",B113="Consultant"),"3 - Strong",IF(B113="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D113" s="10" t="n"/>
+      <c r="E113" s="10" t="n"/>
+      <c r="F113" s="10" t="n"/>
+      <c r="G113" s="10" t="n"/>
+      <c r="H113" s="10" t="n"/>
+      <c r="I113" s="10" t="n"/>
+      <c r="J113" s="12" t="n"/>
+      <c r="K113" s="10" t="n"/>
+      <c r="L113" s="12" t="n"/>
+      <c r="M113" s="11">
+        <f>IF(A113="","",COUNTIF('Referral Log'!$C$4:$C$400,A113))</f>
+        <v/>
+      </c>
+      <c r="N113" s="10" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="n"/>
+      <c r="B114" s="10" t="n"/>
+      <c r="C114" s="11">
+        <f>IF(B114="","",IF(B114="Business broker","1 - Highest",IF(OR(B114="POS installer",B114="Bookkeeper / CPA"),"2 - High",IF(OR(B114="Liquor / food rep",B114="Consultant"),"3 - Strong",IF(B114="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D114" s="10" t="n"/>
+      <c r="E114" s="10" t="n"/>
+      <c r="F114" s="10" t="n"/>
+      <c r="G114" s="10" t="n"/>
+      <c r="H114" s="10" t="n"/>
+      <c r="I114" s="10" t="n"/>
+      <c r="J114" s="12" t="n"/>
+      <c r="K114" s="10" t="n"/>
+      <c r="L114" s="12" t="n"/>
+      <c r="M114" s="11">
+        <f>IF(A114="","",COUNTIF('Referral Log'!$C$4:$C$400,A114))</f>
+        <v/>
+      </c>
+      <c r="N114" s="10" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="n"/>
+      <c r="B115" s="10" t="n"/>
+      <c r="C115" s="11">
+        <f>IF(B115="","",IF(B115="Business broker","1 - Highest",IF(OR(B115="POS installer",B115="Bookkeeper / CPA"),"2 - High",IF(OR(B115="Liquor / food rep",B115="Consultant"),"3 - Strong",IF(B115="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D115" s="10" t="n"/>
+      <c r="E115" s="10" t="n"/>
+      <c r="F115" s="10" t="n"/>
+      <c r="G115" s="10" t="n"/>
+      <c r="H115" s="10" t="n"/>
+      <c r="I115" s="10" t="n"/>
+      <c r="J115" s="12" t="n"/>
+      <c r="K115" s="10" t="n"/>
+      <c r="L115" s="12" t="n"/>
+      <c r="M115" s="11">
+        <f>IF(A115="","",COUNTIF('Referral Log'!$C$4:$C$400,A115))</f>
+        <v/>
+      </c>
+      <c r="N115" s="10" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="n"/>
+      <c r="B116" s="10" t="n"/>
+      <c r="C116" s="11">
+        <f>IF(B116="","",IF(B116="Business broker","1 - Highest",IF(OR(B116="POS installer",B116="Bookkeeper / CPA"),"2 - High",IF(OR(B116="Liquor / food rep",B116="Consultant"),"3 - Strong",IF(B116="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D116" s="10" t="n"/>
+      <c r="E116" s="10" t="n"/>
+      <c r="F116" s="10" t="n"/>
+      <c r="G116" s="10" t="n"/>
+      <c r="H116" s="10" t="n"/>
+      <c r="I116" s="10" t="n"/>
+      <c r="J116" s="12" t="n"/>
+      <c r="K116" s="10" t="n"/>
+      <c r="L116" s="12" t="n"/>
+      <c r="M116" s="11">
+        <f>IF(A116="","",COUNTIF('Referral Log'!$C$4:$C$400,A116))</f>
+        <v/>
+      </c>
+      <c r="N116" s="10" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="n"/>
+      <c r="B117" s="10" t="n"/>
+      <c r="C117" s="11">
+        <f>IF(B117="","",IF(B117="Business broker","1 - Highest",IF(OR(B117="POS installer",B117="Bookkeeper / CPA"),"2 - High",IF(OR(B117="Liquor / food rep",B117="Consultant"),"3 - Strong",IF(B117="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D117" s="10" t="n"/>
+      <c r="E117" s="10" t="n"/>
+      <c r="F117" s="10" t="n"/>
+      <c r="G117" s="10" t="n"/>
+      <c r="H117" s="10" t="n"/>
+      <c r="I117" s="10" t="n"/>
+      <c r="J117" s="12" t="n"/>
+      <c r="K117" s="10" t="n"/>
+      <c r="L117" s="12" t="n"/>
+      <c r="M117" s="11">
+        <f>IF(A117="","",COUNTIF('Referral Log'!$C$4:$C$400,A117))</f>
+        <v/>
+      </c>
+      <c r="N117" s="10" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="n"/>
+      <c r="B118" s="10" t="n"/>
+      <c r="C118" s="11">
+        <f>IF(B118="","",IF(B118="Business broker","1 - Highest",IF(OR(B118="POS installer",B118="Bookkeeper / CPA"),"2 - High",IF(OR(B118="Liquor / food rep",B118="Consultant"),"3 - Strong",IF(B118="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D118" s="10" t="n"/>
+      <c r="E118" s="10" t="n"/>
+      <c r="F118" s="10" t="n"/>
+      <c r="G118" s="10" t="n"/>
+      <c r="H118" s="10" t="n"/>
+      <c r="I118" s="10" t="n"/>
+      <c r="J118" s="12" t="n"/>
+      <c r="K118" s="10" t="n"/>
+      <c r="L118" s="12" t="n"/>
+      <c r="M118" s="11">
+        <f>IF(A118="","",COUNTIF('Referral Log'!$C$4:$C$400,A118))</f>
+        <v/>
+      </c>
+      <c r="N118" s="10" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="n"/>
+      <c r="B119" s="10" t="n"/>
+      <c r="C119" s="11">
+        <f>IF(B119="","",IF(B119="Business broker","1 - Highest",IF(OR(B119="POS installer",B119="Bookkeeper / CPA"),"2 - High",IF(OR(B119="Liquor / food rep",B119="Consultant"),"3 - Strong",IF(B119="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D119" s="10" t="n"/>
+      <c r="E119" s="10" t="n"/>
+      <c r="F119" s="10" t="n"/>
+      <c r="G119" s="10" t="n"/>
+      <c r="H119" s="10" t="n"/>
+      <c r="I119" s="10" t="n"/>
+      <c r="J119" s="12" t="n"/>
+      <c r="K119" s="10" t="n"/>
+      <c r="L119" s="12" t="n"/>
+      <c r="M119" s="11">
+        <f>IF(A119="","",COUNTIF('Referral Log'!$C$4:$C$400,A119))</f>
+        <v/>
+      </c>
+      <c r="N119" s="10" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="n"/>
+      <c r="B120" s="10" t="n"/>
+      <c r="C120" s="11">
+        <f>IF(B120="","",IF(B120="Business broker","1 - Highest",IF(OR(B120="POS installer",B120="Bookkeeper / CPA"),"2 - High",IF(OR(B120="Liquor / food rep",B120="Consultant"),"3 - Strong",IF(B120="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D120" s="10" t="n"/>
+      <c r="E120" s="10" t="n"/>
+      <c r="F120" s="10" t="n"/>
+      <c r="G120" s="10" t="n"/>
+      <c r="H120" s="10" t="n"/>
+      <c r="I120" s="10" t="n"/>
+      <c r="J120" s="12" t="n"/>
+      <c r="K120" s="10" t="n"/>
+      <c r="L120" s="12" t="n"/>
+      <c r="M120" s="11">
+        <f>IF(A120="","",COUNTIF('Referral Log'!$C$4:$C$400,A120))</f>
+        <v/>
+      </c>
+      <c r="N120" s="10" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="n"/>
+      <c r="B121" s="10" t="n"/>
+      <c r="C121" s="11">
+        <f>IF(B121="","",IF(B121="Business broker","1 - Highest",IF(OR(B121="POS installer",B121="Bookkeeper / CPA"),"2 - High",IF(OR(B121="Liquor / food rep",B121="Consultant"),"3 - Strong",IF(B121="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D121" s="10" t="n"/>
+      <c r="E121" s="10" t="n"/>
+      <c r="F121" s="10" t="n"/>
+      <c r="G121" s="10" t="n"/>
+      <c r="H121" s="10" t="n"/>
+      <c r="I121" s="10" t="n"/>
+      <c r="J121" s="12" t="n"/>
+      <c r="K121" s="10" t="n"/>
+      <c r="L121" s="12" t="n"/>
+      <c r="M121" s="11">
+        <f>IF(A121="","",COUNTIF('Referral Log'!$C$4:$C$400,A121))</f>
+        <v/>
+      </c>
+      <c r="N121" s="10" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="n"/>
+      <c r="B122" s="10" t="n"/>
+      <c r="C122" s="11">
+        <f>IF(B122="","",IF(B122="Business broker","1 - Highest",IF(OR(B122="POS installer",B122="Bookkeeper / CPA"),"2 - High",IF(OR(B122="Liquor / food rep",B122="Consultant"),"3 - Strong",IF(B122="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D122" s="10" t="n"/>
+      <c r="E122" s="10" t="n"/>
+      <c r="F122" s="10" t="n"/>
+      <c r="G122" s="10" t="n"/>
+      <c r="H122" s="10" t="n"/>
+      <c r="I122" s="10" t="n"/>
+      <c r="J122" s="12" t="n"/>
+      <c r="K122" s="10" t="n"/>
+      <c r="L122" s="12" t="n"/>
+      <c r="M122" s="11">
+        <f>IF(A122="","",COUNTIF('Referral Log'!$C$4:$C$400,A122))</f>
+        <v/>
+      </c>
+      <c r="N122" s="10" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="n"/>
+      <c r="B123" s="10" t="n"/>
+      <c r="C123" s="11">
+        <f>IF(B123="","",IF(B123="Business broker","1 - Highest",IF(OR(B123="POS installer",B123="Bookkeeper / CPA"),"2 - High",IF(OR(B123="Liquor / food rep",B123="Consultant"),"3 - Strong",IF(B123="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D123" s="10" t="n"/>
+      <c r="E123" s="10" t="n"/>
+      <c r="F123" s="10" t="n"/>
+      <c r="G123" s="10" t="n"/>
+      <c r="H123" s="10" t="n"/>
+      <c r="I123" s="10" t="n"/>
+      <c r="J123" s="12" t="n"/>
+      <c r="K123" s="10" t="n"/>
+      <c r="L123" s="12" t="n"/>
+      <c r="M123" s="11">
+        <f>IF(A123="","",COUNTIF('Referral Log'!$C$4:$C$400,A123))</f>
+        <v/>
+      </c>
+      <c r="N123" s="10" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="n"/>
+      <c r="B124" s="10" t="n"/>
+      <c r="C124" s="11">
+        <f>IF(B124="","",IF(B124="Business broker","1 - Highest",IF(OR(B124="POS installer",B124="Bookkeeper / CPA"),"2 - High",IF(OR(B124="Liquor / food rep",B124="Consultant"),"3 - Strong",IF(B124="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D124" s="10" t="n"/>
+      <c r="E124" s="10" t="n"/>
+      <c r="F124" s="10" t="n"/>
+      <c r="G124" s="10" t="n"/>
+      <c r="H124" s="10" t="n"/>
+      <c r="I124" s="10" t="n"/>
+      <c r="J124" s="12" t="n"/>
+      <c r="K124" s="10" t="n"/>
+      <c r="L124" s="12" t="n"/>
+      <c r="M124" s="11">
+        <f>IF(A124="","",COUNTIF('Referral Log'!$C$4:$C$400,A124))</f>
+        <v/>
+      </c>
+      <c r="N124" s="10" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="n"/>
+      <c r="B125" s="10" t="n"/>
+      <c r="C125" s="11">
+        <f>IF(B125="","",IF(B125="Business broker","1 - Highest",IF(OR(B125="POS installer",B125="Bookkeeper / CPA"),"2 - High",IF(OR(B125="Liquor / food rep",B125="Consultant"),"3 - Strong",IF(B125="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D125" s="10" t="n"/>
+      <c r="E125" s="10" t="n"/>
+      <c r="F125" s="10" t="n"/>
+      <c r="G125" s="10" t="n"/>
+      <c r="H125" s="10" t="n"/>
+      <c r="I125" s="10" t="n"/>
+      <c r="J125" s="12" t="n"/>
+      <c r="K125" s="10" t="n"/>
+      <c r="L125" s="12" t="n"/>
+      <c r="M125" s="11">
+        <f>IF(A125="","",COUNTIF('Referral Log'!$C$4:$C$400,A125))</f>
+        <v/>
+      </c>
+      <c r="N125" s="10" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="n"/>
+      <c r="B126" s="10" t="n"/>
+      <c r="C126" s="11">
+        <f>IF(B126="","",IF(B126="Business broker","1 - Highest",IF(OR(B126="POS installer",B126="Bookkeeper / CPA"),"2 - High",IF(OR(B126="Liquor / food rep",B126="Consultant"),"3 - Strong",IF(B126="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D126" s="10" t="n"/>
+      <c r="E126" s="10" t="n"/>
+      <c r="F126" s="10" t="n"/>
+      <c r="G126" s="10" t="n"/>
+      <c r="H126" s="10" t="n"/>
+      <c r="I126" s="10" t="n"/>
+      <c r="J126" s="12" t="n"/>
+      <c r="K126" s="10" t="n"/>
+      <c r="L126" s="12" t="n"/>
+      <c r="M126" s="11">
+        <f>IF(A126="","",COUNTIF('Referral Log'!$C$4:$C$400,A126))</f>
+        <v/>
+      </c>
+      <c r="N126" s="10" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="n"/>
+      <c r="B127" s="10" t="n"/>
+      <c r="C127" s="11">
+        <f>IF(B127="","",IF(B127="Business broker","1 - Highest",IF(OR(B127="POS installer",B127="Bookkeeper / CPA"),"2 - High",IF(OR(B127="Liquor / food rep",B127="Consultant"),"3 - Strong",IF(B127="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D127" s="10" t="n"/>
+      <c r="E127" s="10" t="n"/>
+      <c r="F127" s="10" t="n"/>
+      <c r="G127" s="10" t="n"/>
+      <c r="H127" s="10" t="n"/>
+      <c r="I127" s="10" t="n"/>
+      <c r="J127" s="12" t="n"/>
+      <c r="K127" s="10" t="n"/>
+      <c r="L127" s="12" t="n"/>
+      <c r="M127" s="11">
+        <f>IF(A127="","",COUNTIF('Referral Log'!$C$4:$C$400,A127))</f>
+        <v/>
+      </c>
+      <c r="N127" s="10" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="n"/>
+      <c r="B128" s="10" t="n"/>
+      <c r="C128" s="11">
+        <f>IF(B128="","",IF(B128="Business broker","1 - Highest",IF(OR(B128="POS installer",B128="Bookkeeper / CPA"),"2 - High",IF(OR(B128="Liquor / food rep",B128="Consultant"),"3 - Strong",IF(B128="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D128" s="10" t="n"/>
+      <c r="E128" s="10" t="n"/>
+      <c r="F128" s="10" t="n"/>
+      <c r="G128" s="10" t="n"/>
+      <c r="H128" s="10" t="n"/>
+      <c r="I128" s="10" t="n"/>
+      <c r="J128" s="12" t="n"/>
+      <c r="K128" s="10" t="n"/>
+      <c r="L128" s="12" t="n"/>
+      <c r="M128" s="11">
+        <f>IF(A128="","",COUNTIF('Referral Log'!$C$4:$C$400,A128))</f>
+        <v/>
+      </c>
+      <c r="N128" s="10" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="n"/>
+      <c r="B129" s="10" t="n"/>
+      <c r="C129" s="11">
+        <f>IF(B129="","",IF(B129="Business broker","1 - Highest",IF(OR(B129="POS installer",B129="Bookkeeper / CPA"),"2 - High",IF(OR(B129="Liquor / food rep",B129="Consultant"),"3 - Strong",IF(B129="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D129" s="10" t="n"/>
+      <c r="E129" s="10" t="n"/>
+      <c r="F129" s="10" t="n"/>
+      <c r="G129" s="10" t="n"/>
+      <c r="H129" s="10" t="n"/>
+      <c r="I129" s="10" t="n"/>
+      <c r="J129" s="12" t="n"/>
+      <c r="K129" s="10" t="n"/>
+      <c r="L129" s="12" t="n"/>
+      <c r="M129" s="11">
+        <f>IF(A129="","",COUNTIF('Referral Log'!$C$4:$C$400,A129))</f>
+        <v/>
+      </c>
+      <c r="N129" s="10" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="n"/>
+      <c r="B130" s="10" t="n"/>
+      <c r="C130" s="11">
+        <f>IF(B130="","",IF(B130="Business broker","1 - Highest",IF(OR(B130="POS installer",B130="Bookkeeper / CPA"),"2 - High",IF(OR(B130="Liquor / food rep",B130="Consultant"),"3 - Strong",IF(B130="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D130" s="10" t="n"/>
+      <c r="E130" s="10" t="n"/>
+      <c r="F130" s="10" t="n"/>
+      <c r="G130" s="10" t="n"/>
+      <c r="H130" s="10" t="n"/>
+      <c r="I130" s="10" t="n"/>
+      <c r="J130" s="12" t="n"/>
+      <c r="K130" s="10" t="n"/>
+      <c r="L130" s="12" t="n"/>
+      <c r="M130" s="11">
+        <f>IF(A130="","",COUNTIF('Referral Log'!$C$4:$C$400,A130))</f>
+        <v/>
+      </c>
+      <c r="N130" s="10" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="n"/>
+      <c r="B131" s="10" t="n"/>
+      <c r="C131" s="11">
+        <f>IF(B131="","",IF(B131="Business broker","1 - Highest",IF(OR(B131="POS installer",B131="Bookkeeper / CPA"),"2 - High",IF(OR(B131="Liquor / food rep",B131="Consultant"),"3 - Strong",IF(B131="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D131" s="10" t="n"/>
+      <c r="E131" s="10" t="n"/>
+      <c r="F131" s="10" t="n"/>
+      <c r="G131" s="10" t="n"/>
+      <c r="H131" s="10" t="n"/>
+      <c r="I131" s="10" t="n"/>
+      <c r="J131" s="12" t="n"/>
+      <c r="K131" s="10" t="n"/>
+      <c r="L131" s="12" t="n"/>
+      <c r="M131" s="11">
+        <f>IF(A131="","",COUNTIF('Referral Log'!$C$4:$C$400,A131))</f>
+        <v/>
+      </c>
+      <c r="N131" s="10" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="n"/>
+      <c r="B132" s="10" t="n"/>
+      <c r="C132" s="11">
+        <f>IF(B132="","",IF(B132="Business broker","1 - Highest",IF(OR(B132="POS installer",B132="Bookkeeper / CPA"),"2 - High",IF(OR(B132="Liquor / food rep",B132="Consultant"),"3 - Strong",IF(B132="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D132" s="10" t="n"/>
+      <c r="E132" s="10" t="n"/>
+      <c r="F132" s="10" t="n"/>
+      <c r="G132" s="10" t="n"/>
+      <c r="H132" s="10" t="n"/>
+      <c r="I132" s="10" t="n"/>
+      <c r="J132" s="12" t="n"/>
+      <c r="K132" s="10" t="n"/>
+      <c r="L132" s="12" t="n"/>
+      <c r="M132" s="11">
+        <f>IF(A132="","",COUNTIF('Referral Log'!$C$4:$C$400,A132))</f>
+        <v/>
+      </c>
+      <c r="N132" s="10" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="10" t="n"/>
+      <c r="B133" s="10" t="n"/>
+      <c r="C133" s="11">
+        <f>IF(B133="","",IF(B133="Business broker","1 - Highest",IF(OR(B133="POS installer",B133="Bookkeeper / CPA"),"2 - High",IF(OR(B133="Liquor / food rep",B133="Consultant"),"3 - Strong",IF(B133="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D133" s="10" t="n"/>
+      <c r="E133" s="10" t="n"/>
+      <c r="F133" s="10" t="n"/>
+      <c r="G133" s="10" t="n"/>
+      <c r="H133" s="10" t="n"/>
+      <c r="I133" s="10" t="n"/>
+      <c r="J133" s="12" t="n"/>
+      <c r="K133" s="10" t="n"/>
+      <c r="L133" s="12" t="n"/>
+      <c r="M133" s="11">
+        <f>IF(A133="","",COUNTIF('Referral Log'!$C$4:$C$400,A133))</f>
+        <v/>
+      </c>
+      <c r="N133" s="10" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="10" t="n"/>
+      <c r="B134" s="10" t="n"/>
+      <c r="C134" s="11">
+        <f>IF(B134="","",IF(B134="Business broker","1 - Highest",IF(OR(B134="POS installer",B134="Bookkeeper / CPA"),"2 - High",IF(OR(B134="Liquor / food rep",B134="Consultant"),"3 - Strong",IF(B134="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D134" s="10" t="n"/>
+      <c r="E134" s="10" t="n"/>
+      <c r="F134" s="10" t="n"/>
+      <c r="G134" s="10" t="n"/>
+      <c r="H134" s="10" t="n"/>
+      <c r="I134" s="10" t="n"/>
+      <c r="J134" s="12" t="n"/>
+      <c r="K134" s="10" t="n"/>
+      <c r="L134" s="12" t="n"/>
+      <c r="M134" s="11">
+        <f>IF(A134="","",COUNTIF('Referral Log'!$C$4:$C$400,A134))</f>
+        <v/>
+      </c>
+      <c r="N134" s="10" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="10" t="n"/>
+      <c r="B135" s="10" t="n"/>
+      <c r="C135" s="11">
+        <f>IF(B135="","",IF(B135="Business broker","1 - Highest",IF(OR(B135="POS installer",B135="Bookkeeper / CPA"),"2 - High",IF(OR(B135="Liquor / food rep",B135="Consultant"),"3 - Strong",IF(B135="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D135" s="10" t="n"/>
+      <c r="E135" s="10" t="n"/>
+      <c r="F135" s="10" t="n"/>
+      <c r="G135" s="10" t="n"/>
+      <c r="H135" s="10" t="n"/>
+      <c r="I135" s="10" t="n"/>
+      <c r="J135" s="12" t="n"/>
+      <c r="K135" s="10" t="n"/>
+      <c r="L135" s="12" t="n"/>
+      <c r="M135" s="11">
+        <f>IF(A135="","",COUNTIF('Referral Log'!$C$4:$C$400,A135))</f>
+        <v/>
+      </c>
+      <c r="N135" s="10" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="n"/>
+      <c r="B136" s="10" t="n"/>
+      <c r="C136" s="11">
+        <f>IF(B136="","",IF(B136="Business broker","1 - Highest",IF(OR(B136="POS installer",B136="Bookkeeper / CPA"),"2 - High",IF(OR(B136="Liquor / food rep",B136="Consultant"),"3 - Strong",IF(B136="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D136" s="10" t="n"/>
+      <c r="E136" s="10" t="n"/>
+      <c r="F136" s="10" t="n"/>
+      <c r="G136" s="10" t="n"/>
+      <c r="H136" s="10" t="n"/>
+      <c r="I136" s="10" t="n"/>
+      <c r="J136" s="12" t="n"/>
+      <c r="K136" s="10" t="n"/>
+      <c r="L136" s="12" t="n"/>
+      <c r="M136" s="11">
+        <f>IF(A136="","",COUNTIF('Referral Log'!$C$4:$C$400,A136))</f>
+        <v/>
+      </c>
+      <c r="N136" s="10" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="10" t="n"/>
+      <c r="B137" s="10" t="n"/>
+      <c r="C137" s="11">
+        <f>IF(B137="","",IF(B137="Business broker","1 - Highest",IF(OR(B137="POS installer",B137="Bookkeeper / CPA"),"2 - High",IF(OR(B137="Liquor / food rep",B137="Consultant"),"3 - Strong",IF(B137="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D137" s="10" t="n"/>
+      <c r="E137" s="10" t="n"/>
+      <c r="F137" s="10" t="n"/>
+      <c r="G137" s="10" t="n"/>
+      <c r="H137" s="10" t="n"/>
+      <c r="I137" s="10" t="n"/>
+      <c r="J137" s="12" t="n"/>
+      <c r="K137" s="10" t="n"/>
+      <c r="L137" s="12" t="n"/>
+      <c r="M137" s="11">
+        <f>IF(A137="","",COUNTIF('Referral Log'!$C$4:$C$400,A137))</f>
+        <v/>
+      </c>
+      <c r="N137" s="10" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="n"/>
+      <c r="B138" s="10" t="n"/>
+      <c r="C138" s="11">
+        <f>IF(B138="","",IF(B138="Business broker","1 - Highest",IF(OR(B138="POS installer",B138="Bookkeeper / CPA"),"2 - High",IF(OR(B138="Liquor / food rep",B138="Consultant"),"3 - Strong",IF(B138="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D138" s="10" t="n"/>
+      <c r="E138" s="10" t="n"/>
+      <c r="F138" s="10" t="n"/>
+      <c r="G138" s="10" t="n"/>
+      <c r="H138" s="10" t="n"/>
+      <c r="I138" s="10" t="n"/>
+      <c r="J138" s="12" t="n"/>
+      <c r="K138" s="10" t="n"/>
+      <c r="L138" s="12" t="n"/>
+      <c r="M138" s="11">
+        <f>IF(A138="","",COUNTIF('Referral Log'!$C$4:$C$400,A138))</f>
+        <v/>
+      </c>
+      <c r="N138" s="10" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="10" t="n"/>
+      <c r="B139" s="10" t="n"/>
+      <c r="C139" s="11">
+        <f>IF(B139="","",IF(B139="Business broker","1 - Highest",IF(OR(B139="POS installer",B139="Bookkeeper / CPA"),"2 - High",IF(OR(B139="Liquor / food rep",B139="Consultant"),"3 - Strong",IF(B139="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D139" s="10" t="n"/>
+      <c r="E139" s="10" t="n"/>
+      <c r="F139" s="10" t="n"/>
+      <c r="G139" s="10" t="n"/>
+      <c r="H139" s="10" t="n"/>
+      <c r="I139" s="10" t="n"/>
+      <c r="J139" s="12" t="n"/>
+      <c r="K139" s="10" t="n"/>
+      <c r="L139" s="12" t="n"/>
+      <c r="M139" s="11">
+        <f>IF(A139="","",COUNTIF('Referral Log'!$C$4:$C$400,A139))</f>
+        <v/>
+      </c>
+      <c r="N139" s="10" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="10" t="n"/>
+      <c r="B140" s="10" t="n"/>
+      <c r="C140" s="11">
+        <f>IF(B140="","",IF(B140="Business broker","1 - Highest",IF(OR(B140="POS installer",B140="Bookkeeper / CPA"),"2 - High",IF(OR(B140="Liquor / food rep",B140="Consultant"),"3 - Strong",IF(B140="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D140" s="10" t="n"/>
+      <c r="E140" s="10" t="n"/>
+      <c r="F140" s="10" t="n"/>
+      <c r="G140" s="10" t="n"/>
+      <c r="H140" s="10" t="n"/>
+      <c r="I140" s="10" t="n"/>
+      <c r="J140" s="12" t="n"/>
+      <c r="K140" s="10" t="n"/>
+      <c r="L140" s="12" t="n"/>
+      <c r="M140" s="11">
+        <f>IF(A140="","",COUNTIF('Referral Log'!$C$4:$C$400,A140))</f>
+        <v/>
+      </c>
+      <c r="N140" s="10" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="10" t="n"/>
+      <c r="B141" s="10" t="n"/>
+      <c r="C141" s="11">
+        <f>IF(B141="","",IF(B141="Business broker","1 - Highest",IF(OR(B141="POS installer",B141="Bookkeeper / CPA"),"2 - High",IF(OR(B141="Liquor / food rep",B141="Consultant"),"3 - Strong",IF(B141="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D141" s="10" t="n"/>
+      <c r="E141" s="10" t="n"/>
+      <c r="F141" s="10" t="n"/>
+      <c r="G141" s="10" t="n"/>
+      <c r="H141" s="10" t="n"/>
+      <c r="I141" s="10" t="n"/>
+      <c r="J141" s="12" t="n"/>
+      <c r="K141" s="10" t="n"/>
+      <c r="L141" s="12" t="n"/>
+      <c r="M141" s="11">
+        <f>IF(A141="","",COUNTIF('Referral Log'!$C$4:$C$400,A141))</f>
+        <v/>
+      </c>
+      <c r="N141" s="10" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="10" t="n"/>
+      <c r="B142" s="10" t="n"/>
+      <c r="C142" s="11">
+        <f>IF(B142="","",IF(B142="Business broker","1 - Highest",IF(OR(B142="POS installer",B142="Bookkeeper / CPA"),"2 - High",IF(OR(B142="Liquor / food rep",B142="Consultant"),"3 - Strong",IF(B142="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D142" s="10" t="n"/>
+      <c r="E142" s="10" t="n"/>
+      <c r="F142" s="10" t="n"/>
+      <c r="G142" s="10" t="n"/>
+      <c r="H142" s="10" t="n"/>
+      <c r="I142" s="10" t="n"/>
+      <c r="J142" s="12" t="n"/>
+      <c r="K142" s="10" t="n"/>
+      <c r="L142" s="12" t="n"/>
+      <c r="M142" s="11">
+        <f>IF(A142="","",COUNTIF('Referral Log'!$C$4:$C$400,A142))</f>
+        <v/>
+      </c>
+      <c r="N142" s="10" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="10" t="n"/>
+      <c r="B143" s="10" t="n"/>
+      <c r="C143" s="11">
+        <f>IF(B143="","",IF(B143="Business broker","1 - Highest",IF(OR(B143="POS installer",B143="Bookkeeper / CPA"),"2 - High",IF(OR(B143="Liquor / food rep",B143="Consultant"),"3 - Strong",IF(B143="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D143" s="10" t="n"/>
+      <c r="E143" s="10" t="n"/>
+      <c r="F143" s="10" t="n"/>
+      <c r="G143" s="10" t="n"/>
+      <c r="H143" s="10" t="n"/>
+      <c r="I143" s="10" t="n"/>
+      <c r="J143" s="12" t="n"/>
+      <c r="K143" s="10" t="n"/>
+      <c r="L143" s="12" t="n"/>
+      <c r="M143" s="11">
+        <f>IF(A143="","",COUNTIF('Referral Log'!$C$4:$C$400,A143))</f>
+        <v/>
+      </c>
+      <c r="N143" s="10" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="10" t="n"/>
+      <c r="B144" s="10" t="n"/>
+      <c r="C144" s="11">
+        <f>IF(B144="","",IF(B144="Business broker","1 - Highest",IF(OR(B144="POS installer",B144="Bookkeeper / CPA"),"2 - High",IF(OR(B144="Liquor / food rep",B144="Consultant"),"3 - Strong",IF(B144="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D144" s="10" t="n"/>
+      <c r="E144" s="10" t="n"/>
+      <c r="F144" s="10" t="n"/>
+      <c r="G144" s="10" t="n"/>
+      <c r="H144" s="10" t="n"/>
+      <c r="I144" s="10" t="n"/>
+      <c r="J144" s="12" t="n"/>
+      <c r="K144" s="10" t="n"/>
+      <c r="L144" s="12" t="n"/>
+      <c r="M144" s="11">
+        <f>IF(A144="","",COUNTIF('Referral Log'!$C$4:$C$400,A144))</f>
+        <v/>
+      </c>
+      <c r="N144" s="10" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="10" t="n"/>
+      <c r="B145" s="10" t="n"/>
+      <c r="C145" s="11">
+        <f>IF(B145="","",IF(B145="Business broker","1 - Highest",IF(OR(B145="POS installer",B145="Bookkeeper / CPA"),"2 - High",IF(OR(B145="Liquor / food rep",B145="Consultant"),"3 - Strong",IF(B145="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D145" s="10" t="n"/>
+      <c r="E145" s="10" t="n"/>
+      <c r="F145" s="10" t="n"/>
+      <c r="G145" s="10" t="n"/>
+      <c r="H145" s="10" t="n"/>
+      <c r="I145" s="10" t="n"/>
+      <c r="J145" s="12" t="n"/>
+      <c r="K145" s="10" t="n"/>
+      <c r="L145" s="12" t="n"/>
+      <c r="M145" s="11">
+        <f>IF(A145="","",COUNTIF('Referral Log'!$C$4:$C$400,A145))</f>
+        <v/>
+      </c>
+      <c r="N145" s="10" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="n"/>
+      <c r="B146" s="10" t="n"/>
+      <c r="C146" s="11">
+        <f>IF(B146="","",IF(B146="Business broker","1 - Highest",IF(OR(B146="POS installer",B146="Bookkeeper / CPA"),"2 - High",IF(OR(B146="Liquor / food rep",B146="Consultant"),"3 - Strong",IF(B146="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D146" s="10" t="n"/>
+      <c r="E146" s="10" t="n"/>
+      <c r="F146" s="10" t="n"/>
+      <c r="G146" s="10" t="n"/>
+      <c r="H146" s="10" t="n"/>
+      <c r="I146" s="10" t="n"/>
+      <c r="J146" s="12" t="n"/>
+      <c r="K146" s="10" t="n"/>
+      <c r="L146" s="12" t="n"/>
+      <c r="M146" s="11">
+        <f>IF(A146="","",COUNTIF('Referral Log'!$C$4:$C$400,A146))</f>
+        <v/>
+      </c>
+      <c r="N146" s="10" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="n"/>
+      <c r="B147" s="10" t="n"/>
+      <c r="C147" s="11">
+        <f>IF(B147="","",IF(B147="Business broker","1 - Highest",IF(OR(B147="POS installer",B147="Bookkeeper / CPA"),"2 - High",IF(OR(B147="Liquor / food rep",B147="Consultant"),"3 - Strong",IF(B147="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D147" s="10" t="n"/>
+      <c r="E147" s="10" t="n"/>
+      <c r="F147" s="10" t="n"/>
+      <c r="G147" s="10" t="n"/>
+      <c r="H147" s="10" t="n"/>
+      <c r="I147" s="10" t="n"/>
+      <c r="J147" s="12" t="n"/>
+      <c r="K147" s="10" t="n"/>
+      <c r="L147" s="12" t="n"/>
+      <c r="M147" s="11">
+        <f>IF(A147="","",COUNTIF('Referral Log'!$C$4:$C$400,A147))</f>
+        <v/>
+      </c>
+      <c r="N147" s="10" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="10" t="n"/>
+      <c r="B148" s="10" t="n"/>
+      <c r="C148" s="11">
+        <f>IF(B148="","",IF(B148="Business broker","1 - Highest",IF(OR(B148="POS installer",B148="Bookkeeper / CPA"),"2 - High",IF(OR(B148="Liquor / food rep",B148="Consultant"),"3 - Strong",IF(B148="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D148" s="10" t="n"/>
+      <c r="E148" s="10" t="n"/>
+      <c r="F148" s="10" t="n"/>
+      <c r="G148" s="10" t="n"/>
+      <c r="H148" s="10" t="n"/>
+      <c r="I148" s="10" t="n"/>
+      <c r="J148" s="12" t="n"/>
+      <c r="K148" s="10" t="n"/>
+      <c r="L148" s="12" t="n"/>
+      <c r="M148" s="11">
+        <f>IF(A148="","",COUNTIF('Referral Log'!$C$4:$C$400,A148))</f>
+        <v/>
+      </c>
+      <c r="N148" s="10" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="n"/>
+      <c r="B149" s="10" t="n"/>
+      <c r="C149" s="11">
+        <f>IF(B149="","",IF(B149="Business broker","1 - Highest",IF(OR(B149="POS installer",B149="Bookkeeper / CPA"),"2 - High",IF(OR(B149="Liquor / food rep",B149="Consultant"),"3 - Strong",IF(B149="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D149" s="10" t="n"/>
+      <c r="E149" s="10" t="n"/>
+      <c r="F149" s="10" t="n"/>
+      <c r="G149" s="10" t="n"/>
+      <c r="H149" s="10" t="n"/>
+      <c r="I149" s="10" t="n"/>
+      <c r="J149" s="12" t="n"/>
+      <c r="K149" s="10" t="n"/>
+      <c r="L149" s="12" t="n"/>
+      <c r="M149" s="11">
+        <f>IF(A149="","",COUNTIF('Referral Log'!$C$4:$C$400,A149))</f>
+        <v/>
+      </c>
+      <c r="N149" s="10" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="10" t="n"/>
+      <c r="B150" s="10" t="n"/>
+      <c r="C150" s="11">
+        <f>IF(B150="","",IF(B150="Business broker","1 - Highest",IF(OR(B150="POS installer",B150="Bookkeeper / CPA"),"2 - High",IF(OR(B150="Liquor / food rep",B150="Consultant"),"3 - Strong",IF(B150="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D150" s="10" t="n"/>
+      <c r="E150" s="10" t="n"/>
+      <c r="F150" s="10" t="n"/>
+      <c r="G150" s="10" t="n"/>
+      <c r="H150" s="10" t="n"/>
+      <c r="I150" s="10" t="n"/>
+      <c r="J150" s="12" t="n"/>
+      <c r="K150" s="10" t="n"/>
+      <c r="L150" s="12" t="n"/>
+      <c r="M150" s="11">
+        <f>IF(A150="","",COUNTIF('Referral Log'!$C$4:$C$400,A150))</f>
+        <v/>
+      </c>
+      <c r="N150" s="10" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="10" t="n"/>
+      <c r="B151" s="10" t="n"/>
+      <c r="C151" s="11">
+        <f>IF(B151="","",IF(B151="Business broker","1 - Highest",IF(OR(B151="POS installer",B151="Bookkeeper / CPA"),"2 - High",IF(OR(B151="Liquor / food rep",B151="Consultant"),"3 - Strong",IF(B151="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D151" s="10" t="n"/>
+      <c r="E151" s="10" t="n"/>
+      <c r="F151" s="10" t="n"/>
+      <c r="G151" s="10" t="n"/>
+      <c r="H151" s="10" t="n"/>
+      <c r="I151" s="10" t="n"/>
+      <c r="J151" s="12" t="n"/>
+      <c r="K151" s="10" t="n"/>
+      <c r="L151" s="12" t="n"/>
+      <c r="M151" s="11">
+        <f>IF(A151="","",COUNTIF('Referral Log'!$C$4:$C$400,A151))</f>
+        <v/>
+      </c>
+      <c r="N151" s="10" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="10" t="n"/>
+      <c r="B152" s="10" t="n"/>
+      <c r="C152" s="11">
+        <f>IF(B152="","",IF(B152="Business broker","1 - Highest",IF(OR(B152="POS installer",B152="Bookkeeper / CPA"),"2 - High",IF(OR(B152="Liquor / food rep",B152="Consultant"),"3 - Strong",IF(B152="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D152" s="10" t="n"/>
+      <c r="E152" s="10" t="n"/>
+      <c r="F152" s="10" t="n"/>
+      <c r="G152" s="10" t="n"/>
+      <c r="H152" s="10" t="n"/>
+      <c r="I152" s="10" t="n"/>
+      <c r="J152" s="12" t="n"/>
+      <c r="K152" s="10" t="n"/>
+      <c r="L152" s="12" t="n"/>
+      <c r="M152" s="11">
+        <f>IF(A152="","",COUNTIF('Referral Log'!$C$4:$C$400,A152))</f>
+        <v/>
+      </c>
+      <c r="N152" s="10" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="10" t="n"/>
+      <c r="B153" s="10" t="n"/>
+      <c r="C153" s="11">
+        <f>IF(B153="","",IF(B153="Business broker","1 - Highest",IF(OR(B153="POS installer",B153="Bookkeeper / CPA"),"2 - High",IF(OR(B153="Liquor / food rep",B153="Consultant"),"3 - Strong",IF(B153="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D153" s="10" t="n"/>
+      <c r="E153" s="10" t="n"/>
+      <c r="F153" s="10" t="n"/>
+      <c r="G153" s="10" t="n"/>
+      <c r="H153" s="10" t="n"/>
+      <c r="I153" s="10" t="n"/>
+      <c r="J153" s="12" t="n"/>
+      <c r="K153" s="10" t="n"/>
+      <c r="L153" s="12" t="n"/>
+      <c r="M153" s="11">
+        <f>IF(A153="","",COUNTIF('Referral Log'!$C$4:$C$400,A153))</f>
+        <v/>
+      </c>
+      <c r="N153" s="10" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="10" t="n"/>
+      <c r="B154" s="10" t="n"/>
+      <c r="C154" s="11">
+        <f>IF(B154="","",IF(B154="Business broker","1 - Highest",IF(OR(B154="POS installer",B154="Bookkeeper / CPA"),"2 - High",IF(OR(B154="Liquor / food rep",B154="Consultant"),"3 - Strong",IF(B154="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D154" s="10" t="n"/>
+      <c r="E154" s="10" t="n"/>
+      <c r="F154" s="10" t="n"/>
+      <c r="G154" s="10" t="n"/>
+      <c r="H154" s="10" t="n"/>
+      <c r="I154" s="10" t="n"/>
+      <c r="J154" s="12" t="n"/>
+      <c r="K154" s="10" t="n"/>
+      <c r="L154" s="12" t="n"/>
+      <c r="M154" s="11">
+        <f>IF(A154="","",COUNTIF('Referral Log'!$C$4:$C$400,A154))</f>
+        <v/>
+      </c>
+      <c r="N154" s="10" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="10" t="n"/>
+      <c r="B155" s="10" t="n"/>
+      <c r="C155" s="11">
+        <f>IF(B155="","",IF(B155="Business broker","1 - Highest",IF(OR(B155="POS installer",B155="Bookkeeper / CPA"),"2 - High",IF(OR(B155="Liquor / food rep",B155="Consultant"),"3 - Strong",IF(B155="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D155" s="10" t="n"/>
+      <c r="E155" s="10" t="n"/>
+      <c r="F155" s="10" t="n"/>
+      <c r="G155" s="10" t="n"/>
+      <c r="H155" s="10" t="n"/>
+      <c r="I155" s="10" t="n"/>
+      <c r="J155" s="12" t="n"/>
+      <c r="K155" s="10" t="n"/>
+      <c r="L155" s="12" t="n"/>
+      <c r="M155" s="11">
+        <f>IF(A155="","",COUNTIF('Referral Log'!$C$4:$C$400,A155))</f>
+        <v/>
+      </c>
+      <c r="N155" s="10" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="10" t="n"/>
+      <c r="B156" s="10" t="n"/>
+      <c r="C156" s="11">
+        <f>IF(B156="","",IF(B156="Business broker","1 - Highest",IF(OR(B156="POS installer",B156="Bookkeeper / CPA"),"2 - High",IF(OR(B156="Liquor / food rep",B156="Consultant"),"3 - Strong",IF(B156="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D156" s="10" t="n"/>
+      <c r="E156" s="10" t="n"/>
+      <c r="F156" s="10" t="n"/>
+      <c r="G156" s="10" t="n"/>
+      <c r="H156" s="10" t="n"/>
+      <c r="I156" s="10" t="n"/>
+      <c r="J156" s="12" t="n"/>
+      <c r="K156" s="10" t="n"/>
+      <c r="L156" s="12" t="n"/>
+      <c r="M156" s="11">
+        <f>IF(A156="","",COUNTIF('Referral Log'!$C$4:$C$400,A156))</f>
+        <v/>
+      </c>
+      <c r="N156" s="10" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="10" t="n"/>
+      <c r="B157" s="10" t="n"/>
+      <c r="C157" s="11">
+        <f>IF(B157="","",IF(B157="Business broker","1 - Highest",IF(OR(B157="POS installer",B157="Bookkeeper / CPA"),"2 - High",IF(OR(B157="Liquor / food rep",B157="Consultant"),"3 - Strong",IF(B157="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D157" s="10" t="n"/>
+      <c r="E157" s="10" t="n"/>
+      <c r="F157" s="10" t="n"/>
+      <c r="G157" s="10" t="n"/>
+      <c r="H157" s="10" t="n"/>
+      <c r="I157" s="10" t="n"/>
+      <c r="J157" s="12" t="n"/>
+      <c r="K157" s="10" t="n"/>
+      <c r="L157" s="12" t="n"/>
+      <c r="M157" s="11">
+        <f>IF(A157="","",COUNTIF('Referral Log'!$C$4:$C$400,A157))</f>
+        <v/>
+      </c>
+      <c r="N157" s="10" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="10" t="n"/>
+      <c r="B158" s="10" t="n"/>
+      <c r="C158" s="11">
+        <f>IF(B158="","",IF(B158="Business broker","1 - Highest",IF(OR(B158="POS installer",B158="Bookkeeper / CPA"),"2 - High",IF(OR(B158="Liquor / food rep",B158="Consultant"),"3 - Strong",IF(B158="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D158" s="10" t="n"/>
+      <c r="E158" s="10" t="n"/>
+      <c r="F158" s="10" t="n"/>
+      <c r="G158" s="10" t="n"/>
+      <c r="H158" s="10" t="n"/>
+      <c r="I158" s="10" t="n"/>
+      <c r="J158" s="12" t="n"/>
+      <c r="K158" s="10" t="n"/>
+      <c r="L158" s="12" t="n"/>
+      <c r="M158" s="11">
+        <f>IF(A158="","",COUNTIF('Referral Log'!$C$4:$C$400,A158))</f>
+        <v/>
+      </c>
+      <c r="N158" s="10" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="10" t="n"/>
+      <c r="B159" s="10" t="n"/>
+      <c r="C159" s="11">
+        <f>IF(B159="","",IF(B159="Business broker","1 - Highest",IF(OR(B159="POS installer",B159="Bookkeeper / CPA"),"2 - High",IF(OR(B159="Liquor / food rep",B159="Consultant"),"3 - Strong",IF(B159="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D159" s="10" t="n"/>
+      <c r="E159" s="10" t="n"/>
+      <c r="F159" s="10" t="n"/>
+      <c r="G159" s="10" t="n"/>
+      <c r="H159" s="10" t="n"/>
+      <c r="I159" s="10" t="n"/>
+      <c r="J159" s="12" t="n"/>
+      <c r="K159" s="10" t="n"/>
+      <c r="L159" s="12" t="n"/>
+      <c r="M159" s="11">
+        <f>IF(A159="","",COUNTIF('Referral Log'!$C$4:$C$400,A159))</f>
+        <v/>
+      </c>
+      <c r="N159" s="10" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="10" t="n"/>
+      <c r="B160" s="10" t="n"/>
+      <c r="C160" s="11">
+        <f>IF(B160="","",IF(B160="Business broker","1 - Highest",IF(OR(B160="POS installer",B160="Bookkeeper / CPA"),"2 - High",IF(OR(B160="Liquor / food rep",B160="Consultant"),"3 - Strong",IF(B160="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D160" s="10" t="n"/>
+      <c r="E160" s="10" t="n"/>
+      <c r="F160" s="10" t="n"/>
+      <c r="G160" s="10" t="n"/>
+      <c r="H160" s="10" t="n"/>
+      <c r="I160" s="10" t="n"/>
+      <c r="J160" s="12" t="n"/>
+      <c r="K160" s="10" t="n"/>
+      <c r="L160" s="12" t="n"/>
+      <c r="M160" s="11">
+        <f>IF(A160="","",COUNTIF('Referral Log'!$C$4:$C$400,A160))</f>
+        <v/>
+      </c>
+      <c r="N160" s="10" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="10" t="n"/>
+      <c r="B161" s="10" t="n"/>
+      <c r="C161" s="11">
+        <f>IF(B161="","",IF(B161="Business broker","1 - Highest",IF(OR(B161="POS installer",B161="Bookkeeper / CPA"),"2 - High",IF(OR(B161="Liquor / food rep",B161="Consultant"),"3 - Strong",IF(B161="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D161" s="10" t="n"/>
+      <c r="E161" s="10" t="n"/>
+      <c r="F161" s="10" t="n"/>
+      <c r="G161" s="10" t="n"/>
+      <c r="H161" s="10" t="n"/>
+      <c r="I161" s="10" t="n"/>
+      <c r="J161" s="12" t="n"/>
+      <c r="K161" s="10" t="n"/>
+      <c r="L161" s="12" t="n"/>
+      <c r="M161" s="11">
+        <f>IF(A161="","",COUNTIF('Referral Log'!$C$4:$C$400,A161))</f>
+        <v/>
+      </c>
+      <c r="N161" s="10" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="10" t="n"/>
+      <c r="B162" s="10" t="n"/>
+      <c r="C162" s="11">
+        <f>IF(B162="","",IF(B162="Business broker","1 - Highest",IF(OR(B162="POS installer",B162="Bookkeeper / CPA"),"2 - High",IF(OR(B162="Liquor / food rep",B162="Consultant"),"3 - Strong",IF(B162="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D162" s="10" t="n"/>
+      <c r="E162" s="10" t="n"/>
+      <c r="F162" s="10" t="n"/>
+      <c r="G162" s="10" t="n"/>
+      <c r="H162" s="10" t="n"/>
+      <c r="I162" s="10" t="n"/>
+      <c r="J162" s="12" t="n"/>
+      <c r="K162" s="10" t="n"/>
+      <c r="L162" s="12" t="n"/>
+      <c r="M162" s="11">
+        <f>IF(A162="","",COUNTIF('Referral Log'!$C$4:$C$400,A162))</f>
+        <v/>
+      </c>
+      <c r="N162" s="10" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="10" t="n"/>
+      <c r="B163" s="10" t="n"/>
+      <c r="C163" s="11">
+        <f>IF(B163="","",IF(B163="Business broker","1 - Highest",IF(OR(B163="POS installer",B163="Bookkeeper / CPA"),"2 - High",IF(OR(B163="Liquor / food rep",B163="Consultant"),"3 - Strong",IF(B163="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D163" s="10" t="n"/>
+      <c r="E163" s="10" t="n"/>
+      <c r="F163" s="10" t="n"/>
+      <c r="G163" s="10" t="n"/>
+      <c r="H163" s="10" t="n"/>
+      <c r="I163" s="10" t="n"/>
+      <c r="J163" s="12" t="n"/>
+      <c r="K163" s="10" t="n"/>
+      <c r="L163" s="12" t="n"/>
+      <c r="M163" s="11">
+        <f>IF(A163="","",COUNTIF('Referral Log'!$C$4:$C$400,A163))</f>
+        <v/>
+      </c>
+      <c r="N163" s="10" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="10" t="n"/>
+      <c r="B164" s="10" t="n"/>
+      <c r="C164" s="11">
+        <f>IF(B164="","",IF(B164="Business broker","1 - Highest",IF(OR(B164="POS installer",B164="Bookkeeper / CPA"),"2 - High",IF(OR(B164="Liquor / food rep",B164="Consultant"),"3 - Strong",IF(B164="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D164" s="10" t="n"/>
+      <c r="E164" s="10" t="n"/>
+      <c r="F164" s="10" t="n"/>
+      <c r="G164" s="10" t="n"/>
+      <c r="H164" s="10" t="n"/>
+      <c r="I164" s="10" t="n"/>
+      <c r="J164" s="12" t="n"/>
+      <c r="K164" s="10" t="n"/>
+      <c r="L164" s="12" t="n"/>
+      <c r="M164" s="11">
+        <f>IF(A164="","",COUNTIF('Referral Log'!$C$4:$C$400,A164))</f>
+        <v/>
+      </c>
+      <c r="N164" s="10" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="10" t="n"/>
+      <c r="B165" s="10" t="n"/>
+      <c r="C165" s="11">
+        <f>IF(B165="","",IF(B165="Business broker","1 - Highest",IF(OR(B165="POS installer",B165="Bookkeeper / CPA"),"2 - High",IF(OR(B165="Liquor / food rep",B165="Consultant"),"3 - Strong",IF(B165="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D165" s="10" t="n"/>
+      <c r="E165" s="10" t="n"/>
+      <c r="F165" s="10" t="n"/>
+      <c r="G165" s="10" t="n"/>
+      <c r="H165" s="10" t="n"/>
+      <c r="I165" s="10" t="n"/>
+      <c r="J165" s="12" t="n"/>
+      <c r="K165" s="10" t="n"/>
+      <c r="L165" s="12" t="n"/>
+      <c r="M165" s="11">
+        <f>IF(A165="","",COUNTIF('Referral Log'!$C$4:$C$400,A165))</f>
+        <v/>
+      </c>
+      <c r="N165" s="10" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="10" t="n"/>
+      <c r="B166" s="10" t="n"/>
+      <c r="C166" s="11">
+        <f>IF(B166="","",IF(B166="Business broker","1 - Highest",IF(OR(B166="POS installer",B166="Bookkeeper / CPA"),"2 - High",IF(OR(B166="Liquor / food rep",B166="Consultant"),"3 - Strong",IF(B166="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D166" s="10" t="n"/>
+      <c r="E166" s="10" t="n"/>
+      <c r="F166" s="10" t="n"/>
+      <c r="G166" s="10" t="n"/>
+      <c r="H166" s="10" t="n"/>
+      <c r="I166" s="10" t="n"/>
+      <c r="J166" s="12" t="n"/>
+      <c r="K166" s="10" t="n"/>
+      <c r="L166" s="12" t="n"/>
+      <c r="M166" s="11">
+        <f>IF(A166="","",COUNTIF('Referral Log'!$C$4:$C$400,A166))</f>
+        <v/>
+      </c>
+      <c r="N166" s="10" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="10" t="n"/>
+      <c r="B167" s="10" t="n"/>
+      <c r="C167" s="11">
+        <f>IF(B167="","",IF(B167="Business broker","1 - Highest",IF(OR(B167="POS installer",B167="Bookkeeper / CPA"),"2 - High",IF(OR(B167="Liquor / food rep",B167="Consultant"),"3 - Strong",IF(B167="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D167" s="10" t="n"/>
+      <c r="E167" s="10" t="n"/>
+      <c r="F167" s="10" t="n"/>
+      <c r="G167" s="10" t="n"/>
+      <c r="H167" s="10" t="n"/>
+      <c r="I167" s="10" t="n"/>
+      <c r="J167" s="12" t="n"/>
+      <c r="K167" s="10" t="n"/>
+      <c r="L167" s="12" t="n"/>
+      <c r="M167" s="11">
+        <f>IF(A167="","",COUNTIF('Referral Log'!$C$4:$C$400,A167))</f>
+        <v/>
+      </c>
+      <c r="N167" s="10" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="10" t="n"/>
+      <c r="B168" s="10" t="n"/>
+      <c r="C168" s="11">
+        <f>IF(B168="","",IF(B168="Business broker","1 - Highest",IF(OR(B168="POS installer",B168="Bookkeeper / CPA"),"2 - High",IF(OR(B168="Liquor / food rep",B168="Consultant"),"3 - Strong",IF(B168="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D168" s="10" t="n"/>
+      <c r="E168" s="10" t="n"/>
+      <c r="F168" s="10" t="n"/>
+      <c r="G168" s="10" t="n"/>
+      <c r="H168" s="10" t="n"/>
+      <c r="I168" s="10" t="n"/>
+      <c r="J168" s="12" t="n"/>
+      <c r="K168" s="10" t="n"/>
+      <c r="L168" s="12" t="n"/>
+      <c r="M168" s="11">
+        <f>IF(A168="","",COUNTIF('Referral Log'!$C$4:$C$400,A168))</f>
+        <v/>
+      </c>
+      <c r="N168" s="10" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="10" t="n"/>
+      <c r="B169" s="10" t="n"/>
+      <c r="C169" s="11">
+        <f>IF(B169="","",IF(B169="Business broker","1 - Highest",IF(OR(B169="POS installer",B169="Bookkeeper / CPA"),"2 - High",IF(OR(B169="Liquor / food rep",B169="Consultant"),"3 - Strong",IF(B169="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D169" s="10" t="n"/>
+      <c r="E169" s="10" t="n"/>
+      <c r="F169" s="10" t="n"/>
+      <c r="G169" s="10" t="n"/>
+      <c r="H169" s="10" t="n"/>
+      <c r="I169" s="10" t="n"/>
+      <c r="J169" s="12" t="n"/>
+      <c r="K169" s="10" t="n"/>
+      <c r="L169" s="12" t="n"/>
+      <c r="M169" s="11">
+        <f>IF(A169="","",COUNTIF('Referral Log'!$C$4:$C$400,A169))</f>
+        <v/>
+      </c>
+      <c r="N169" s="10" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="10" t="n"/>
+      <c r="B170" s="10" t="n"/>
+      <c r="C170" s="11">
+        <f>IF(B170="","",IF(B170="Business broker","1 - Highest",IF(OR(B170="POS installer",B170="Bookkeeper / CPA"),"2 - High",IF(OR(B170="Liquor / food rep",B170="Consultant"),"3 - Strong",IF(B170="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D170" s="10" t="n"/>
+      <c r="E170" s="10" t="n"/>
+      <c r="F170" s="10" t="n"/>
+      <c r="G170" s="10" t="n"/>
+      <c r="H170" s="10" t="n"/>
+      <c r="I170" s="10" t="n"/>
+      <c r="J170" s="12" t="n"/>
+      <c r="K170" s="10" t="n"/>
+      <c r="L170" s="12" t="n"/>
+      <c r="M170" s="11">
+        <f>IF(A170="","",COUNTIF('Referral Log'!$C$4:$C$400,A170))</f>
+        <v/>
+      </c>
+      <c r="N170" s="10" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="10" t="n"/>
+      <c r="B171" s="10" t="n"/>
+      <c r="C171" s="11">
+        <f>IF(B171="","",IF(B171="Business broker","1 - Highest",IF(OR(B171="POS installer",B171="Bookkeeper / CPA"),"2 - High",IF(OR(B171="Liquor / food rep",B171="Consultant"),"3 - Strong",IF(B171="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D171" s="10" t="n"/>
+      <c r="E171" s="10" t="n"/>
+      <c r="F171" s="10" t="n"/>
+      <c r="G171" s="10" t="n"/>
+      <c r="H171" s="10" t="n"/>
+      <c r="I171" s="10" t="n"/>
+      <c r="J171" s="12" t="n"/>
+      <c r="K171" s="10" t="n"/>
+      <c r="L171" s="12" t="n"/>
+      <c r="M171" s="11">
+        <f>IF(A171="","",COUNTIF('Referral Log'!$C$4:$C$400,A171))</f>
+        <v/>
+      </c>
+      <c r="N171" s="10" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="10" t="n"/>
+      <c r="B172" s="10" t="n"/>
+      <c r="C172" s="11">
+        <f>IF(B172="","",IF(B172="Business broker","1 - Highest",IF(OR(B172="POS installer",B172="Bookkeeper / CPA"),"2 - High",IF(OR(B172="Liquor / food rep",B172="Consultant"),"3 - Strong",IF(B172="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D172" s="10" t="n"/>
+      <c r="E172" s="10" t="n"/>
+      <c r="F172" s="10" t="n"/>
+      <c r="G172" s="10" t="n"/>
+      <c r="H172" s="10" t="n"/>
+      <c r="I172" s="10" t="n"/>
+      <c r="J172" s="12" t="n"/>
+      <c r="K172" s="10" t="n"/>
+      <c r="L172" s="12" t="n"/>
+      <c r="M172" s="11">
+        <f>IF(A172="","",COUNTIF('Referral Log'!$C$4:$C$400,A172))</f>
+        <v/>
+      </c>
+      <c r="N172" s="10" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="10" t="n"/>
+      <c r="B173" s="10" t="n"/>
+      <c r="C173" s="11">
+        <f>IF(B173="","",IF(B173="Business broker","1 - Highest",IF(OR(B173="POS installer",B173="Bookkeeper / CPA"),"2 - High",IF(OR(B173="Liquor / food rep",B173="Consultant"),"3 - Strong",IF(B173="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D173" s="10" t="n"/>
+      <c r="E173" s="10" t="n"/>
+      <c r="F173" s="10" t="n"/>
+      <c r="G173" s="10" t="n"/>
+      <c r="H173" s="10" t="n"/>
+      <c r="I173" s="10" t="n"/>
+      <c r="J173" s="12" t="n"/>
+      <c r="K173" s="10" t="n"/>
+      <c r="L173" s="12" t="n"/>
+      <c r="M173" s="11">
+        <f>IF(A173="","",COUNTIF('Referral Log'!$C$4:$C$400,A173))</f>
+        <v/>
+      </c>
+      <c r="N173" s="10" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="10" t="n"/>
+      <c r="B174" s="10" t="n"/>
+      <c r="C174" s="11">
+        <f>IF(B174="","",IF(B174="Business broker","1 - Highest",IF(OR(B174="POS installer",B174="Bookkeeper / CPA"),"2 - High",IF(OR(B174="Liquor / food rep",B174="Consultant"),"3 - Strong",IF(B174="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D174" s="10" t="n"/>
+      <c r="E174" s="10" t="n"/>
+      <c r="F174" s="10" t="n"/>
+      <c r="G174" s="10" t="n"/>
+      <c r="H174" s="10" t="n"/>
+      <c r="I174" s="10" t="n"/>
+      <c r="J174" s="12" t="n"/>
+      <c r="K174" s="10" t="n"/>
+      <c r="L174" s="12" t="n"/>
+      <c r="M174" s="11">
+        <f>IF(A174="","",COUNTIF('Referral Log'!$C$4:$C$400,A174))</f>
+        <v/>
+      </c>
+      <c r="N174" s="10" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="10" t="n"/>
+      <c r="B175" s="10" t="n"/>
+      <c r="C175" s="11">
+        <f>IF(B175="","",IF(B175="Business broker","1 - Highest",IF(OR(B175="POS installer",B175="Bookkeeper / CPA"),"2 - High",IF(OR(B175="Liquor / food rep",B175="Consultant"),"3 - Strong",IF(B175="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D175" s="10" t="n"/>
+      <c r="E175" s="10" t="n"/>
+      <c r="F175" s="10" t="n"/>
+      <c r="G175" s="10" t="n"/>
+      <c r="H175" s="10" t="n"/>
+      <c r="I175" s="10" t="n"/>
+      <c r="J175" s="12" t="n"/>
+      <c r="K175" s="10" t="n"/>
+      <c r="L175" s="12" t="n"/>
+      <c r="M175" s="11">
+        <f>IF(A175="","",COUNTIF('Referral Log'!$C$4:$C$400,A175))</f>
+        <v/>
+      </c>
+      <c r="N175" s="10" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="10" t="n"/>
+      <c r="B176" s="10" t="n"/>
+      <c r="C176" s="11">
+        <f>IF(B176="","",IF(B176="Business broker","1 - Highest",IF(OR(B176="POS installer",B176="Bookkeeper / CPA"),"2 - High",IF(OR(B176="Liquor / food rep",B176="Consultant"),"3 - Strong",IF(B176="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D176" s="10" t="n"/>
+      <c r="E176" s="10" t="n"/>
+      <c r="F176" s="10" t="n"/>
+      <c r="G176" s="10" t="n"/>
+      <c r="H176" s="10" t="n"/>
+      <c r="I176" s="10" t="n"/>
+      <c r="J176" s="12" t="n"/>
+      <c r="K176" s="10" t="n"/>
+      <c r="L176" s="12" t="n"/>
+      <c r="M176" s="11">
+        <f>IF(A176="","",COUNTIF('Referral Log'!$C$4:$C$400,A176))</f>
+        <v/>
+      </c>
+      <c r="N176" s="10" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="10" t="n"/>
+      <c r="B177" s="10" t="n"/>
+      <c r="C177" s="11">
+        <f>IF(B177="","",IF(B177="Business broker","1 - Highest",IF(OR(B177="POS installer",B177="Bookkeeper / CPA"),"2 - High",IF(OR(B177="Liquor / food rep",B177="Consultant"),"3 - Strong",IF(B177="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D177" s="10" t="n"/>
+      <c r="E177" s="10" t="n"/>
+      <c r="F177" s="10" t="n"/>
+      <c r="G177" s="10" t="n"/>
+      <c r="H177" s="10" t="n"/>
+      <c r="I177" s="10" t="n"/>
+      <c r="J177" s="12" t="n"/>
+      <c r="K177" s="10" t="n"/>
+      <c r="L177" s="12" t="n"/>
+      <c r="M177" s="11">
+        <f>IF(A177="","",COUNTIF('Referral Log'!$C$4:$C$400,A177))</f>
+        <v/>
+      </c>
+      <c r="N177" s="10" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="10" t="n"/>
+      <c r="B178" s="10" t="n"/>
+      <c r="C178" s="11">
+        <f>IF(B178="","",IF(B178="Business broker","1 - Highest",IF(OR(B178="POS installer",B178="Bookkeeper / CPA"),"2 - High",IF(OR(B178="Liquor / food rep",B178="Consultant"),"3 - Strong",IF(B178="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D178" s="10" t="n"/>
+      <c r="E178" s="10" t="n"/>
+      <c r="F178" s="10" t="n"/>
+      <c r="G178" s="10" t="n"/>
+      <c r="H178" s="10" t="n"/>
+      <c r="I178" s="10" t="n"/>
+      <c r="J178" s="12" t="n"/>
+      <c r="K178" s="10" t="n"/>
+      <c r="L178" s="12" t="n"/>
+      <c r="M178" s="11">
+        <f>IF(A178="","",COUNTIF('Referral Log'!$C$4:$C$400,A178))</f>
+        <v/>
+      </c>
+      <c r="N178" s="10" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="10" t="n"/>
+      <c r="B179" s="10" t="n"/>
+      <c r="C179" s="11">
+        <f>IF(B179="","",IF(B179="Business broker","1 - Highest",IF(OR(B179="POS installer",B179="Bookkeeper / CPA"),"2 - High",IF(OR(B179="Liquor / food rep",B179="Consultant"),"3 - Strong",IF(B179="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D179" s="10" t="n"/>
+      <c r="E179" s="10" t="n"/>
+      <c r="F179" s="10" t="n"/>
+      <c r="G179" s="10" t="n"/>
+      <c r="H179" s="10" t="n"/>
+      <c r="I179" s="10" t="n"/>
+      <c r="J179" s="12" t="n"/>
+      <c r="K179" s="10" t="n"/>
+      <c r="L179" s="12" t="n"/>
+      <c r="M179" s="11">
+        <f>IF(A179="","",COUNTIF('Referral Log'!$C$4:$C$400,A179))</f>
+        <v/>
+      </c>
+      <c r="N179" s="10" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="10" t="n"/>
+      <c r="B180" s="10" t="n"/>
+      <c r="C180" s="11">
+        <f>IF(B180="","",IF(B180="Business broker","1 - Highest",IF(OR(B180="POS installer",B180="Bookkeeper / CPA"),"2 - High",IF(OR(B180="Liquor / food rep",B180="Consultant"),"3 - Strong",IF(B180="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D180" s="10" t="n"/>
+      <c r="E180" s="10" t="n"/>
+      <c r="F180" s="10" t="n"/>
+      <c r="G180" s="10" t="n"/>
+      <c r="H180" s="10" t="n"/>
+      <c r="I180" s="10" t="n"/>
+      <c r="J180" s="12" t="n"/>
+      <c r="K180" s="10" t="n"/>
+      <c r="L180" s="12" t="n"/>
+      <c r="M180" s="11">
+        <f>IF(A180="","",COUNTIF('Referral Log'!$C$4:$C$400,A180))</f>
+        <v/>
+      </c>
+      <c r="N180" s="10" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="10" t="n"/>
+      <c r="B181" s="10" t="n"/>
+      <c r="C181" s="11">
+        <f>IF(B181="","",IF(B181="Business broker","1 - Highest",IF(OR(B181="POS installer",B181="Bookkeeper / CPA"),"2 - High",IF(OR(B181="Liquor / food rep",B181="Consultant"),"3 - Strong",IF(B181="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D181" s="10" t="n"/>
+      <c r="E181" s="10" t="n"/>
+      <c r="F181" s="10" t="n"/>
+      <c r="G181" s="10" t="n"/>
+      <c r="H181" s="10" t="n"/>
+      <c r="I181" s="10" t="n"/>
+      <c r="J181" s="12" t="n"/>
+      <c r="K181" s="10" t="n"/>
+      <c r="L181" s="12" t="n"/>
+      <c r="M181" s="11">
+        <f>IF(A181="","",COUNTIF('Referral Log'!$C$4:$C$400,A181))</f>
+        <v/>
+      </c>
+      <c r="N181" s="10" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="10" t="n"/>
+      <c r="B182" s="10" t="n"/>
+      <c r="C182" s="11">
+        <f>IF(B182="","",IF(B182="Business broker","1 - Highest",IF(OR(B182="POS installer",B182="Bookkeeper / CPA"),"2 - High",IF(OR(B182="Liquor / food rep",B182="Consultant"),"3 - Strong",IF(B182="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D182" s="10" t="n"/>
+      <c r="E182" s="10" t="n"/>
+      <c r="F182" s="10" t="n"/>
+      <c r="G182" s="10" t="n"/>
+      <c r="H182" s="10" t="n"/>
+      <c r="I182" s="10" t="n"/>
+      <c r="J182" s="12" t="n"/>
+      <c r="K182" s="10" t="n"/>
+      <c r="L182" s="12" t="n"/>
+      <c r="M182" s="11">
+        <f>IF(A182="","",COUNTIF('Referral Log'!$C$4:$C$400,A182))</f>
+        <v/>
+      </c>
+      <c r="N182" s="10" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="10" t="n"/>
+      <c r="B183" s="10" t="n"/>
+      <c r="C183" s="11">
+        <f>IF(B183="","",IF(B183="Business broker","1 - Highest",IF(OR(B183="POS installer",B183="Bookkeeper / CPA"),"2 - High",IF(OR(B183="Liquor / food rep",B183="Consultant"),"3 - Strong",IF(B183="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D183" s="10" t="n"/>
+      <c r="E183" s="10" t="n"/>
+      <c r="F183" s="10" t="n"/>
+      <c r="G183" s="10" t="n"/>
+      <c r="H183" s="10" t="n"/>
+      <c r="I183" s="10" t="n"/>
+      <c r="J183" s="12" t="n"/>
+      <c r="K183" s="10" t="n"/>
+      <c r="L183" s="12" t="n"/>
+      <c r="M183" s="11">
+        <f>IF(A183="","",COUNTIF('Referral Log'!$C$4:$C$400,A183))</f>
+        <v/>
+      </c>
+      <c r="N183" s="10" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="10" t="n"/>
+      <c r="B184" s="10" t="n"/>
+      <c r="C184" s="11">
+        <f>IF(B184="","",IF(B184="Business broker","1 - Highest",IF(OR(B184="POS installer",B184="Bookkeeper / CPA"),"2 - High",IF(OR(B184="Liquor / food rep",B184="Consultant"),"3 - Strong",IF(B184="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D184" s="10" t="n"/>
+      <c r="E184" s="10" t="n"/>
+      <c r="F184" s="10" t="n"/>
+      <c r="G184" s="10" t="n"/>
+      <c r="H184" s="10" t="n"/>
+      <c r="I184" s="10" t="n"/>
+      <c r="J184" s="12" t="n"/>
+      <c r="K184" s="10" t="n"/>
+      <c r="L184" s="12" t="n"/>
+      <c r="M184" s="11">
+        <f>IF(A184="","",COUNTIF('Referral Log'!$C$4:$C$400,A184))</f>
+        <v/>
+      </c>
+      <c r="N184" s="10" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="10" t="n"/>
+      <c r="B185" s="10" t="n"/>
+      <c r="C185" s="11">
+        <f>IF(B185="","",IF(B185="Business broker","1 - Highest",IF(OR(B185="POS installer",B185="Bookkeeper / CPA"),"2 - High",IF(OR(B185="Liquor / food rep",B185="Consultant"),"3 - Strong",IF(B185="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D185" s="10" t="n"/>
+      <c r="E185" s="10" t="n"/>
+      <c r="F185" s="10" t="n"/>
+      <c r="G185" s="10" t="n"/>
+      <c r="H185" s="10" t="n"/>
+      <c r="I185" s="10" t="n"/>
+      <c r="J185" s="12" t="n"/>
+      <c r="K185" s="10" t="n"/>
+      <c r="L185" s="12" t="n"/>
+      <c r="M185" s="11">
+        <f>IF(A185="","",COUNTIF('Referral Log'!$C$4:$C$400,A185))</f>
+        <v/>
+      </c>
+      <c r="N185" s="10" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="10" t="n"/>
+      <c r="B186" s="10" t="n"/>
+      <c r="C186" s="11">
+        <f>IF(B186="","",IF(B186="Business broker","1 - Highest",IF(OR(B186="POS installer",B186="Bookkeeper / CPA"),"2 - High",IF(OR(B186="Liquor / food rep",B186="Consultant"),"3 - Strong",IF(B186="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D186" s="10" t="n"/>
+      <c r="E186" s="10" t="n"/>
+      <c r="F186" s="10" t="n"/>
+      <c r="G186" s="10" t="n"/>
+      <c r="H186" s="10" t="n"/>
+      <c r="I186" s="10" t="n"/>
+      <c r="J186" s="12" t="n"/>
+      <c r="K186" s="10" t="n"/>
+      <c r="L186" s="12" t="n"/>
+      <c r="M186" s="11">
+        <f>IF(A186="","",COUNTIF('Referral Log'!$C$4:$C$400,A186))</f>
+        <v/>
+      </c>
+      <c r="N186" s="10" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="10" t="n"/>
+      <c r="B187" s="10" t="n"/>
+      <c r="C187" s="11">
+        <f>IF(B187="","",IF(B187="Business broker","1 - Highest",IF(OR(B187="POS installer",B187="Bookkeeper / CPA"),"2 - High",IF(OR(B187="Liquor / food rep",B187="Consultant"),"3 - Strong",IF(B187="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D187" s="10" t="n"/>
+      <c r="E187" s="10" t="n"/>
+      <c r="F187" s="10" t="n"/>
+      <c r="G187" s="10" t="n"/>
+      <c r="H187" s="10" t="n"/>
+      <c r="I187" s="10" t="n"/>
+      <c r="J187" s="12" t="n"/>
+      <c r="K187" s="10" t="n"/>
+      <c r="L187" s="12" t="n"/>
+      <c r="M187" s="11">
+        <f>IF(A187="","",COUNTIF('Referral Log'!$C$4:$C$400,A187))</f>
+        <v/>
+      </c>
+      <c r="N187" s="10" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="10" t="n"/>
+      <c r="B188" s="10" t="n"/>
+      <c r="C188" s="11">
+        <f>IF(B188="","",IF(B188="Business broker","1 - Highest",IF(OR(B188="POS installer",B188="Bookkeeper / CPA"),"2 - High",IF(OR(B188="Liquor / food rep",B188="Consultant"),"3 - Strong",IF(B188="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D188" s="10" t="n"/>
+      <c r="E188" s="10" t="n"/>
+      <c r="F188" s="10" t="n"/>
+      <c r="G188" s="10" t="n"/>
+      <c r="H188" s="10" t="n"/>
+      <c r="I188" s="10" t="n"/>
+      <c r="J188" s="12" t="n"/>
+      <c r="K188" s="10" t="n"/>
+      <c r="L188" s="12" t="n"/>
+      <c r="M188" s="11">
+        <f>IF(A188="","",COUNTIF('Referral Log'!$C$4:$C$400,A188))</f>
+        <v/>
+      </c>
+      <c r="N188" s="10" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="10" t="n"/>
+      <c r="B189" s="10" t="n"/>
+      <c r="C189" s="11">
+        <f>IF(B189="","",IF(B189="Business broker","1 - Highest",IF(OR(B189="POS installer",B189="Bookkeeper / CPA"),"2 - High",IF(OR(B189="Liquor / food rep",B189="Consultant"),"3 - Strong",IF(B189="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D189" s="10" t="n"/>
+      <c r="E189" s="10" t="n"/>
+      <c r="F189" s="10" t="n"/>
+      <c r="G189" s="10" t="n"/>
+      <c r="H189" s="10" t="n"/>
+      <c r="I189" s="10" t="n"/>
+      <c r="J189" s="12" t="n"/>
+      <c r="K189" s="10" t="n"/>
+      <c r="L189" s="12" t="n"/>
+      <c r="M189" s="11">
+        <f>IF(A189="","",COUNTIF('Referral Log'!$C$4:$C$400,A189))</f>
+        <v/>
+      </c>
+      <c r="N189" s="10" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="10" t="n"/>
+      <c r="B190" s="10" t="n"/>
+      <c r="C190" s="11">
+        <f>IF(B190="","",IF(B190="Business broker","1 - Highest",IF(OR(B190="POS installer",B190="Bookkeeper / CPA"),"2 - High",IF(OR(B190="Liquor / food rep",B190="Consultant"),"3 - Strong",IF(B190="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D190" s="10" t="n"/>
+      <c r="E190" s="10" t="n"/>
+      <c r="F190" s="10" t="n"/>
+      <c r="G190" s="10" t="n"/>
+      <c r="H190" s="10" t="n"/>
+      <c r="I190" s="10" t="n"/>
+      <c r="J190" s="12" t="n"/>
+      <c r="K190" s="10" t="n"/>
+      <c r="L190" s="12" t="n"/>
+      <c r="M190" s="11">
+        <f>IF(A190="","",COUNTIF('Referral Log'!$C$4:$C$400,A190))</f>
+        <v/>
+      </c>
+      <c r="N190" s="10" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="10" t="n"/>
+      <c r="B191" s="10" t="n"/>
+      <c r="C191" s="11">
+        <f>IF(B191="","",IF(B191="Business broker","1 - Highest",IF(OR(B191="POS installer",B191="Bookkeeper / CPA"),"2 - High",IF(OR(B191="Liquor / food rep",B191="Consultant"),"3 - Strong",IF(B191="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D191" s="10" t="n"/>
+      <c r="E191" s="10" t="n"/>
+      <c r="F191" s="10" t="n"/>
+      <c r="G191" s="10" t="n"/>
+      <c r="H191" s="10" t="n"/>
+      <c r="I191" s="10" t="n"/>
+      <c r="J191" s="12" t="n"/>
+      <c r="K191" s="10" t="n"/>
+      <c r="L191" s="12" t="n"/>
+      <c r="M191" s="11">
+        <f>IF(A191="","",COUNTIF('Referral Log'!$C$4:$C$400,A191))</f>
+        <v/>
+      </c>
+      <c r="N191" s="10" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="10" t="n"/>
+      <c r="B192" s="10" t="n"/>
+      <c r="C192" s="11">
+        <f>IF(B192="","",IF(B192="Business broker","1 - Highest",IF(OR(B192="POS installer",B192="Bookkeeper / CPA"),"2 - High",IF(OR(B192="Liquor / food rep",B192="Consultant"),"3 - Strong",IF(B192="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D192" s="10" t="n"/>
+      <c r="E192" s="10" t="n"/>
+      <c r="F192" s="10" t="n"/>
+      <c r="G192" s="10" t="n"/>
+      <c r="H192" s="10" t="n"/>
+      <c r="I192" s="10" t="n"/>
+      <c r="J192" s="12" t="n"/>
+      <c r="K192" s="10" t="n"/>
+      <c r="L192" s="12" t="n"/>
+      <c r="M192" s="11">
+        <f>IF(A192="","",COUNTIF('Referral Log'!$C$4:$C$400,A192))</f>
+        <v/>
+      </c>
+      <c r="N192" s="10" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="10" t="n"/>
+      <c r="B193" s="10" t="n"/>
+      <c r="C193" s="11">
+        <f>IF(B193="","",IF(B193="Business broker","1 - Highest",IF(OR(B193="POS installer",B193="Bookkeeper / CPA"),"2 - High",IF(OR(B193="Liquor / food rep",B193="Consultant"),"3 - Strong",IF(B193="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D193" s="10" t="n"/>
+      <c r="E193" s="10" t="n"/>
+      <c r="F193" s="10" t="n"/>
+      <c r="G193" s="10" t="n"/>
+      <c r="H193" s="10" t="n"/>
+      <c r="I193" s="10" t="n"/>
+      <c r="J193" s="12" t="n"/>
+      <c r="K193" s="10" t="n"/>
+      <c r="L193" s="12" t="n"/>
+      <c r="M193" s="11">
+        <f>IF(A193="","",COUNTIF('Referral Log'!$C$4:$C$400,A193))</f>
+        <v/>
+      </c>
+      <c r="N193" s="10" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="10" t="n"/>
+      <c r="B194" s="10" t="n"/>
+      <c r="C194" s="11">
+        <f>IF(B194="","",IF(B194="Business broker","1 - Highest",IF(OR(B194="POS installer",B194="Bookkeeper / CPA"),"2 - High",IF(OR(B194="Liquor / food rep",B194="Consultant"),"3 - Strong",IF(B194="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D194" s="10" t="n"/>
+      <c r="E194" s="10" t="n"/>
+      <c r="F194" s="10" t="n"/>
+      <c r="G194" s="10" t="n"/>
+      <c r="H194" s="10" t="n"/>
+      <c r="I194" s="10" t="n"/>
+      <c r="J194" s="12" t="n"/>
+      <c r="K194" s="10" t="n"/>
+      <c r="L194" s="12" t="n"/>
+      <c r="M194" s="11">
+        <f>IF(A194="","",COUNTIF('Referral Log'!$C$4:$C$400,A194))</f>
+        <v/>
+      </c>
+      <c r="N194" s="10" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="10" t="n"/>
+      <c r="B195" s="10" t="n"/>
+      <c r="C195" s="11">
+        <f>IF(B195="","",IF(B195="Business broker","1 - Highest",IF(OR(B195="POS installer",B195="Bookkeeper / CPA"),"2 - High",IF(OR(B195="Liquor / food rep",B195="Consultant"),"3 - Strong",IF(B195="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D195" s="10" t="n"/>
+      <c r="E195" s="10" t="n"/>
+      <c r="F195" s="10" t="n"/>
+      <c r="G195" s="10" t="n"/>
+      <c r="H195" s="10" t="n"/>
+      <c r="I195" s="10" t="n"/>
+      <c r="J195" s="12" t="n"/>
+      <c r="K195" s="10" t="n"/>
+      <c r="L195" s="12" t="n"/>
+      <c r="M195" s="11">
+        <f>IF(A195="","",COUNTIF('Referral Log'!$C$4:$C$400,A195))</f>
+        <v/>
+      </c>
+      <c r="N195" s="10" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="10" t="n"/>
+      <c r="B196" s="10" t="n"/>
+      <c r="C196" s="11">
+        <f>IF(B196="","",IF(B196="Business broker","1 - Highest",IF(OR(B196="POS installer",B196="Bookkeeper / CPA"),"2 - High",IF(OR(B196="Liquor / food rep",B196="Consultant"),"3 - Strong",IF(B196="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D196" s="10" t="n"/>
+      <c r="E196" s="10" t="n"/>
+      <c r="F196" s="10" t="n"/>
+      <c r="G196" s="10" t="n"/>
+      <c r="H196" s="10" t="n"/>
+      <c r="I196" s="10" t="n"/>
+      <c r="J196" s="12" t="n"/>
+      <c r="K196" s="10" t="n"/>
+      <c r="L196" s="12" t="n"/>
+      <c r="M196" s="11">
+        <f>IF(A196="","",COUNTIF('Referral Log'!$C$4:$C$400,A196))</f>
+        <v/>
+      </c>
+      <c r="N196" s="10" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="10" t="n"/>
+      <c r="B197" s="10" t="n"/>
+      <c r="C197" s="11">
+        <f>IF(B197="","",IF(B197="Business broker","1 - Highest",IF(OR(B197="POS installer",B197="Bookkeeper / CPA"),"2 - High",IF(OR(B197="Liquor / food rep",B197="Consultant"),"3 - Strong",IF(B197="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D197" s="10" t="n"/>
+      <c r="E197" s="10" t="n"/>
+      <c r="F197" s="10" t="n"/>
+      <c r="G197" s="10" t="n"/>
+      <c r="H197" s="10" t="n"/>
+      <c r="I197" s="10" t="n"/>
+      <c r="J197" s="12" t="n"/>
+      <c r="K197" s="10" t="n"/>
+      <c r="L197" s="12" t="n"/>
+      <c r="M197" s="11">
+        <f>IF(A197="","",COUNTIF('Referral Log'!$C$4:$C$400,A197))</f>
+        <v/>
+      </c>
+      <c r="N197" s="10" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="10" t="n"/>
+      <c r="B198" s="10" t="n"/>
+      <c r="C198" s="11">
+        <f>IF(B198="","",IF(B198="Business broker","1 - Highest",IF(OR(B198="POS installer",B198="Bookkeeper / CPA"),"2 - High",IF(OR(B198="Liquor / food rep",B198="Consultant"),"3 - Strong",IF(B198="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D198" s="10" t="n"/>
+      <c r="E198" s="10" t="n"/>
+      <c r="F198" s="10" t="n"/>
+      <c r="G198" s="10" t="n"/>
+      <c r="H198" s="10" t="n"/>
+      <c r="I198" s="10" t="n"/>
+      <c r="J198" s="12" t="n"/>
+      <c r="K198" s="10" t="n"/>
+      <c r="L198" s="12" t="n"/>
+      <c r="M198" s="11">
+        <f>IF(A198="","",COUNTIF('Referral Log'!$C$4:$C$400,A198))</f>
+        <v/>
+      </c>
+      <c r="N198" s="10" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="10" t="n"/>
+      <c r="B199" s="10" t="n"/>
+      <c r="C199" s="11">
+        <f>IF(B199="","",IF(B199="Business broker","1 - Highest",IF(OR(B199="POS installer",B199="Bookkeeper / CPA"),"2 - High",IF(OR(B199="Liquor / food rep",B199="Consultant"),"3 - Strong",IF(B199="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D199" s="10" t="n"/>
+      <c r="E199" s="10" t="n"/>
+      <c r="F199" s="10" t="n"/>
+      <c r="G199" s="10" t="n"/>
+      <c r="H199" s="10" t="n"/>
+      <c r="I199" s="10" t="n"/>
+      <c r="J199" s="12" t="n"/>
+      <c r="K199" s="10" t="n"/>
+      <c r="L199" s="12" t="n"/>
+      <c r="M199" s="11">
+        <f>IF(A199="","",COUNTIF('Referral Log'!$C$4:$C$400,A199))</f>
+        <v/>
+      </c>
+      <c r="N199" s="10" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="10" t="n"/>
+      <c r="B200" s="10" t="n"/>
+      <c r="C200" s="11">
+        <f>IF(B200="","",IF(B200="Business broker","1 - Highest",IF(OR(B200="POS installer",B200="Bookkeeper / CPA"),"2 - High",IF(OR(B200="Liquor / food rep",B200="Consultant"),"3 - Strong",IF(B200="Other","5 - Other","4 - Good")))))</f>
+        <v/>
+      </c>
+      <c r="D200" s="10" t="n"/>
+      <c r="E200" s="10" t="n"/>
+      <c r="F200" s="10" t="n"/>
+      <c r="G200" s="10" t="n"/>
+      <c r="H200" s="10" t="n"/>
+      <c r="I200" s="10" t="n"/>
+      <c r="J200" s="12" t="n"/>
+      <c r="K200" s="10" t="n"/>
+      <c r="L200" s="12" t="n"/>
+      <c r="M200" s="11">
+        <f>IF(A200="","",COUNTIF('Referral Log'!$C$4:$C$400,A200))</f>
+        <v/>
+      </c>
+      <c r="N200" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation sqref="B3:B200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Business broker,POS installer,Bookkeeper / CPA,Liquor / food rep,Consultant,Commercial broker / landlord,Route vendor (linen, uniform, waste, pest),Other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I3:I200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not contacted,Contacted,Agreed to refer,Active - has sent one,Cold"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -24267,7 +29610,7 @@
         </is>
       </c>
       <c r="D16" s="22">
-        <f>COUNTIF('Referral Log'!$G$4:$G$400,"Closed won")</f>
+        <f>COUNTIF('Referral Log'!$I$4:$I$400,"Closed won")</f>
         <v/>
       </c>
       <c r="E16" s="16" t="inlineStr">
@@ -24324,8 +29667,40 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>Active referral partners</t>
+        </is>
+      </c>
+      <c r="D20" s="22">
+        <f>COUNTIF('Referral Partners'!$I$4:$I$200,"Active - has sent one")</f>
+        <v/>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>people who have actually sent you someone</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>From outside the warm list</t>
+        </is>
+      </c>
+      <c r="D21" s="23">
+        <f>IF(COUNTA('Referral Log'!$B$4:$B$400)=0,"",COUNTIFS('Referral Log'!$B$4:$B$400,"&lt;&gt;Warm list",'Referral Log'!$B$4:$B$400,"&lt;&gt;")/COUNTA('Referral Log'!$B$4:$B$400))</f>
+        <v/>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>zero in month one is fine; still zero at month four means nothing replaced the list</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Judge month one against the range above, not against $10k. Clay's first residual was $32.62; Jeremy's was $100.</t>
         </is>
